--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{097511E1-F35A-430D-96E2-16CA5AD53A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C76865-1DBF-4EBA-9C67-5ABD0305E7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
@@ -17,6 +17,9 @@
     <sheet name="クラス一覧" sheetId="2" r:id="rId2"/>
     <sheet name="クラス図" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$5:$G$103</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="83">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -192,6 +195,339 @@
   <si>
     <t>EnemyBase</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>概要</t>
+    <rPh sb="0" eb="2">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>詳細</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>優先度</t>
+    <rPh sb="0" eb="3">
+      <t>ユウセンド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バージョン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実コスト</t>
+    <rPh sb="0" eb="1">
+      <t>ジツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進捗</t>
+    <rPh sb="0" eb="2">
+      <t>シンチョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コリジョンマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロト</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>未着手</t>
+  </si>
+  <si>
+    <t>球と球</t>
+    <rPh sb="0" eb="1">
+      <t>キュウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>球とカプセル</t>
+    <rPh sb="0" eb="1">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>球とモデル</t>
+    <rPh sb="0" eb="1">
+      <t>キュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カプセルとモデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>素材</t>
+    <rPh sb="0" eb="2">
+      <t>ソザイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デバッグ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作成</t>
+    <rPh sb="0" eb="2">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アニメーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リソース管理</t>
+    <rPh sb="4" eb="6">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵1</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵2</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵3</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>回避</t>
+    <rPh sb="0" eb="2">
+      <t>カイヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャスト回避</t>
+    <rPh sb="4" eb="6">
+      <t>カイヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャスト回避反撃</t>
+    <rPh sb="4" eb="6">
+      <t>カイヒ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パリィ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パリィ反撃</t>
+    <rPh sb="3" eb="5">
+      <t>ハンゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1コスト1時間</t>
+    <rPh sb="5" eb="7">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5月</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>月</t>
+    <rPh sb="0" eb="1">
+      <t>ゲツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水</t>
+    <rPh sb="0" eb="1">
+      <t>ミズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木</t>
+    <rPh sb="0" eb="1">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金</t>
+    <rPh sb="0" eb="1">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>土</t>
+    <rPh sb="0" eb="1">
+      <t>ド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日</t>
+    <rPh sb="0" eb="1">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6月</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7月</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8月</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9月</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルファ</t>
+  </si>
+  <si>
+    <t>アルファ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベータ</t>
+  </si>
+  <si>
+    <t>ベータ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マスター</t>
+  </si>
+  <si>
+    <t>マスター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>締め切り</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>修正</t>
+    <rPh sb="0" eb="2">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マスターアップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悪いとこ洗い出し</t>
+    <rPh sb="0" eb="1">
+      <t>ワル</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>アラ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -215,15 +551,51 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -231,14 +603,540 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -247,6 +1145,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCCCC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -575,95 +1478,2012 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="K2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="K3" s="21"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="25"/>
+    </row>
+    <row r="4" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="I4" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M5" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N5" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="O5" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A6" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+      <c r="B6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="7">
+        <v>5</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="9"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10">
         <v>1</v>
       </c>
-      <c r="B5" t="s">
+      <c r="O6" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A7" s="9"/>
+      <c r="B7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="10">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="9">
+        <v>3</v>
+      </c>
+      <c r="J7" s="10">
+        <v>4</v>
+      </c>
+      <c r="K7" s="10">
+        <v>5</v>
+      </c>
+      <c r="L7" s="10">
+        <v>6</v>
+      </c>
+      <c r="M7" s="10">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B6" t="s">
+      <c r="N7" s="10">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B7" t="s">
+      <c r="O7" s="11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A8" s="9"/>
+      <c r="B8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="10">
+        <v>2</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="9">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B8" t="s">
+      <c r="J8" s="10">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B9" t="s">
+      <c r="K8" s="10">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B10" t="s">
+      <c r="L8" s="10">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
+      <c r="M8" s="10">
+        <v>14</v>
+      </c>
+      <c r="N8" s="10">
+        <v>15</v>
+      </c>
+      <c r="O8" s="11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A9" s="9"/>
+      <c r="B9" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="10">
+        <v>2</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="9">
+        <v>17</v>
+      </c>
+      <c r="J9" s="10">
+        <v>18</v>
+      </c>
+      <c r="K9" s="10">
+        <v>19</v>
+      </c>
+      <c r="L9" s="10">
+        <v>20</v>
+      </c>
+      <c r="M9" s="10">
+        <v>21</v>
+      </c>
+      <c r="N9" s="10">
+        <v>22</v>
+      </c>
+      <c r="O9" s="11">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="12"/>
+      <c r="B10" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="13">
+        <v>2</v>
+      </c>
+      <c r="F10" s="13"/>
+      <c r="G10" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="9">
+        <v>24</v>
+      </c>
+      <c r="J10" s="10">
+        <v>25</v>
+      </c>
+      <c r="K10" s="10">
+        <v>26</v>
+      </c>
+      <c r="L10" s="10">
+        <v>27</v>
+      </c>
+      <c r="M10" s="10">
+        <v>28</v>
+      </c>
+      <c r="N10" s="10">
+        <v>29</v>
+      </c>
+      <c r="O10" s="11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" s="12">
+        <v>31</v>
+      </c>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="14"/>
+    </row>
+    <row r="12" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="9"/>
+      <c r="B12" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="10">
+        <v>2</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="9"/>
+      <c r="B13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="10">
         <v>5</v>
       </c>
-      <c r="B13" t="s">
+      <c r="F13" s="10"/>
+      <c r="G13" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A14" s="9"/>
+      <c r="B14" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="10">
+        <v>3</v>
+      </c>
+      <c r="F14" s="10"/>
+      <c r="G14" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="35"/>
+      <c r="J14" s="48">
+        <v>1</v>
+      </c>
+      <c r="K14" s="48">
+        <v>2</v>
+      </c>
+      <c r="L14" s="48">
+        <v>3</v>
+      </c>
+      <c r="M14" s="48">
+        <v>4</v>
+      </c>
+      <c r="N14" s="48">
+        <v>5</v>
+      </c>
+      <c r="O14" s="49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A15" s="9"/>
+      <c r="B15" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="10">
+        <v>3</v>
+      </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="50">
+        <v>7</v>
+      </c>
+      <c r="J15" s="27">
+        <v>8</v>
+      </c>
+      <c r="K15" s="27">
+        <v>9</v>
+      </c>
+      <c r="L15" s="27">
+        <v>10</v>
+      </c>
+      <c r="M15" s="27">
+        <v>11</v>
+      </c>
+      <c r="N15" s="27">
+        <v>12</v>
+      </c>
+      <c r="O15" s="57">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A16" s="9"/>
+      <c r="B16" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="10">
+        <v>2</v>
+      </c>
+      <c r="F16" s="10"/>
+      <c r="G16" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I16" s="50">
+        <v>14</v>
+      </c>
+      <c r="J16" s="27">
+        <v>15</v>
+      </c>
+      <c r="K16" s="27">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B14" t="s">
+      <c r="L16" s="27">
+        <v>17</v>
+      </c>
+      <c r="M16" s="27">
+        <v>18</v>
+      </c>
+      <c r="N16" s="27">
+        <v>19</v>
+      </c>
+      <c r="O16" s="57">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A17" s="9"/>
+      <c r="B17" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="10">
+        <v>4</v>
+      </c>
+      <c r="F17" s="10"/>
+      <c r="G17" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" s="50">
+        <v>21</v>
+      </c>
+      <c r="J17" s="27">
+        <v>22</v>
+      </c>
+      <c r="K17" s="27">
+        <v>23</v>
+      </c>
+      <c r="L17" s="27">
+        <v>24</v>
+      </c>
+      <c r="M17" s="27">
+        <v>25</v>
+      </c>
+      <c r="N17" s="27">
+        <v>26</v>
+      </c>
+      <c r="O17" s="57">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="9"/>
+      <c r="B18" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="10">
+        <v>3</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="58">
+        <v>28</v>
+      </c>
+      <c r="J18" s="59">
+        <v>29</v>
+      </c>
+      <c r="K18" s="59">
+        <v>30</v>
+      </c>
+      <c r="L18" s="45"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="46"/>
+    </row>
+    <row r="19" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="9"/>
+      <c r="B19" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="10">
+        <v>4</v>
+      </c>
+      <c r="F19" s="10"/>
+      <c r="G19" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I19" s="26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="9"/>
+      <c r="B20" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="10">
+        <v>2</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="G20" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="12"/>
+      <c r="B21" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="13">
+        <v>2</v>
+      </c>
+      <c r="F21" s="13"/>
+      <c r="G21" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I21" s="47"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="48">
+        <v>1</v>
+      </c>
+      <c r="M21" s="48">
+        <v>2</v>
+      </c>
+      <c r="N21" s="48">
+        <v>3</v>
+      </c>
+      <c r="O21" s="49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A22" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="7">
+        <v>2</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I22" s="50">
+        <v>5</v>
+      </c>
+      <c r="J22" s="27">
+        <v>6</v>
+      </c>
+      <c r="K22" s="27">
+        <v>7</v>
+      </c>
+      <c r="L22" s="27">
+        <v>8</v>
+      </c>
+      <c r="M22" s="29">
+        <v>9</v>
+      </c>
+      <c r="N22" s="29">
+        <v>10</v>
+      </c>
+      <c r="O22" s="51">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A23" s="9"/>
+      <c r="B23" s="11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B15" t="s">
+      <c r="C23" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="10">
+        <v>5</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" s="52">
+        <v>12</v>
+      </c>
+      <c r="J23" s="29">
+        <v>13</v>
+      </c>
+      <c r="K23" s="29">
+        <v>14</v>
+      </c>
+      <c r="L23" s="29">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
+      <c r="M23" s="29">
+        <v>16</v>
+      </c>
+      <c r="N23" s="29">
+        <v>17</v>
+      </c>
+      <c r="O23" s="51">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="12"/>
+      <c r="B24" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="13">
+        <v>4</v>
+      </c>
+      <c r="F24" s="13"/>
+      <c r="G24" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I24" s="52">
+        <v>19</v>
+      </c>
+      <c r="J24" s="29">
+        <v>20</v>
+      </c>
+      <c r="K24" s="29">
+        <v>21</v>
+      </c>
+      <c r="L24" s="29">
+        <v>22</v>
+      </c>
+      <c r="M24" s="29">
+        <v>23</v>
+      </c>
+      <c r="N24" s="29">
+        <v>24</v>
+      </c>
+      <c r="O24" s="51">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
+      <c r="B25" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
+      <c r="F25" s="7"/>
+      <c r="G25" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I25" s="53">
+        <v>26</v>
+      </c>
+      <c r="J25" s="54">
+        <v>27</v>
+      </c>
+      <c r="K25" s="54">
+        <v>28</v>
+      </c>
+      <c r="L25" s="54">
+        <v>29</v>
+      </c>
+      <c r="M25" s="55">
+        <v>30</v>
+      </c>
+      <c r="N25" s="55">
+        <v>31</v>
+      </c>
+      <c r="O25" s="56"/>
+    </row>
+    <row r="26" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="9"/>
+      <c r="B26" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="10">
+        <v>2</v>
+      </c>
+      <c r="F26" s="10"/>
+      <c r="G26" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I26" s="28" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="12"/>
+      <c r="B27" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
+      <c r="F27" s="13"/>
+      <c r="G27" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="O27" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A28" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="7">
+        <v>6</v>
+      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I28" s="35"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="36"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A29" s="9"/>
+      <c r="B29" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="10">
+        <v>2</v>
+      </c>
+      <c r="F29" s="10"/>
+      <c r="G29" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I29" s="38">
+        <v>2</v>
+      </c>
+      <c r="J29" s="30">
+        <v>3</v>
+      </c>
+      <c r="K29" s="30">
+        <v>4</v>
+      </c>
+      <c r="L29" s="30">
+        <v>5</v>
+      </c>
+      <c r="M29" s="30">
+        <v>6</v>
+      </c>
+      <c r="N29" s="30">
+        <v>7</v>
+      </c>
+      <c r="O29" s="39">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="12"/>
+      <c r="B30" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="13">
+        <v>4</v>
+      </c>
+      <c r="F30" s="13"/>
+      <c r="G30" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I30" s="38">
         <v>9</v>
       </c>
+      <c r="J30" s="30">
+        <v>10</v>
+      </c>
+      <c r="K30" s="30">
+        <v>11</v>
+      </c>
+      <c r="L30" s="30">
+        <v>12</v>
+      </c>
+      <c r="M30" s="30">
+        <v>13</v>
+      </c>
+      <c r="N30" s="30">
+        <v>14</v>
+      </c>
+      <c r="O30" s="39">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" s="16">
+        <v>10</v>
+      </c>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="I31" s="38">
+        <v>16</v>
+      </c>
+      <c r="J31" s="30">
+        <v>17</v>
+      </c>
+      <c r="K31" s="30">
+        <v>18</v>
+      </c>
+      <c r="L31" s="30">
+        <v>19</v>
+      </c>
+      <c r="M31" s="31">
+        <v>20</v>
+      </c>
+      <c r="N31" s="31">
+        <v>21</v>
+      </c>
+      <c r="O31" s="40">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="7">
+        <v>2</v>
+      </c>
+      <c r="F32" s="7"/>
+      <c r="G32" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I32" s="41">
+        <v>23</v>
+      </c>
+      <c r="J32" s="31">
+        <v>24</v>
+      </c>
+      <c r="K32" s="31">
+        <v>25</v>
+      </c>
+      <c r="L32" s="31">
+        <v>26</v>
+      </c>
+      <c r="M32" s="32">
+        <v>27</v>
+      </c>
+      <c r="N32" s="32">
+        <v>28</v>
+      </c>
+      <c r="O32" s="42">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="12"/>
+      <c r="B33" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="13">
+        <v>4</v>
+      </c>
+      <c r="F33" s="13"/>
+      <c r="G33" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I33" s="43">
+        <v>30</v>
+      </c>
+      <c r="J33" s="44">
+        <v>31</v>
+      </c>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45"/>
+      <c r="M33" s="45"/>
+      <c r="N33" s="45"/>
+      <c r="O33" s="46"/>
+    </row>
+    <row r="34" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="7">
+        <v>2</v>
+      </c>
+      <c r="F34" s="7"/>
+      <c r="G34" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I34" s="28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="9"/>
+      <c r="B35" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="10">
+        <v>2</v>
+      </c>
+      <c r="F35" s="10"/>
+      <c r="G35" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="O35" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="9"/>
+      <c r="B36" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" s="10">
+        <v>2</v>
+      </c>
+      <c r="F36" s="10"/>
+      <c r="G36" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="33">
+        <v>1</v>
+      </c>
+      <c r="L36" s="33">
+        <v>2</v>
+      </c>
+      <c r="M36" s="34">
+        <v>3</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="3"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A37" s="9"/>
+      <c r="B37" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" s="10">
+        <v>2</v>
+      </c>
+      <c r="F37" s="10"/>
+      <c r="G37" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A38" s="9"/>
+      <c r="B38" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="10">
+        <v>2</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="12"/>
+      <c r="B39" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" s="13">
+        <v>2</v>
+      </c>
+      <c r="F39" s="13"/>
+      <c r="G39" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A40" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="12"/>
+      <c r="B41" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A42" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="12"/>
+      <c r="B43" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="C44" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44" t="s">
+        <v>36</v>
+      </c>
+      <c r="G44" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="C45" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G45" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="C46" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G46" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="C47" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" t="s">
+        <v>36</v>
+      </c>
+      <c r="G47" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="C48" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" t="s">
+        <v>36</v>
+      </c>
+      <c r="G48" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C49" t="s">
+        <v>37</v>
+      </c>
+      <c r="D49" t="s">
+        <v>36</v>
+      </c>
+      <c r="G49" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C50" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" t="s">
+        <v>36</v>
+      </c>
+      <c r="G50" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C51" t="s">
+        <v>37</v>
+      </c>
+      <c r="D51" t="s">
+        <v>36</v>
+      </c>
+      <c r="G51" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C52" t="s">
+        <v>37</v>
+      </c>
+      <c r="D52" t="s">
+        <v>36</v>
+      </c>
+      <c r="G52" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C53" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53" t="s">
+        <v>36</v>
+      </c>
+      <c r="G53" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C54" t="s">
+        <v>37</v>
+      </c>
+      <c r="D54" t="s">
+        <v>36</v>
+      </c>
+      <c r="G54" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="55" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C55" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" t="s">
+        <v>36</v>
+      </c>
+      <c r="G55" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C56" t="s">
+        <v>37</v>
+      </c>
+      <c r="D56" t="s">
+        <v>36</v>
+      </c>
+      <c r="G56" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="57" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C57" t="s">
+        <v>37</v>
+      </c>
+      <c r="D57" t="s">
+        <v>36</v>
+      </c>
+      <c r="G57" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="58" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C58" t="s">
+        <v>37</v>
+      </c>
+      <c r="D58" t="s">
+        <v>36</v>
+      </c>
+      <c r="G58" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C59" t="s">
+        <v>37</v>
+      </c>
+      <c r="D59" t="s">
+        <v>36</v>
+      </c>
+      <c r="G59" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="60" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C60" t="s">
+        <v>37</v>
+      </c>
+      <c r="D60" t="s">
+        <v>36</v>
+      </c>
+      <c r="G60" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="61" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C61" t="s">
+        <v>37</v>
+      </c>
+      <c r="D61" t="s">
+        <v>36</v>
+      </c>
+      <c r="G61" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="62" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C62" t="s">
+        <v>37</v>
+      </c>
+      <c r="D62" t="s">
+        <v>36</v>
+      </c>
+      <c r="G62" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="63" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C63" t="s">
+        <v>37</v>
+      </c>
+      <c r="D63" t="s">
+        <v>36</v>
+      </c>
+      <c r="G63" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="64" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C64" t="s">
+        <v>37</v>
+      </c>
+      <c r="D64" t="s">
+        <v>36</v>
+      </c>
+      <c r="G64" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C65" t="s">
+        <v>37</v>
+      </c>
+      <c r="D65" t="s">
+        <v>36</v>
+      </c>
+      <c r="G65" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="66" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C66" t="s">
+        <v>37</v>
+      </c>
+      <c r="D66" t="s">
+        <v>36</v>
+      </c>
+      <c r="G66" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="67" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C67" t="s">
+        <v>37</v>
+      </c>
+      <c r="D67" t="s">
+        <v>36</v>
+      </c>
+      <c r="G67" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="68" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C68" t="s">
+        <v>37</v>
+      </c>
+      <c r="D68" t="s">
+        <v>36</v>
+      </c>
+      <c r="G68" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="69" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C69" t="s">
+        <v>37</v>
+      </c>
+      <c r="D69" t="s">
+        <v>36</v>
+      </c>
+      <c r="G69" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="70" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C70" t="s">
+        <v>37</v>
+      </c>
+      <c r="D70" t="s">
+        <v>36</v>
+      </c>
+      <c r="G70" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="71" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C71" t="s">
+        <v>37</v>
+      </c>
+      <c r="D71" t="s">
+        <v>36</v>
+      </c>
+      <c r="G71" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="72" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C72" t="s">
+        <v>37</v>
+      </c>
+      <c r="D72" t="s">
+        <v>36</v>
+      </c>
+      <c r="G72" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="73" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C73" t="s">
+        <v>37</v>
+      </c>
+      <c r="D73" t="s">
+        <v>36</v>
+      </c>
+      <c r="G73" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="74" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C74" t="s">
+        <v>37</v>
+      </c>
+      <c r="D74" t="s">
+        <v>36</v>
+      </c>
+      <c r="G74" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="75" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C75" t="s">
+        <v>37</v>
+      </c>
+      <c r="D75" t="s">
+        <v>36</v>
+      </c>
+      <c r="G75" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="76" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C76" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" t="s">
+        <v>36</v>
+      </c>
+      <c r="G76" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="77" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C77" t="s">
+        <v>37</v>
+      </c>
+      <c r="D77" t="s">
+        <v>36</v>
+      </c>
+      <c r="G77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C78" t="s">
+        <v>37</v>
+      </c>
+      <c r="D78" t="s">
+        <v>36</v>
+      </c>
+      <c r="G78" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="79" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C79" t="s">
+        <v>37</v>
+      </c>
+      <c r="D79" t="s">
+        <v>36</v>
+      </c>
+      <c r="G79" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="80" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C80" t="s">
+        <v>37</v>
+      </c>
+      <c r="D80" t="s">
+        <v>36</v>
+      </c>
+      <c r="G80" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="81" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C81" t="s">
+        <v>37</v>
+      </c>
+      <c r="D81" t="s">
+        <v>36</v>
+      </c>
+      <c r="G81" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="82" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C82" t="s">
+        <v>37</v>
+      </c>
+      <c r="D82" t="s">
+        <v>36</v>
+      </c>
+      <c r="G82" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="83" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C83" t="s">
+        <v>37</v>
+      </c>
+      <c r="D83" t="s">
+        <v>36</v>
+      </c>
+      <c r="G83" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="84" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C84" t="s">
+        <v>37</v>
+      </c>
+      <c r="D84" t="s">
+        <v>36</v>
+      </c>
+      <c r="G84" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="85" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C85" t="s">
+        <v>37</v>
+      </c>
+      <c r="D85" t="s">
+        <v>36</v>
+      </c>
+      <c r="G85" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="86" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C86" t="s">
+        <v>37</v>
+      </c>
+      <c r="D86" t="s">
+        <v>36</v>
+      </c>
+      <c r="G86" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="87" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C87" t="s">
+        <v>37</v>
+      </c>
+      <c r="D87" t="s">
+        <v>36</v>
+      </c>
+      <c r="G87" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="88" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C88" t="s">
+        <v>37</v>
+      </c>
+      <c r="D88" t="s">
+        <v>36</v>
+      </c>
+      <c r="G88" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="89" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C89" t="s">
+        <v>37</v>
+      </c>
+      <c r="D89" t="s">
+        <v>36</v>
+      </c>
+      <c r="G89" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="90" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C90" t="s">
+        <v>37</v>
+      </c>
+      <c r="D90" t="s">
+        <v>36</v>
+      </c>
+      <c r="G90" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="91" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C91" t="s">
+        <v>37</v>
+      </c>
+      <c r="D91" t="s">
+        <v>36</v>
+      </c>
+      <c r="G91" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="92" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C92" t="s">
+        <v>37</v>
+      </c>
+      <c r="D92" t="s">
+        <v>36</v>
+      </c>
+      <c r="G92" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="93" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C93" t="s">
+        <v>37</v>
+      </c>
+      <c r="D93" t="s">
+        <v>36</v>
+      </c>
+      <c r="G93" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="94" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C94" t="s">
+        <v>37</v>
+      </c>
+      <c r="D94" t="s">
+        <v>36</v>
+      </c>
+      <c r="G94" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="95" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C95" t="s">
+        <v>37</v>
+      </c>
+      <c r="D95" t="s">
+        <v>36</v>
+      </c>
+      <c r="G95" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="96" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C96" t="s">
+        <v>37</v>
+      </c>
+      <c r="D96" t="s">
+        <v>36</v>
+      </c>
+      <c r="G96" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="97" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C97" t="s">
+        <v>37</v>
+      </c>
+      <c r="D97" t="s">
+        <v>36</v>
+      </c>
+      <c r="G97" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="98" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C98" t="s">
+        <v>37</v>
+      </c>
+      <c r="D98" t="s">
+        <v>36</v>
+      </c>
+      <c r="G98" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="99" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C99" t="s">
+        <v>37</v>
+      </c>
+      <c r="D99" t="s">
+        <v>36</v>
+      </c>
+      <c r="G99" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="100" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C100" t="s">
+        <v>37</v>
+      </c>
+      <c r="D100" t="s">
+        <v>36</v>
+      </c>
+      <c r="G100" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="101" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C101" t="s">
+        <v>37</v>
+      </c>
+      <c r="D101" t="s">
+        <v>36</v>
+      </c>
+      <c r="G101" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="102" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C102" t="s">
+        <v>37</v>
+      </c>
+      <c r="D102" t="s">
+        <v>36</v>
+      </c>
+      <c r="G102" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="103" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C103" t="s">
+        <v>37</v>
+      </c>
+      <c r="D103" t="s">
+        <v>36</v>
+      </c>
+      <c r="G103" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A5:G103" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}"/>
   <phoneticPr fontId="1"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6:G103" xr:uid="{05F1DF74-5C3A-4656-9180-8CB2E572755F}">
+      <formula1>"未着手,作業中,完了"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C103" xr:uid="{02D66180-7540-49E9-8878-4AAA7C63EEA4}">
+      <formula1>"C,B,A,S"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D103" xr:uid="{485BBF23-C878-4534-89D7-53615FBE9943}">
+      <formula1>"プロト,アルファ,ベータ,マスター"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\SummerGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C76865-1DBF-4EBA-9C67-5ABD0305E7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D25EB52-5944-41A4-8217-49FA6CDC70AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="85">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -528,6 +528,12 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>作業中</t>
+  </si>
+  <si>
+    <t>完了</t>
   </si>
 </sst>
 </file>
@@ -958,7 +964,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -989,9 +995,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1013,15 +1016,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1100,9 +1094,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1125,9 +1116,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1">
@@ -1512,11 +1500,11 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="K3" s="21"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="25"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="21"/>
     </row>
     <row r="4" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="I4" s="5" t="s">
@@ -1545,25 +1533,25 @@
       <c r="G5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="L5" s="16" t="s">
+      <c r="L5" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M5" s="16" t="s">
+      <c r="M5" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="N5" s="16" t="s">
+      <c r="N5" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="O5" s="17" t="s">
+      <c r="O5" s="16" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1588,174 +1576,167 @@
         <v>38</v>
       </c>
       <c r="I6" s="9"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10">
+      <c r="N6">
         <v>1</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7" s="9"/>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="10">
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="10" t="s">
         <v>38</v>
       </c>
       <c r="I7" s="9">
         <v>3</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7">
         <v>4</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7">
         <v>5</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7">
         <v>6</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7">
         <v>7</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7">
         <v>8</v>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="10">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8" s="9"/>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="10">
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8">
         <v>2</v>
       </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="10" t="s">
         <v>38</v>
       </c>
       <c r="I8" s="9">
         <v>10</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8">
         <v>11</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8">
         <v>12</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8">
         <v>13</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8">
         <v>14</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8">
         <v>15</v>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="10">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9" s="9"/>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="10">
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9">
         <v>2</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="10" t="s">
         <v>38</v>
       </c>
       <c r="I9" s="9">
         <v>17</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9">
         <v>18</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9">
         <v>19</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9">
         <v>20</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9">
         <v>21</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9">
         <v>22</v>
       </c>
-      <c r="O9" s="11">
+      <c r="O9" s="10">
         <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="12"/>
-      <c r="B10" s="14" t="s">
+      <c r="A10" s="11"/>
+      <c r="B10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="13">
+      <c r="C10" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="12">
         <v>2</v>
       </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="14" t="s">
-        <v>38</v>
+      <c r="F10" s="12"/>
+      <c r="G10" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="I10" s="9">
         <v>24</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10">
         <v>25</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10">
         <v>26</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10">
         <v>27</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10">
         <v>28</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10">
         <v>29</v>
       </c>
-      <c r="O10" s="11">
+      <c r="O10" s="10">
         <v>30</v>
       </c>
     </row>
@@ -1775,37 +1756,41 @@
       <c r="E11" s="7">
         <v>1</v>
       </c>
-      <c r="F11" s="7"/>
+      <c r="F11" s="7">
+        <v>1.5</v>
+      </c>
       <c r="G11" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11" s="12">
+        <v>84</v>
+      </c>
+      <c r="I11" s="11">
         <v>31</v>
       </c>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="14"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="13"/>
     </row>
     <row r="12" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="9"/>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="10">
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12">
         <v>2</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="11" t="s">
-        <v>38</v>
+      <c r="F12">
+        <v>1.5</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>84</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>67</v>
@@ -1813,20 +1798,19 @@
     </row>
     <row r="13" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="9"/>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="10">
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13">
         <v>5</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="10" t="s">
         <v>38</v>
       </c>
       <c r="I13" s="6" t="s">
@@ -1853,232 +1837,225 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14" s="9"/>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="10">
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14">
         <v>3</v>
       </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I14" s="35"/>
-      <c r="J14" s="48">
+      <c r="G14" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="31"/>
+      <c r="J14" s="43">
         <v>1</v>
       </c>
-      <c r="K14" s="48">
+      <c r="K14" s="43">
         <v>2</v>
       </c>
-      <c r="L14" s="48">
+      <c r="L14" s="43">
         <v>3</v>
       </c>
-      <c r="M14" s="48">
+      <c r="M14" s="43">
         <v>4</v>
       </c>
-      <c r="N14" s="48">
+      <c r="N14" s="43">
         <v>5</v>
       </c>
-      <c r="O14" s="49">
+      <c r="O14" s="44">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A15" s="9"/>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="10">
+      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15">
         <v>3</v>
       </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I15" s="50">
+      <c r="G15" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="45">
         <v>7</v>
       </c>
-      <c r="J15" s="27">
+      <c r="J15" s="23">
         <v>8</v>
       </c>
-      <c r="K15" s="27">
+      <c r="K15" s="23">
         <v>9</v>
       </c>
-      <c r="L15" s="27">
+      <c r="L15" s="23">
         <v>10</v>
       </c>
-      <c r="M15" s="27">
+      <c r="M15" s="23">
         <v>11</v>
       </c>
-      <c r="N15" s="27">
+      <c r="N15" s="23">
         <v>12</v>
       </c>
-      <c r="O15" s="57">
+      <c r="O15" s="51">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A16" s="9"/>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="10">
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16">
         <v>2</v>
       </c>
-      <c r="F16" s="10"/>
-      <c r="G16" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I16" s="50">
+      <c r="G16" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I16" s="45">
         <v>14</v>
       </c>
-      <c r="J16" s="27">
+      <c r="J16" s="23">
         <v>15</v>
       </c>
-      <c r="K16" s="27">
+      <c r="K16" s="23">
         <v>16</v>
       </c>
-      <c r="L16" s="27">
+      <c r="L16" s="23">
         <v>17</v>
       </c>
-      <c r="M16" s="27">
+      <c r="M16" s="23">
         <v>18</v>
       </c>
-      <c r="N16" s="27">
+      <c r="N16" s="23">
         <v>19</v>
       </c>
-      <c r="O16" s="57">
+      <c r="O16" s="51">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A17" s="9"/>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="10">
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17">
         <v>4</v>
       </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I17" s="50">
+      <c r="G17" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" s="45">
         <v>21</v>
       </c>
-      <c r="J17" s="27">
+      <c r="J17" s="23">
         <v>22</v>
       </c>
-      <c r="K17" s="27">
+      <c r="K17" s="23">
         <v>23</v>
       </c>
-      <c r="L17" s="27">
+      <c r="L17" s="23">
         <v>24</v>
       </c>
-      <c r="M17" s="27">
+      <c r="M17" s="23">
         <v>25</v>
       </c>
-      <c r="N17" s="27">
+      <c r="N17" s="23">
         <v>26</v>
       </c>
-      <c r="O17" s="57">
+      <c r="O17" s="51">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="9"/>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="10">
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18">
         <v>3</v>
       </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I18" s="58">
+      <c r="G18" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="52">
         <v>28</v>
       </c>
-      <c r="J18" s="59">
+      <c r="J18" s="53">
         <v>29</v>
       </c>
-      <c r="K18" s="59">
+      <c r="K18" s="53">
         <v>30</v>
       </c>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="45"/>
-      <c r="O18" s="46"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="42"/>
     </row>
     <row r="19" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="9"/>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="10">
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19">
         <v>4</v>
       </c>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I19" s="26" t="s">
+      <c r="G19" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I19" s="22" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="9"/>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" t="s">
         <v>72</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20">
         <v>2</v>
       </c>
-      <c r="F20" s="10"/>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="10" t="s">
         <v>38</v>
       </c>
       <c r="I20" s="6" t="s">
@@ -2104,36 +2081,36 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="12"/>
-      <c r="B21" s="14" t="s">
+      <c r="A21" s="11"/>
+      <c r="B21" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="12">
         <v>2</v>
       </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="I21" s="47"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="48">
+      <c r="F21" s="12"/>
+      <c r="G21" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I21" s="31"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="43">
         <v>1</v>
       </c>
-      <c r="M21" s="48">
+      <c r="M21" s="43">
         <v>2</v>
       </c>
-      <c r="N21" s="48">
+      <c r="N21" s="43">
         <v>3</v>
       </c>
-      <c r="O21" s="49">
+      <c r="O21" s="44">
         <v>4</v>
       </c>
     </row>
@@ -2153,109 +2130,110 @@
       <c r="E22" s="7">
         <v>2</v>
       </c>
-      <c r="F22" s="7"/>
+      <c r="F22" s="7">
+        <v>2</v>
+      </c>
       <c r="G22" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I22" s="50">
+        <v>84</v>
+      </c>
+      <c r="I22" s="45">
         <v>5</v>
       </c>
-      <c r="J22" s="27">
+      <c r="J22" s="23">
         <v>6</v>
       </c>
-      <c r="K22" s="27">
+      <c r="K22" s="23">
         <v>7</v>
       </c>
-      <c r="L22" s="27">
+      <c r="L22" s="23">
         <v>8</v>
       </c>
-      <c r="M22" s="29">
+      <c r="M22" s="25">
         <v>9</v>
       </c>
-      <c r="N22" s="29">
+      <c r="N22" s="25">
         <v>10</v>
       </c>
-      <c r="O22" s="51">
+      <c r="O22" s="46">
         <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A23" s="9"/>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="10">
+      <c r="C23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23">
         <v>5</v>
       </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I23" s="52">
+      <c r="G23" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" s="47">
         <v>12</v>
       </c>
-      <c r="J23" s="29">
+      <c r="J23" s="25">
         <v>13</v>
       </c>
-      <c r="K23" s="29">
+      <c r="K23" s="25">
         <v>14</v>
       </c>
-      <c r="L23" s="29">
+      <c r="L23" s="25">
         <v>15</v>
       </c>
-      <c r="M23" s="29">
+      <c r="M23" s="25">
         <v>16</v>
       </c>
-      <c r="N23" s="29">
+      <c r="N23" s="25">
         <v>17</v>
       </c>
-      <c r="O23" s="51">
+      <c r="O23" s="46">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="12"/>
-      <c r="B24" s="14" t="s">
+      <c r="A24" s="11"/>
+      <c r="B24" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="13">
+      <c r="C24" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="12">
         <v>4</v>
       </c>
-      <c r="F24" s="13"/>
-      <c r="G24" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="I24" s="52">
+      <c r="F24" s="12"/>
+      <c r="G24" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I24" s="47">
         <v>19</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="25">
         <v>20</v>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="25">
         <v>21</v>
       </c>
-      <c r="L24" s="29">
+      <c r="L24" s="25">
         <v>22</v>
       </c>
-      <c r="M24" s="29">
+      <c r="M24" s="25">
         <v>23</v>
       </c>
-      <c r="N24" s="29">
+      <c r="N24" s="25">
         <v>24</v>
       </c>
-      <c r="O24" s="51">
+      <c r="O24" s="46">
         <v>25</v>
       </c>
     </row>
@@ -2279,64 +2257,63 @@
       <c r="G25" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I25" s="53">
+      <c r="I25" s="48">
         <v>26</v>
       </c>
-      <c r="J25" s="54">
+      <c r="J25" s="49">
         <v>27</v>
       </c>
-      <c r="K25" s="54">
+      <c r="K25" s="49">
         <v>28</v>
       </c>
-      <c r="L25" s="54">
+      <c r="L25" s="49">
         <v>29</v>
       </c>
-      <c r="M25" s="55">
+      <c r="M25" s="50">
         <v>30</v>
       </c>
-      <c r="N25" s="55">
+      <c r="N25" s="50">
         <v>31</v>
       </c>
-      <c r="O25" s="56"/>
+      <c r="O25" s="42"/>
     </row>
     <row r="26" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="9"/>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="10">
+      <c r="C26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26">
         <v>2</v>
       </c>
-      <c r="F26" s="10"/>
-      <c r="G26" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I26" s="28" t="s">
+      <c r="G26" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I26" s="24" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="12"/>
-      <c r="B27" s="14" t="s">
+      <c r="A27" s="11"/>
+      <c r="B27" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="13">
+      <c r="C27" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="12">
         <v>3</v>
       </c>
-      <c r="F27" s="13"/>
-      <c r="G27" s="14" t="s">
+      <c r="F27" s="12"/>
+      <c r="G27" s="13" t="s">
         <v>38</v>
       </c>
       <c r="I27" s="6" t="s">
@@ -2381,135 +2358,134 @@
       <c r="G28" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I28" s="35"/>
-      <c r="J28" s="36"/>
-      <c r="K28" s="36"/>
-      <c r="L28" s="36"/>
-      <c r="M28" s="36"/>
-      <c r="N28" s="36"/>
-      <c r="O28" s="37">
+      <c r="I28" s="31"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="33">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A29" s="9"/>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="10">
+      <c r="C29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29">
         <v>2</v>
       </c>
-      <c r="F29" s="10"/>
-      <c r="G29" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I29" s="38">
+      <c r="G29" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I29" s="34">
         <v>2</v>
       </c>
-      <c r="J29" s="30">
+      <c r="J29" s="26">
         <v>3</v>
       </c>
-      <c r="K29" s="30">
+      <c r="K29" s="26">
         <v>4</v>
       </c>
-      <c r="L29" s="30">
+      <c r="L29" s="26">
         <v>5</v>
       </c>
-      <c r="M29" s="30">
+      <c r="M29" s="26">
         <v>6</v>
       </c>
-      <c r="N29" s="30">
+      <c r="N29" s="26">
         <v>7</v>
       </c>
-      <c r="O29" s="39">
+      <c r="O29" s="35">
         <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="12"/>
-      <c r="B30" s="14" t="s">
+      <c r="A30" s="11"/>
+      <c r="B30" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="13">
+      <c r="C30" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="12">
         <v>4</v>
       </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="I30" s="38">
+      <c r="F30" s="12"/>
+      <c r="G30" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I30" s="34">
         <v>9</v>
       </c>
-      <c r="J30" s="30">
+      <c r="J30" s="26">
         <v>10</v>
       </c>
-      <c r="K30" s="30">
+      <c r="K30" s="26">
         <v>11</v>
       </c>
-      <c r="L30" s="30">
+      <c r="L30" s="26">
         <v>12</v>
       </c>
-      <c r="M30" s="30">
+      <c r="M30" s="26">
         <v>13</v>
       </c>
-      <c r="N30" s="30">
+      <c r="N30" s="26">
         <v>14</v>
       </c>
-      <c r="O30" s="39">
+      <c r="O30" s="35">
         <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="15" t="s">
+      <c r="A31" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C31" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="16">
+      <c r="C31" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" s="15">
         <v>10</v>
       </c>
-      <c r="F31" s="16"/>
-      <c r="G31" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="I31" s="38">
+      <c r="F31" s="15"/>
+      <c r="G31" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="I31" s="34">
         <v>16</v>
       </c>
-      <c r="J31" s="30">
+      <c r="J31" s="26">
         <v>17</v>
       </c>
-      <c r="K31" s="30">
+      <c r="K31" s="26">
         <v>18</v>
       </c>
-      <c r="L31" s="30">
+      <c r="L31" s="26">
         <v>19</v>
       </c>
-      <c r="M31" s="31">
+      <c r="M31" s="27">
         <v>20</v>
       </c>
-      <c r="N31" s="31">
+      <c r="N31" s="27">
         <v>21</v>
       </c>
-      <c r="O31" s="40">
+      <c r="O31" s="36">
         <v>22</v>
       </c>
     </row>
@@ -2533,57 +2509,57 @@
       <c r="G32" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I32" s="41">
+      <c r="I32" s="37">
         <v>23</v>
       </c>
-      <c r="J32" s="31">
+      <c r="J32" s="27">
         <v>24</v>
       </c>
-      <c r="K32" s="31">
+      <c r="K32" s="27">
         <v>25</v>
       </c>
-      <c r="L32" s="31">
+      <c r="L32" s="27">
         <v>26</v>
       </c>
-      <c r="M32" s="32">
+      <c r="M32" s="28">
         <v>27</v>
       </c>
-      <c r="N32" s="32">
+      <c r="N32" s="28">
         <v>28</v>
       </c>
-      <c r="O32" s="42">
+      <c r="O32" s="38">
         <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="12"/>
-      <c r="B33" s="14" t="s">
+      <c r="A33" s="11"/>
+      <c r="B33" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33" s="13">
+      <c r="C33" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="12">
         <v>4</v>
       </c>
-      <c r="F33" s="13"/>
-      <c r="G33" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="I33" s="43">
+      <c r="F33" s="12"/>
+      <c r="G33" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I33" s="39">
         <v>30</v>
       </c>
-      <c r="J33" s="44">
+      <c r="J33" s="40">
         <v>31</v>
       </c>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="45"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="46"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="41"/>
+      <c r="O33" s="42"/>
     </row>
     <row r="34" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="6" t="s">
@@ -2601,30 +2577,31 @@
       <c r="E34" s="7">
         <v>2</v>
       </c>
-      <c r="F34" s="7"/>
+      <c r="F34" s="7">
+        <v>2</v>
+      </c>
       <c r="G34" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I34" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="I34" s="24" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="9"/>
-      <c r="B35" s="10" t="s">
+      <c r="B35" t="s">
         <v>50</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E35" s="10">
+      <c r="D35" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35">
         <v>2</v>
       </c>
-      <c r="F35" s="10"/>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="10" t="s">
         <v>38</v>
       </c>
       <c r="I35" s="6" t="s">
@@ -2651,31 +2628,30 @@
     </row>
     <row r="36" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="9"/>
-      <c r="B36" s="10" t="s">
+      <c r="B36" t="s">
         <v>51</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36" s="10">
+      <c r="D36" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36">
         <v>2</v>
       </c>
-      <c r="F36" s="10"/>
-      <c r="G36" s="11" t="s">
+      <c r="G36" s="10" t="s">
         <v>38</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="2"/>
-      <c r="K36" s="33">
+      <c r="K36" s="29">
         <v>1</v>
       </c>
-      <c r="L36" s="33">
+      <c r="L36" s="29">
         <v>2</v>
       </c>
-      <c r="M36" s="34">
+      <c r="M36" s="30">
         <v>3</v>
       </c>
       <c r="N36" s="2"/>
@@ -2683,58 +2659,56 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A37" s="9"/>
-      <c r="B37" s="10" t="s">
+      <c r="B37" t="s">
         <v>52</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E37" s="10">
+      <c r="D37" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37">
         <v>2</v>
       </c>
-      <c r="F37" s="10"/>
-      <c r="G37" s="11" t="s">
+      <c r="G37" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A38" s="9"/>
-      <c r="B38" s="10" t="s">
+      <c r="B38" t="s">
         <v>4</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38" s="10">
+      <c r="D38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38">
         <v>2</v>
       </c>
-      <c r="F38" s="10"/>
-      <c r="G38" s="11" t="s">
+      <c r="G38" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="12"/>
-      <c r="B39" s="13" t="s">
+      <c r="A39" s="11"/>
+      <c r="B39" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C39" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" s="13">
+      <c r="C39" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" s="12">
         <v>2</v>
       </c>
-      <c r="F39" s="13"/>
-      <c r="G39" s="14" t="s">
+      <c r="F39" s="12"/>
+      <c r="G39" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2742,35 +2716,33 @@
       <c r="A40" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" s="10" t="s">
+      <c r="C40" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" t="s">
         <v>74</v>
       </c>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="11" t="s">
+      <c r="G40" s="10" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="12"/>
-      <c r="B41" s="20" t="s">
+      <c r="A41" s="11"/>
+      <c r="B41" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D41" s="13" t="s">
+      <c r="C41" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="14" t="s">
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2778,7 +2750,7 @@
       <c r="A42" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="19" t="s">
+      <c r="B42" s="8" t="s">
         <v>81</v>
       </c>
       <c r="C42" s="7" t="s">
@@ -2794,19 +2766,19 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="12"/>
-      <c r="B43" s="20" t="s">
+      <c r="A43" s="11"/>
+      <c r="B43" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43" s="13" t="s">
+      <c r="C43" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="14" t="s">
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="13" t="s">
         <v>38</v>
       </c>
     </row>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D25EB52-5944-41A4-8217-49FA6CDC70AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE7F5A2-DC2B-421F-8C41-AAEB4FF3F76F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
-    <sheet name="クラス一覧" sheetId="2" r:id="rId2"/>
-    <sheet name="クラス図" sheetId="3" r:id="rId3"/>
+    <sheet name="カレンダー" sheetId="4" r:id="rId2"/>
+    <sheet name="クラス一覧" sheetId="2" r:id="rId3"/>
+    <sheet name="クラス図" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$5:$G$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$G$102</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="93">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -530,10 +531,55 @@
     <t>A</t>
   </si>
   <si>
-    <t>作業中</t>
-  </si>
-  <si>
     <t>完了</t>
+  </si>
+  <si>
+    <t>必殺技ゲージ</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>総コスト</t>
+    <rPh sb="0" eb="1">
+      <t>ソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すべて</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルファ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベータ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マスター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未完了</t>
+    <rPh sb="0" eb="3">
+      <t>ミカンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進捗率</t>
+    <rPh sb="0" eb="3">
+      <t>シンチョクリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1466,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}">
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
@@ -1474,7 +1520,7 @@
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1482,111 +1528,121 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="K2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M2" t="s">
-        <v>75</v>
-      </c>
-      <c r="N2" t="s">
-        <v>77</v>
-      </c>
-      <c r="O2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="K3" s="17"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="21"/>
-    </row>
-    <row r="4" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="I4" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
+    <row r="2" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="3" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="M5" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="N5" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="O5" s="16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
+      <c r="J3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="7">
+      <c r="C4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="7">
         <v>5</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="9"/>
-      <c r="N6">
+      <c r="F4" s="7"/>
+      <c r="G4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J4">
+        <f>SUM(E4:E100)</f>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A5" s="9"/>
+      <c r="B5" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="O6" s="10">
+      <c r="G5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5">
+        <f>SUMIFS(E4:E100,D4:D100,"プロト")</f>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A6" s="9"/>
+      <c r="B6" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="G6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" t="s">
+        <v>88</v>
+      </c>
+      <c r="J6">
+        <f>SUMIFS(E4:E100,D4:D100,"アルファ")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="9"/>
       <c r="B7" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
         <v>37</v>
@@ -1595,187 +1651,116 @@
         <v>36</v>
       </c>
       <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" t="s">
+        <v>89</v>
+      </c>
+      <c r="J7">
+        <f>SUMIFS(E4:E100,D4:D100,"ベータ")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="11"/>
+      <c r="B8" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="12">
+        <v>2</v>
+      </c>
+      <c r="F8" s="12">
+        <v>3</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J8">
+        <f>SUMIFS(E4:E100,D4:D100,"マスター")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A9" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="9">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
+      <c r="B9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>1.5</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11">
         <v>5</v>
       </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
-      </c>
-      <c r="N7">
-        <v>8</v>
-      </c>
-      <c r="O7" s="10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" s="9">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>11</v>
-      </c>
-      <c r="K8">
-        <v>12</v>
-      </c>
-      <c r="L8">
-        <v>13</v>
-      </c>
-      <c r="M8">
-        <v>14</v>
-      </c>
-      <c r="N8">
-        <v>15</v>
-      </c>
-      <c r="O8" s="10">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="9">
-        <v>17</v>
-      </c>
-      <c r="J9">
-        <v>18</v>
-      </c>
-      <c r="K9">
-        <v>19</v>
-      </c>
-      <c r="L9">
-        <v>20</v>
-      </c>
-      <c r="M9">
-        <v>21</v>
-      </c>
-      <c r="N9">
-        <v>22</v>
-      </c>
-      <c r="O9" s="10">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="11"/>
-      <c r="B10" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="12">
-        <v>2</v>
-      </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="13" t="s">
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="I10" s="9">
-        <v>24</v>
-      </c>
-      <c r="J10">
-        <v>25</v>
-      </c>
-      <c r="K10">
-        <v>26</v>
-      </c>
-      <c r="L10">
-        <v>27</v>
-      </c>
-      <c r="M10">
-        <v>28</v>
-      </c>
-      <c r="N10">
-        <v>29</v>
-      </c>
-      <c r="O10" s="10">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1</v>
-      </c>
-      <c r="F11" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I11" s="11">
-        <v>31</v>
-      </c>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="13"/>
-    </row>
-    <row r="12" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="9"/>
       <c r="B12" s="10" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
         <v>37</v>
@@ -1784,22 +1769,19 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="9"/>
       <c r="B13" s="10" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
         <v>37</v>
@@ -1808,37 +1790,16 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="9"/>
       <c r="B14" s="10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
         <v>37</v>
@@ -1847,35 +1808,16 @@
         <v>36</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I14" s="31"/>
-      <c r="J14" s="43">
-        <v>1</v>
-      </c>
-      <c r="K14" s="43">
-        <v>2</v>
-      </c>
-      <c r="L14" s="43">
-        <v>3</v>
-      </c>
-      <c r="M14" s="43">
-        <v>4</v>
-      </c>
-      <c r="N14" s="43">
-        <v>5</v>
-      </c>
-      <c r="O14" s="44">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="9"/>
       <c r="B15" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
         <v>37</v>
@@ -1884,37 +1826,16 @@
         <v>36</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I15" s="45">
-        <v>7</v>
-      </c>
-      <c r="J15" s="23">
-        <v>8</v>
-      </c>
-      <c r="K15" s="23">
-        <v>9</v>
-      </c>
-      <c r="L15" s="23">
-        <v>10</v>
-      </c>
-      <c r="M15" s="23">
-        <v>11</v>
-      </c>
-      <c r="N15" s="23">
-        <v>12</v>
-      </c>
-      <c r="O15" s="51">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="9"/>
       <c r="B16" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
         <v>37</v>
@@ -1923,37 +1844,16 @@
         <v>36</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I16" s="45">
-        <v>14</v>
-      </c>
-      <c r="J16" s="23">
-        <v>15</v>
-      </c>
-      <c r="K16" s="23">
-        <v>16</v>
-      </c>
-      <c r="L16" s="23">
-        <v>17</v>
-      </c>
-      <c r="M16" s="23">
-        <v>18</v>
-      </c>
-      <c r="N16" s="23">
-        <v>19</v>
-      </c>
-      <c r="O16" s="51">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="9"/>
       <c r="B17" s="10" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
         <v>37</v>
@@ -1962,37 +1862,16 @@
         <v>36</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I17" s="45">
-        <v>21</v>
-      </c>
-      <c r="J17" s="23">
-        <v>22</v>
-      </c>
-      <c r="K17" s="23">
-        <v>23</v>
-      </c>
-      <c r="L17" s="23">
-        <v>24</v>
-      </c>
-      <c r="M17" s="23">
-        <v>25</v>
-      </c>
-      <c r="N17" s="23">
-        <v>26</v>
-      </c>
-      <c r="O17" s="51">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="9"/>
       <c r="B18" s="10" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
         <v>37</v>
@@ -2001,596 +1880,331 @@
         <v>36</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I18" s="52">
-        <v>28</v>
-      </c>
-      <c r="J18" s="53">
-        <v>29</v>
-      </c>
-      <c r="K18" s="53">
-        <v>30</v>
-      </c>
-      <c r="L18" s="41"/>
-      <c r="M18" s="41"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="42"/>
-    </row>
-    <row r="19" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="9"/>
       <c r="B19" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="11"/>
+      <c r="B20" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="12">
+        <v>2</v>
+      </c>
+      <c r="F20" s="12"/>
+      <c r="G20" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2</v>
+      </c>
+      <c r="F21" s="7">
+        <v>2</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="9"/>
+      <c r="B22" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22">
+        <v>5</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="11"/>
+      <c r="B23" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="12">
         <v>4</v>
       </c>
-      <c r="G19" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I19" s="22" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="9"/>
-      <c r="B20" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20">
+      <c r="F23" s="12"/>
+      <c r="G23" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="11"/>
-      <c r="B21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" s="12">
+      <c r="B24" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="7">
+        <v>4</v>
+      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="9"/>
+      <c r="B25" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25">
         <v>2</v>
       </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I21" s="31"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="43">
+      <c r="G25" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="11"/>
+      <c r="B26" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="12">
+        <v>3</v>
+      </c>
+      <c r="F26" s="12"/>
+      <c r="G26" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="7">
+        <v>6</v>
+      </c>
+      <c r="F27" s="7"/>
+      <c r="G27" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="9"/>
+      <c r="B28" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="11"/>
+      <c r="B29" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="12">
+        <v>4</v>
+      </c>
+      <c r="F29" s="12"/>
+      <c r="G29" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="15">
+        <v>10</v>
+      </c>
+      <c r="F30" s="15"/>
+      <c r="G30" s="16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" s="7">
+        <v>2</v>
+      </c>
+      <c r="F31" s="7"/>
+      <c r="G31" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="11"/>
+      <c r="B32" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="12">
+        <v>4</v>
+      </c>
+      <c r="F32" s="12"/>
+      <c r="G32" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="M21" s="43">
+      <c r="C33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="7">
         <v>2</v>
       </c>
-      <c r="N21" s="43">
-        <v>3</v>
-      </c>
-      <c r="O21" s="44">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A22" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="7">
+      <c r="F33" s="7">
         <v>2</v>
       </c>
-      <c r="F22" s="7">
+      <c r="G33" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="9"/>
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34">
         <v>2</v>
       </c>
-      <c r="G22" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I22" s="45">
-        <v>5</v>
-      </c>
-      <c r="J22" s="23">
-        <v>6</v>
-      </c>
-      <c r="K22" s="23">
-        <v>7</v>
-      </c>
-      <c r="L22" s="23">
-        <v>8</v>
-      </c>
-      <c r="M22" s="25">
-        <v>9</v>
-      </c>
-      <c r="N22" s="25">
-        <v>10</v>
-      </c>
-      <c r="O22" s="46">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A23" s="9"/>
-      <c r="B23" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23">
-        <v>5</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I23" s="47">
-        <v>12</v>
-      </c>
-      <c r="J23" s="25">
-        <v>13</v>
-      </c>
-      <c r="K23" s="25">
-        <v>14</v>
-      </c>
-      <c r="L23" s="25">
-        <v>15</v>
-      </c>
-      <c r="M23" s="25">
-        <v>16</v>
-      </c>
-      <c r="N23" s="25">
-        <v>17</v>
-      </c>
-      <c r="O23" s="46">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="11"/>
-      <c r="B24" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="12">
-        <v>4</v>
-      </c>
-      <c r="F24" s="12"/>
-      <c r="G24" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I24" s="47">
-        <v>19</v>
-      </c>
-      <c r="J24" s="25">
-        <v>20</v>
-      </c>
-      <c r="K24" s="25">
-        <v>21</v>
-      </c>
-      <c r="L24" s="25">
-        <v>22</v>
-      </c>
-      <c r="M24" s="25">
-        <v>23</v>
-      </c>
-      <c r="N24" s="25">
-        <v>24</v>
-      </c>
-      <c r="O24" s="46">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="7">
-        <v>4</v>
-      </c>
-      <c r="F25" s="7"/>
-      <c r="G25" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I25" s="48">
-        <v>26</v>
-      </c>
-      <c r="J25" s="49">
-        <v>27</v>
-      </c>
-      <c r="K25" s="49">
-        <v>28</v>
-      </c>
-      <c r="L25" s="49">
-        <v>29</v>
-      </c>
-      <c r="M25" s="50">
-        <v>30</v>
-      </c>
-      <c r="N25" s="50">
-        <v>31</v>
-      </c>
-      <c r="O25" s="42"/>
-    </row>
-    <row r="26" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="9"/>
-      <c r="B26" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I26" s="24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="11"/>
-      <c r="B27" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="12">
-        <v>3</v>
-      </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="N27" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="O27" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A28" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="7">
-        <v>6</v>
-      </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I28" s="31"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
-      <c r="O28" s="33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A29" s="9"/>
-      <c r="B29" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29">
-        <v>2</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="I29" s="34">
-        <v>2</v>
-      </c>
-      <c r="J29" s="26">
-        <v>3</v>
-      </c>
-      <c r="K29" s="26">
-        <v>4</v>
-      </c>
-      <c r="L29" s="26">
-        <v>5</v>
-      </c>
-      <c r="M29" s="26">
-        <v>6</v>
-      </c>
-      <c r="N29" s="26">
-        <v>7</v>
-      </c>
-      <c r="O29" s="35">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="11"/>
-      <c r="B30" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="12">
-        <v>4</v>
-      </c>
-      <c r="F30" s="12"/>
-      <c r="G30" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I30" s="34">
-        <v>9</v>
-      </c>
-      <c r="J30" s="26">
-        <v>10</v>
-      </c>
-      <c r="K30" s="26">
-        <v>11</v>
-      </c>
-      <c r="L30" s="26">
-        <v>12</v>
-      </c>
-      <c r="M30" s="26">
-        <v>13</v>
-      </c>
-      <c r="N30" s="26">
-        <v>14</v>
-      </c>
-      <c r="O30" s="35">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="15">
-        <v>10</v>
-      </c>
-      <c r="F31" s="15"/>
-      <c r="G31" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="I31" s="34">
-        <v>16</v>
-      </c>
-      <c r="J31" s="26">
-        <v>17</v>
-      </c>
-      <c r="K31" s="26">
-        <v>18</v>
-      </c>
-      <c r="L31" s="26">
-        <v>19</v>
-      </c>
-      <c r="M31" s="27">
-        <v>20</v>
-      </c>
-      <c r="N31" s="27">
-        <v>21</v>
-      </c>
-      <c r="O31" s="36">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A32" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E32" s="7">
-        <v>2</v>
-      </c>
-      <c r="F32" s="7"/>
-      <c r="G32" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I32" s="37">
-        <v>23</v>
-      </c>
-      <c r="J32" s="27">
-        <v>24</v>
-      </c>
-      <c r="K32" s="27">
-        <v>25</v>
-      </c>
-      <c r="L32" s="27">
-        <v>26</v>
-      </c>
-      <c r="M32" s="28">
-        <v>27</v>
-      </c>
-      <c r="N32" s="28">
-        <v>28</v>
-      </c>
-      <c r="O32" s="38">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="11"/>
-      <c r="B33" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33" s="12">
-        <v>4</v>
-      </c>
-      <c r="F33" s="12"/>
-      <c r="G33" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I33" s="39">
-        <v>30</v>
-      </c>
-      <c r="J33" s="40">
-        <v>31</v>
-      </c>
-      <c r="K33" s="41"/>
-      <c r="L33" s="41"/>
-      <c r="M33" s="41"/>
-      <c r="N33" s="41"/>
-      <c r="O33" s="42"/>
-    </row>
-    <row r="34" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="7">
-        <v>2</v>
-      </c>
-      <c r="F34" s="7">
-        <v>2</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I34" s="24" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G34" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="9"/>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>37</v>
@@ -2604,32 +2218,11 @@
       <c r="G35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I35" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L35" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="M35" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="N35" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="O35" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="9"/>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>37</v>
@@ -2643,24 +2236,11 @@
       <c r="G36" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I36" s="1"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="29">
-        <v>1</v>
-      </c>
-      <c r="L36" s="29">
-        <v>2</v>
-      </c>
-      <c r="M36" s="30">
-        <v>3</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="3"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="9"/>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>37</v>
@@ -2675,114 +2255,107 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A38" s="9"/>
-      <c r="B38" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38">
+    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="11"/>
+      <c r="B38" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="12">
         <v>2</v>
       </c>
-      <c r="G38" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="11"/>
-      <c r="B39" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E39" s="12">
-        <v>2</v>
-      </c>
-      <c r="F39" s="12"/>
-      <c r="G39" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A40" s="9" t="s">
+      <c r="F38" s="12"/>
+      <c r="G38" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B39" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C40" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="C39" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" t="s">
         <v>74</v>
       </c>
-      <c r="G40" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="11"/>
-      <c r="B41" s="13" t="s">
+      <c r="G39" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="11"/>
+      <c r="B40" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C41" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D41" s="12" t="s">
+      <c r="C40" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A42" s="6" t="s">
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B41" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C42" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" s="7" t="s">
+      <c r="C41" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="11"/>
-      <c r="B43" s="13" t="s">
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="11"/>
+      <c r="B42" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C43" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43" s="12" t="s">
+      <c r="C42" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="C43" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C44" t="s">
         <v>37</v>
       </c>
@@ -2793,7 +2366,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C45" t="s">
         <v>37</v>
       </c>
@@ -2804,7 +2377,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C46" t="s">
         <v>37</v>
       </c>
@@ -2815,7 +2388,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C47" t="s">
         <v>37</v>
       </c>
@@ -2826,7 +2399,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C48" t="s">
         <v>37</v>
       </c>
@@ -3431,28 +3004,17 @@
         <v>38</v>
       </c>
     </row>
-    <row r="103" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C103" t="s">
-        <v>37</v>
-      </c>
-      <c r="D103" t="s">
-        <v>36</v>
-      </c>
-      <c r="G103" t="s">
-        <v>38</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A5:G103" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}"/>
+  <autoFilter ref="A3:G102" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}"/>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6:G103" xr:uid="{05F1DF74-5C3A-4656-9180-8CB2E572755F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G102" xr:uid="{05F1DF74-5C3A-4656-9180-8CB2E572755F}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C103" xr:uid="{02D66180-7540-49E9-8878-4AAA7C63EEA4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C102" xr:uid="{02D66180-7540-49E9-8878-4AAA7C63EEA4}">
       <formula1>"C,B,A,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D103" xr:uid="{485BBF23-C878-4534-89D7-53615FBE9943}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D102" xr:uid="{485BBF23-C878-4534-89D7-53615FBE9943}">
       <formula1>"プロト,アルファ,ベータ,マスター"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3461,6 +3023,636 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB8A7F07-4822-4AA8-B3C3-66F7A08D4E6E}">
+  <dimension ref="B2:H36"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="D2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D3" s="17"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="21"/>
+    </row>
+    <row r="4" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B6" s="9"/>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B7" s="9">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7" s="10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B8" s="9">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>14</v>
+      </c>
+      <c r="G8">
+        <v>15</v>
+      </c>
+      <c r="H8" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B9" s="9">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>18</v>
+      </c>
+      <c r="D9">
+        <v>19</v>
+      </c>
+      <c r="E9">
+        <v>20</v>
+      </c>
+      <c r="F9">
+        <v>21</v>
+      </c>
+      <c r="G9">
+        <v>22</v>
+      </c>
+      <c r="H9" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B10" s="9">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>25</v>
+      </c>
+      <c r="D10">
+        <v>26</v>
+      </c>
+      <c r="E10">
+        <v>27</v>
+      </c>
+      <c r="F10">
+        <v>28</v>
+      </c>
+      <c r="G10">
+        <v>29</v>
+      </c>
+      <c r="H10" s="10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="11">
+        <v>31</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="13"/>
+    </row>
+    <row r="12" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B14" s="31"/>
+      <c r="C14" s="43">
+        <v>1</v>
+      </c>
+      <c r="D14" s="43">
+        <v>2</v>
+      </c>
+      <c r="E14" s="43">
+        <v>3</v>
+      </c>
+      <c r="F14" s="43">
+        <v>4</v>
+      </c>
+      <c r="G14" s="43">
+        <v>5</v>
+      </c>
+      <c r="H14" s="44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B15" s="45">
+        <v>7</v>
+      </c>
+      <c r="C15" s="23">
+        <v>8</v>
+      </c>
+      <c r="D15" s="23">
+        <v>9</v>
+      </c>
+      <c r="E15" s="23">
+        <v>10</v>
+      </c>
+      <c r="F15" s="23">
+        <v>11</v>
+      </c>
+      <c r="G15" s="23">
+        <v>12</v>
+      </c>
+      <c r="H15" s="51">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B16" s="45">
+        <v>14</v>
+      </c>
+      <c r="C16" s="23">
+        <v>15</v>
+      </c>
+      <c r="D16" s="23">
+        <v>16</v>
+      </c>
+      <c r="E16" s="23">
+        <v>17</v>
+      </c>
+      <c r="F16" s="23">
+        <v>18</v>
+      </c>
+      <c r="G16" s="23">
+        <v>19</v>
+      </c>
+      <c r="H16" s="51">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B17" s="45">
+        <v>21</v>
+      </c>
+      <c r="C17" s="23">
+        <v>22</v>
+      </c>
+      <c r="D17" s="23">
+        <v>23</v>
+      </c>
+      <c r="E17" s="23">
+        <v>24</v>
+      </c>
+      <c r="F17" s="23">
+        <v>25</v>
+      </c>
+      <c r="G17" s="23">
+        <v>26</v>
+      </c>
+      <c r="H17" s="51">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="52">
+        <v>28</v>
+      </c>
+      <c r="C18" s="53">
+        <v>29</v>
+      </c>
+      <c r="D18" s="53">
+        <v>30</v>
+      </c>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="42"/>
+    </row>
+    <row r="19" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B20" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B21" s="31"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="43">
+        <v>1</v>
+      </c>
+      <c r="F21" s="43">
+        <v>2</v>
+      </c>
+      <c r="G21" s="43">
+        <v>3</v>
+      </c>
+      <c r="H21" s="44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B22" s="45">
+        <v>5</v>
+      </c>
+      <c r="C22" s="23">
+        <v>6</v>
+      </c>
+      <c r="D22" s="23">
+        <v>7</v>
+      </c>
+      <c r="E22" s="23">
+        <v>8</v>
+      </c>
+      <c r="F22" s="25">
+        <v>9</v>
+      </c>
+      <c r="G22" s="25">
+        <v>10</v>
+      </c>
+      <c r="H22" s="46">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B23" s="47">
+        <v>12</v>
+      </c>
+      <c r="C23" s="25">
+        <v>13</v>
+      </c>
+      <c r="D23" s="25">
+        <v>14</v>
+      </c>
+      <c r="E23" s="25">
+        <v>15</v>
+      </c>
+      <c r="F23" s="25">
+        <v>16</v>
+      </c>
+      <c r="G23" s="25">
+        <v>17</v>
+      </c>
+      <c r="H23" s="46">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B24" s="47">
+        <v>19</v>
+      </c>
+      <c r="C24" s="25">
+        <v>20</v>
+      </c>
+      <c r="D24" s="25">
+        <v>21</v>
+      </c>
+      <c r="E24" s="25">
+        <v>22</v>
+      </c>
+      <c r="F24" s="25">
+        <v>23</v>
+      </c>
+      <c r="G24" s="25">
+        <v>24</v>
+      </c>
+      <c r="H24" s="46">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B25" s="48">
+        <v>26</v>
+      </c>
+      <c r="C25" s="49">
+        <v>27</v>
+      </c>
+      <c r="D25" s="49">
+        <v>28</v>
+      </c>
+      <c r="E25" s="49">
+        <v>29</v>
+      </c>
+      <c r="F25" s="50">
+        <v>30</v>
+      </c>
+      <c r="G25" s="50">
+        <v>31</v>
+      </c>
+      <c r="H25" s="42"/>
+    </row>
+    <row r="26" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="24" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B28" s="31"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B29" s="34">
+        <v>2</v>
+      </c>
+      <c r="C29" s="26">
+        <v>3</v>
+      </c>
+      <c r="D29" s="26">
+        <v>4</v>
+      </c>
+      <c r="E29" s="26">
+        <v>5</v>
+      </c>
+      <c r="F29" s="26">
+        <v>6</v>
+      </c>
+      <c r="G29" s="26">
+        <v>7</v>
+      </c>
+      <c r="H29" s="35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B30" s="34">
+        <v>9</v>
+      </c>
+      <c r="C30" s="26">
+        <v>10</v>
+      </c>
+      <c r="D30" s="26">
+        <v>11</v>
+      </c>
+      <c r="E30" s="26">
+        <v>12</v>
+      </c>
+      <c r="F30" s="26">
+        <v>13</v>
+      </c>
+      <c r="G30" s="26">
+        <v>14</v>
+      </c>
+      <c r="H30" s="35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B31" s="34">
+        <v>16</v>
+      </c>
+      <c r="C31" s="26">
+        <v>17</v>
+      </c>
+      <c r="D31" s="26">
+        <v>18</v>
+      </c>
+      <c r="E31" s="26">
+        <v>19</v>
+      </c>
+      <c r="F31" s="27">
+        <v>20</v>
+      </c>
+      <c r="G31" s="27">
+        <v>21</v>
+      </c>
+      <c r="H31" s="36">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B32" s="37">
+        <v>23</v>
+      </c>
+      <c r="C32" s="27">
+        <v>24</v>
+      </c>
+      <c r="D32" s="27">
+        <v>25</v>
+      </c>
+      <c r="E32" s="27">
+        <v>26</v>
+      </c>
+      <c r="F32" s="28">
+        <v>27</v>
+      </c>
+      <c r="G32" s="28">
+        <v>28</v>
+      </c>
+      <c r="H32" s="38">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B33" s="39">
+        <v>30</v>
+      </c>
+      <c r="C33" s="40">
+        <v>31</v>
+      </c>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="42"/>
+    </row>
+    <row r="34" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B34" s="24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B35" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B36" s="1"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="29">
+        <v>1</v>
+      </c>
+      <c r="E36" s="29">
+        <v>2</v>
+      </c>
+      <c r="F36" s="30">
+        <v>3</v>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7012B8F-1C48-446B-B3CE-6022D8D4AF46}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -3526,7 +3718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B5AFA5-DA2E-4B9D-AA4F-6348B1D1D3C1}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE7F5A2-DC2B-421F-8C41-AAEB4FF3F76F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A93499-90C5-4DB8-8813-7733E2DD4191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
     <sheet name="カレンダー" sheetId="4" r:id="rId2"/>
     <sheet name="クラス一覧" sheetId="2" r:id="rId3"/>
     <sheet name="クラス図" sheetId="3" r:id="rId4"/>
+    <sheet name="memo" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$G$102</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="95">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -578,6 +579,17 @@
     <t>進捗率</t>
     <rPh sb="0" eb="3">
       <t>シンチョクリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーのできること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃(コンボ)</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3726,4 +3738,40 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CADF38F-73BE-4B6B-BA66-331B33FA1371}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A93499-90C5-4DB8-8813-7733E2DD4191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5D3B0C-733E-4D7C-92EF-501EF5B9C460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
     <sheet name="カレンダー" sheetId="4" r:id="rId2"/>
     <sheet name="クラス一覧" sheetId="2" r:id="rId3"/>
     <sheet name="クラス図" sheetId="3" r:id="rId4"/>
-    <sheet name="memo" sheetId="5" r:id="rId5"/>
+    <sheet name="プレイヤー設計" sheetId="6" r:id="rId5"/>
+    <sheet name="memo" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$G$102</definedName>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="171">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -583,13 +584,608 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プレイヤーのできること</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>攻撃(コンボ)</t>
+    <t>プレイヤーのできる行動</t>
+    <rPh sb="9" eb="11">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コンボ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フェニックスシフト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>転生の炎</t>
+    <rPh sb="0" eb="2">
+      <t>テンセイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ホノオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ライトニングロッド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガウジ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>斬鉄剣</t>
+    <rPh sb="0" eb="3">
+      <t>ザンテツケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の目の前にテレポート</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自身を中心にでか攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雷のオブジェクトを設置。これに攻撃するとそこから範囲攻撃</t>
+    <rPh sb="0" eb="1">
+      <t>カミナリ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="24" eb="28">
+      <t>ハンイコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>爪で切り裂く連続攻撃</t>
+    <rPh sb="0" eb="1">
+      <t>ツメ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>レンゾクコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲージを消費してめっちゃかっこいい全体攻撃</t>
+    <rPh sb="4" eb="6">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="17" eb="21">
+      <t>ゼンタイコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲージがたまる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SS</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵はボス単体</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラがいっぱい動くからそのへん考えないといけなそう</t>
+    <rPh sb="8" eb="9">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キャラクター</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージは平面で障害物なし</t>
+    <rPh sb="5" eb="7">
+      <t>ヘイメン</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ショウガイブツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーステート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスステート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アプリケーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーンマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルトシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーの細かい設計</t>
+    <rPh sb="6" eb="7">
+      <t>コマ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>待機</t>
+    <rPh sb="0" eb="2">
+      <t>タイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の位置を持つ必要がある</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラ演出</t>
+    <rPh sb="3" eb="5">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>別オブジェクトとして設置する必要がある</t>
+    <rPh sb="0" eb="1">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セッチ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>連打してる間継続してアニメーションを行う</t>
+    <rPh sb="0" eb="2">
+      <t>レンダ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケイゾク</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>オコナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指定したシェーダーを使用して描画を行うクラスが必要そう=シェーダー管理クラス</t>
+    <rPh sb="0" eb="2">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ビョウガ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃の設計</t>
     <rPh sb="0" eb="2">
       <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>セッケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃のデータがいりそう</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃のアニメーション</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たり判定がいつからいつまでいるか</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・攻撃のアニメーション</t>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・当たり判定がいつからいつまでいるか</t>
+    <rPh sb="1" eb="2">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・コンボのキャンセル可能時間</t>
+    <rPh sb="10" eb="12">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課題：敵に当たった瞬間だけダメージ処理</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→攻撃が当たった敵のIDを覚えておいて、すでに当たっていたなら当たり判定しない</t>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オボ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・当たったオブジェクトのIDのList</t>
+    <rPh sb="1" eb="2">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↑この攻撃のデータを管理するクラスもいりそう</t>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課題2：攻撃の汎用化</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ハンヨウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→プレイヤーの攻撃、という感じではなく、プレイヤーでも敵でもおんなじクラスで攻撃判定ができるようにする</t>
+    <rPh sb="7" eb="9">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="38" eb="43">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・どのキャラに当たるか</t>
+    <rPh sb="7" eb="8">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→キャラクタータグみたいなのがいりそう</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームに登場する主要なものをまとめる</t>
+    <rPh sb="4" eb="6">
+      <t>トウジョウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それぞれが持つものをまとめる</t>
+    <rPh sb="5" eb="6">
+      <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・プレイヤー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃の当たり判定</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自身の当たり判定</t>
+    <rPh sb="0" eb="2">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>位置</t>
+    <rPh sb="0" eb="2">
+      <t>イチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>速度</t>
+    <rPh sb="0" eb="2">
+      <t>ソクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モデル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ボス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ステージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・攻撃</t>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>当たったオブジェクトのIDのList</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どのキャラに当たるか</t>
+    <rPh sb="6" eb="7">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓継承</t>
+    <rPh sb="1" eb="3">
+      <t>ケイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーステートベース</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスステートベース</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスどうする？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドラゴン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悪魔的な奴</t>
+    <rPh sb="0" eb="2">
+      <t>アクマ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヤツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鉄巨人</t>
+    <rPh sb="0" eb="3">
+      <t>テツキョジン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3732,42 +4328,544 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B5AFA5-DA2E-4B9D-AA4F-6348B1D1D3C1}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:P14"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>163</v>
+      </c>
+      <c r="I3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="I5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D7" t="s">
+        <v>166</v>
+      </c>
+      <c r="I7" t="s">
+        <v>124</v>
+      </c>
+      <c r="N7" t="s">
+        <v>123</v>
+      </c>
+      <c r="P7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>128</v>
+      </c>
+      <c r="I9" t="s">
+        <v>117</v>
+      </c>
+      <c r="K9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>165</v>
+      </c>
+      <c r="H13" t="s">
+        <v>119</v>
+      </c>
+      <c r="J13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5C4C0C2-367A-48F7-A4B4-6D80F4D5CB06}">
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>135</v>
+      </c>
+      <c r="E16" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>140</v>
+      </c>
+      <c r="E19" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CADF38F-73BE-4B6B-BA66-331B33FA1371}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.75" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B3" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>149</v>
+      </c>
+      <c r="C21" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C26" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C27" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C28" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C30" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C31" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C32" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C33" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C34" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C35" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C36" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C38" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C39" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C40" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C42" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C43" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C44" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C45" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C46" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5D3B0C-733E-4D7C-92EF-501EF5B9C460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7CADDF8-BAF7-4F5B-B123-F26E0543FE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="3600" yWindow="2280" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="176">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1187,6 +1187,29 @@
     <rPh sb="0" eb="3">
       <t>テツキョジン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→オブジェクトにIDを配るIDマネージャーみたいなのがいりそう</t>
+    <rPh sb="11" eb="12">
+      <t>クバ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モデルマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IDマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サウンドマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インプット</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4336,6 +4359,7 @@
     <col min="4" max="5" width="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.25" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.4">
@@ -4350,6 +4374,18 @@
       <c r="I3" t="s">
         <v>121</v>
       </c>
+      <c r="J3" t="s">
+        <v>172</v>
+      </c>
+      <c r="K3" t="s">
+        <v>173</v>
+      </c>
+      <c r="L3" t="s">
+        <v>174</v>
+      </c>
+      <c r="M3" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
@@ -4392,9 +4428,6 @@
     <row r="9" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
         <v>128</v>
-      </c>
-      <c r="I9" t="s">
-        <v>117</v>
       </c>
       <c r="K9" t="s">
         <v>35</v>
@@ -4445,44 +4478,44 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5C4C0C2-367A-48F7-A4B4-6D80F4D5CB06}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="23.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>100</v>
       </c>
@@ -4493,7 +4526,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>101</v>
       </c>
@@ -4501,7 +4534,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>102</v>
       </c>
@@ -4509,7 +4542,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>103</v>
       </c>
@@ -4517,7 +4550,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>98</v>
       </c>
@@ -4528,49 +4561,52 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>135</v>
       </c>
       <c r="E16" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="N16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>138</v>
       </c>
       <c r="E17" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="N17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>140</v>
       </c>
-      <c r="E19" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>143</v>
       </c>
-      <c r="E20" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>147</v>
       </c>
@@ -4578,7 +4614,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>144</v>
       </c>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7CADDF8-BAF7-4F5B-B123-F26E0543FE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF85490A-537A-429C-94FB-4945CF4B95EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3600" yWindow="2280" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="177">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1210,6 +1210,10 @@
   </si>
   <si>
     <t>インプット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ターゲットマネージャー</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4432,6 +4436,9 @@
       <c r="K9" t="s">
         <v>35</v>
       </c>
+      <c r="M9" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B10" t="s">

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF85490A-537A-429C-94FB-4945CF4B95EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BA4B99-4859-44A0-BAE3-68A24317F737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,11 @@
     <sheet name="クラス一覧" sheetId="2" r:id="rId3"/>
     <sheet name="クラス図" sheetId="3" r:id="rId4"/>
     <sheet name="プレイヤー設計" sheetId="6" r:id="rId5"/>
-    <sheet name="memo" sheetId="5" r:id="rId6"/>
+    <sheet name="ゲーム画面イメージ" sheetId="7" r:id="rId6"/>
+    <sheet name="memo" sheetId="5" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$G$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$G$108</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="206">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -114,27 +115,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>必殺技lv1</t>
-    <rPh sb="0" eb="3">
-      <t>ヒッサツワザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>必殺技lv2</t>
-    <rPh sb="0" eb="3">
-      <t>ヒッサツワザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>必殺技lv3</t>
-    <rPh sb="0" eb="3">
-      <t>ヒッサツワザ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ロックオン</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -352,34 +332,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ジャスト回避</t>
-    <rPh sb="4" eb="6">
-      <t>カイヒ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ジャスト回避反撃</t>
-    <rPh sb="4" eb="6">
-      <t>カイヒ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ハンゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>パリィ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>パリィ反撃</t>
-    <rPh sb="3" eb="5">
-      <t>ハンゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1コスト1時間</t>
     <rPh sb="5" eb="7">
       <t>ジカン</t>
@@ -476,9 +428,6 @@
   </si>
   <si>
     <t>アルファ</t>
-  </si>
-  <si>
-    <t>アルファ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -530,9 +479,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>完了</t>
   </si>
   <si>
@@ -1214,6 +1160,211 @@
   </si>
   <si>
     <t>ターゲットマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作業中</t>
+  </si>
+  <si>
+    <t>ライジングフレイム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スカーレットサイクロン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーのスキル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゾンビ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鳥</t>
+    <rPh sb="0" eb="1">
+      <t>トリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オーク</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オークロード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル1(テレポート)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル2(単体攻撃)</t>
+    <rPh sb="5" eb="9">
+      <t>タンタイコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル3(範囲攻撃)</t>
+    <rPh sb="5" eb="9">
+      <t>ハンイコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル4(必殺技)</t>
+    <rPh sb="5" eb="8">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未着手</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遷移</t>
+    <rPh sb="0" eb="2">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー体力</t>
+    <rPh sb="5" eb="7">
+      <t>タイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー必殺ゲージ</t>
+    <rPh sb="5" eb="7">
+      <t>ヒッサツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵体力</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>タイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス体力</t>
+    <rPh sb="2" eb="4">
+      <t>タイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームシーン(雑魚戦)</t>
+    <rPh sb="7" eb="9">
+      <t>ザコ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵体力</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>タイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺ゲージ</t>
+    <rPh sb="0" eb="2">
+      <t>ヒッサツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームシーン(ボス戦)</t>
+    <rPh sb="9" eb="10">
+      <t>セン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作ガイド</t>
+    <rPh sb="0" eb="2">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトルメニュー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リザルトメニュー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーズメニュー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オプションメニュー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雑魚敵</t>
+    <rPh sb="0" eb="3">
+      <t>ザコテキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1238,7 +1389,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1281,6 +1432,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="28">
     <border>
@@ -1645,7 +1802,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1808,6 +1965,57 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1828,6 +2036,1665 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2C976F0-AFD9-254F-807A-9362A6A17E6E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="809625" y="400050"/>
+          <a:ext cx="2152650" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>プレイヤー体力</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>200026</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B01FFF53-E475-482F-BF4D-2D57A53B064E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="809625" y="685801"/>
+          <a:ext cx="1847850" cy="76200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>プレイヤー体力</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="楕円 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21107852-E1DA-1FD3-E059-35C77375E2C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2600325" y="1657350"/>
+          <a:ext cx="762000" cy="1733550"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>プレイヤー</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="楕円 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDAEA0D5-524D-8278-C997-97F5010E14F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4067175" y="1438275"/>
+          <a:ext cx="209550" cy="828675"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="楕円 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{369153F1-DF23-495C-8E72-7DAA1DE9359A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4514850" y="1771650"/>
+          <a:ext cx="209550" cy="828675"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DCB61F8-36BF-13B9-192F-06283B5EF7C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3781425" y="1304925"/>
+          <a:ext cx="752475" cy="47625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DA0E7B8-5C15-4ACC-B177-D5D56100170D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4257675" y="1619250"/>
+          <a:ext cx="752475" cy="47625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B36282A-B39C-4539-4940-CD340CC1A553}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6115050" y="2762250"/>
+          <a:ext cx="1219200" cy="885825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>操作ガイド</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>UI</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="直線矢印コネクタ 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12D8401D-70BF-BD55-F385-381F84C572D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1524000" y="723900"/>
+          <a:ext cx="0" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>33338</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="直線矢印コネクタ 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B42334C-94B3-DB14-53F6-F63EB1733BBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="6" idx="6"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4724400" y="2009775"/>
+          <a:ext cx="819150" cy="176213"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>176213</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="直線矢印コネクタ 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{990BB2CA-6298-EFE3-7614-BCF5D61E75EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="5" idx="6"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="4276725" y="1852613"/>
+          <a:ext cx="1276350" cy="71437"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="直線矢印コネクタ 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94AC126B-DFCF-DFE0-C765-B8B7A7607AF9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4333875" y="952500"/>
+          <a:ext cx="38100" cy="371475"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>519113</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="24" name="直線矢印コネクタ 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51582A8E-84A0-3F8E-F676-AC89587E6B91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="8" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4552950" y="981075"/>
+          <a:ext cx="80963" cy="638175"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="楕円 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D91653E2-3262-4017-B2DD-B0018FFC8430}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2562225" y="5295900"/>
+          <a:ext cx="762000" cy="1733550"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>プレイヤー</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="正方形/長方形 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A9F0904-3441-414A-A6EA-823F8F5E993C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="838200" y="4267200"/>
+          <a:ext cx="2152650" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>プレイヤー体力</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="正方形/長方形 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D35846B-BE74-4DC6-BCF6-F7AD7C4452E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="838200" y="4552951"/>
+          <a:ext cx="1847850" cy="76200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>プレイヤー体力</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="正方形/長方形 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DEC7D24-11E6-45B8-B974-4E1B6A797B7C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6134100" y="6362700"/>
+          <a:ext cx="1219200" cy="885825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>操作ガイド</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>UI</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>219074</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>104776</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>533399</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="楕円 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEED2E41-F40D-4E6B-9BED-2E9B99388A76}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4333874" y="4895851"/>
+          <a:ext cx="1000125" cy="1695450"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ボス</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>666751</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>552451</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="正方形/長方形 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F8AC022-30CD-4C84-939E-81C91EF0981C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4095751" y="4257675"/>
+          <a:ext cx="3314700" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ボス</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>HP</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="正方形/長方形 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D71044A-9442-8275-12E3-4E546839D308}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2228850" y="8077200"/>
+          <a:ext cx="3905250" cy="838200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>タイトル</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="正方形/長方形 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D05CB1E7-788F-4D97-BC79-308C43257EC3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3248025" y="9486900"/>
+          <a:ext cx="1838325" cy="247650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>スタート</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="正方形/長方形 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45B6A834-9D66-4248-B56B-7D2089CE2D41}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3238500" y="9867900"/>
+          <a:ext cx="1838325" cy="247650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>オプション</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="正方形/長方形 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E553A48A-0F86-42A8-893E-0D99C77FBAED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3219450" y="10267950"/>
+          <a:ext cx="1838325" cy="247650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>終了</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>209551</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="正方形/長方形 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E09BE1B-D711-43C6-A960-7884BDB72429}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3457575" y="11944351"/>
+          <a:ext cx="1438275" cy="1390650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ランク</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>238124</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>409576</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="正方形/長方形 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EB9F24F-F338-4E50-A83E-CEA1EE16F9D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3219450" y="11496674"/>
+          <a:ext cx="1990726" cy="266701"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>スコア</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>342901</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="正方形/長方形 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FC17201-6985-4BEC-B854-48BE0DA84D1B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3152775" y="13554074"/>
+          <a:ext cx="1990726" cy="266701"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>タイトルに戻る</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2147,7 +4014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
@@ -2160,40 +4027,40 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="3" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="J3" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K3" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="L3" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
@@ -2201,114 +4068,126 @@
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E4" s="7">
         <v>5</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="7">
+        <v>3</v>
+      </c>
       <c r="G4" s="8" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="I4" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J4">
-        <f>SUM(E4:E100)</f>
-        <v>106</v>
+        <f>SUM(E4:E106)</f>
+        <v>128</v>
+      </c>
+      <c r="K4">
+        <f>SUMIFS(E4:E100,G4:G100,"未着手",G4:G100,"作業中")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="9"/>
       <c r="B5" s="10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
       <c r="G5" s="10" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="I5" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J5">
-        <f>SUMIFS(E4:E100,D4:D100,"プロト")</f>
-        <v>102</v>
+        <f>SUMIFS(E4:E106,D4:D106,"プロト")</f>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="9"/>
       <c r="B6" s="10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
       <c r="G6" s="10" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="I6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="J6">
-        <f>SUMIFS(E4:E100,D4:D100,"アルファ")</f>
-        <v>4</v>
+        <f>SUMIFS(E4:E106,D4:D106,"アルファ")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="9"/>
       <c r="B7" s="10" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>38</v>
+        <v>168</v>
       </c>
       <c r="I7" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="J7">
-        <f>SUMIFS(E4:E100,D4:D100,"ベータ")</f>
+        <f>SUMIFS(E4:E106,D4:D106,"ベータ")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="11"/>
       <c r="B8" s="13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E8" s="12">
         <v>2</v>
@@ -2317,13 +4196,13 @@
         <v>3</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="I8" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J8">
-        <f>SUMIFS(E4:E100,D4:D100,"マスター")</f>
+        <f>SUMIFS(E4:E106,D4:D106,"マスター")</f>
         <v>0</v>
       </c>
     </row>
@@ -2335,10 +4214,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E9" s="7">
         <v>1</v>
@@ -2347,7 +4226,7 @@
         <v>1.5</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
@@ -2356,10 +4235,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -2368,7 +4247,7 @@
         <v>1.5</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
@@ -2377,10 +4256,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -2389,19 +4268,19 @@
         <v>5</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="9"/>
       <c r="B12" s="10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -2410,97 +4289,108 @@
         <v>3</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="9"/>
       <c r="B13" s="10" t="s">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
       <c r="G13" s="10" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="9"/>
       <c r="B14" s="10" t="s">
-        <v>55</v>
+        <v>177</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="9"/>
       <c r="B15" s="10" t="s">
-        <v>56</v>
+        <v>178</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="9"/>
       <c r="B16" s="10" t="s">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
       <c r="G16" s="10" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17">
-        <v>3</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>38</v>
+      <c r="A17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2</v>
+      </c>
+      <c r="F17" s="7">
+        <v>2</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
@@ -2509,1147 +4399,1297 @@
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E18">
+        <v>5</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="11"/>
+      <c r="B19" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="12">
         <v>4</v>
       </c>
-      <c r="G18" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A19" s="9"/>
-      <c r="B19" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" t="s">
-        <v>72</v>
-      </c>
-      <c r="E19">
+      <c r="F19" s="12"/>
+      <c r="G19" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="7">
+        <v>4</v>
+      </c>
+      <c r="F20" s="7">
+        <v>4</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="9"/>
+      <c r="B21" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21">
         <v>2</v>
       </c>
-      <c r="G19" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="11"/>
-      <c r="B20" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" s="12">
+      <c r="F21">
         <v>2</v>
       </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A21" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="7">
+      <c r="G21" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="11"/>
+      <c r="B22" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="12">
+        <v>3</v>
+      </c>
+      <c r="F22" s="12">
         <v>2</v>
       </c>
-      <c r="F21" s="7">
+      <c r="G22" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="7">
+        <v>4</v>
+      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="9"/>
+      <c r="B24" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24">
         <v>2</v>
       </c>
-      <c r="G21" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A22" s="9"/>
-      <c r="B22" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22">
-        <v>5</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="11"/>
-      <c r="B23" s="13" t="s">
+      <c r="G24" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="11"/>
+      <c r="B25" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="12">
+        <v>3</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="7">
+        <v>4</v>
+      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="9"/>
+      <c r="B27" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="11"/>
+      <c r="B28" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" s="12">
+        <v>3</v>
+      </c>
+      <c r="F28" s="12"/>
+      <c r="G28" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="7">
+        <v>6</v>
+      </c>
+      <c r="F29" s="7"/>
+      <c r="G29" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="9"/>
+      <c r="B30" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="11"/>
+      <c r="B31" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="12">
+        <v>4</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="15">
         <v>15</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="12">
-        <v>4</v>
-      </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A24" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="7">
-        <v>4</v>
-      </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A25" s="9"/>
-      <c r="B25" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="11"/>
-      <c r="B26" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" s="12">
-        <v>3</v>
-      </c>
-      <c r="F26" s="12"/>
-      <c r="G26" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A27" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="7">
-        <v>6</v>
-      </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A28" s="9"/>
-      <c r="B28" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28">
-        <v>2</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="11"/>
-      <c r="B29" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="12">
-        <v>4</v>
-      </c>
-      <c r="F29" s="12"/>
-      <c r="G29" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="15">
-        <v>10</v>
-      </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A31" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="7">
-        <v>2</v>
-      </c>
-      <c r="F31" s="7"/>
-      <c r="G31" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="11"/>
-      <c r="B32" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E32" s="12">
-        <v>4</v>
-      </c>
-      <c r="F32" s="12"/>
-      <c r="G32" s="13" t="s">
-        <v>38</v>
+      <c r="F32" s="15"/>
+      <c r="G32" s="16" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>37</v>
+        <v>9</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E33" s="7">
         <v>2</v>
       </c>
       <c r="F33" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A34" s="9"/>
-      <c r="B34" t="s">
-        <v>50</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34">
-        <v>2</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>38</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="11"/>
+      <c r="B34" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" s="12">
+        <v>4</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="G34" s="13" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A35" s="9"/>
-      <c r="B35" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" t="s">
-        <v>36</v>
-      </c>
-      <c r="E35">
-        <v>2</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>38</v>
+      <c r="A35" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E35" s="7">
+        <v>3</v>
+      </c>
+      <c r="F35" s="7"/>
+      <c r="G35" s="8" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="9"/>
-      <c r="B36" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>37</v>
+      <c r="B36" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C36" t="s">
+        <v>186</v>
       </c>
       <c r="D36" t="s">
-        <v>36</v>
+        <v>187</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>38</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="9"/>
-      <c r="B37" t="s">
-        <v>4</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>37</v>
+      <c r="B37" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C37" t="s">
+        <v>186</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>187</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>38</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="11"/>
-      <c r="B38" s="12" t="s">
+      <c r="A38" s="9"/>
+      <c r="B38" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C38" t="s">
+        <v>186</v>
+      </c>
+      <c r="D38" t="s">
+        <v>187</v>
+      </c>
+      <c r="E38">
         <v>3</v>
       </c>
-      <c r="C38" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38" s="12">
+      <c r="G38" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="8"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="9"/>
+      <c r="B40" t="s">
+        <v>190</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D40" t="s">
+        <v>187</v>
+      </c>
+      <c r="G40" s="10"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" s="9"/>
+      <c r="B41" t="s">
+        <v>191</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D41" t="s">
+        <v>187</v>
+      </c>
+      <c r="G41" s="10"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42" s="9"/>
+      <c r="B42" t="s">
+        <v>192</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D42" t="s">
+        <v>187</v>
+      </c>
+      <c r="G42" s="10"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" s="9"/>
+      <c r="B43" t="s">
+        <v>199</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D43" t="s">
+        <v>187</v>
+      </c>
+      <c r="G43" s="10"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A44" s="9"/>
+      <c r="B44" t="s">
+        <v>200</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D44" t="s">
+        <v>187</v>
+      </c>
+      <c r="G44" s="10"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A45" s="9"/>
+      <c r="B45" t="s">
+        <v>201</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D45" t="s">
+        <v>187</v>
+      </c>
+      <c r="G45" s="10"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A46" s="9"/>
+      <c r="B46" t="s">
+        <v>202</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D46" t="s">
+        <v>187</v>
+      </c>
+      <c r="G46" s="10"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A47" s="9"/>
+      <c r="B47" t="s">
+        <v>203</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D47" t="s">
+        <v>187</v>
+      </c>
+      <c r="G47" s="10"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A48" s="9"/>
+      <c r="C48" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D48" t="s">
+        <v>187</v>
+      </c>
+      <c r="G48" s="10"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A49" s="9"/>
+      <c r="C49" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D49" t="s">
+        <v>187</v>
+      </c>
+      <c r="G49" s="10"/>
+    </row>
+    <row r="50" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="11"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="13"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A51" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" t="s">
+        <v>33</v>
+      </c>
+      <c r="E51">
         <v>2</v>
       </c>
-      <c r="F38" s="12"/>
-      <c r="G38" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A39" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="F51">
+        <v>2</v>
+      </c>
+      <c r="G51" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G39" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="11"/>
-      <c r="B40" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" s="12" t="s">
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A52" s="9"/>
+      <c r="B52" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52" t="s">
+        <v>33</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A41" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="11"/>
-      <c r="B42" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="C43" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43" t="s">
-        <v>36</v>
-      </c>
-      <c r="G43" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="C44" t="s">
-        <v>37</v>
-      </c>
-      <c r="D44" t="s">
-        <v>36</v>
-      </c>
-      <c r="G44" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="C45" t="s">
-        <v>37</v>
-      </c>
-      <c r="D45" t="s">
-        <v>36</v>
-      </c>
-      <c r="G45" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="C46" t="s">
-        <v>37</v>
-      </c>
-      <c r="D46" t="s">
-        <v>36</v>
-      </c>
-      <c r="G46" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="C47" t="s">
-        <v>37</v>
-      </c>
-      <c r="D47" t="s">
-        <v>36</v>
-      </c>
-      <c r="G47" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="C48" t="s">
-        <v>37</v>
-      </c>
-      <c r="D48" t="s">
-        <v>36</v>
-      </c>
-      <c r="G48" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="49" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C49" t="s">
-        <v>37</v>
-      </c>
-      <c r="D49" t="s">
-        <v>36</v>
-      </c>
-      <c r="G49" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="50" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C50" t="s">
-        <v>37</v>
-      </c>
-      <c r="D50" t="s">
-        <v>36</v>
-      </c>
-      <c r="G50" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="51" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C51" t="s">
-        <v>37</v>
-      </c>
-      <c r="D51" t="s">
-        <v>36</v>
-      </c>
-      <c r="G51" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="52" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C52" t="s">
-        <v>37</v>
-      </c>
-      <c r="D52" t="s">
-        <v>36</v>
-      </c>
-      <c r="G52" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="53" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C53" t="s">
-        <v>37</v>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A53" s="9"/>
+      <c r="B53" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D53" t="s">
-        <v>36</v>
-      </c>
-      <c r="G53" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C54" t="s">
-        <v>37</v>
+        <v>33</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A54" s="9"/>
+      <c r="B54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D54" t="s">
-        <v>36</v>
-      </c>
-      <c r="G54" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="55" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C55" t="s">
-        <v>37</v>
+        <v>33</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A55" s="9"/>
+      <c r="B55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D55" t="s">
-        <v>36</v>
-      </c>
-      <c r="G55" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="56" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C56" t="s">
-        <v>37</v>
-      </c>
-      <c r="D56" t="s">
-        <v>36</v>
-      </c>
-      <c r="G56" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="57" spans="3:7" x14ac:dyDescent="0.4">
+        <v>33</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="11"/>
+      <c r="B56" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E56" s="12">
+        <v>2</v>
+      </c>
+      <c r="F56" s="12"/>
+      <c r="G56" s="13" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A57" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>41</v>
+      </c>
       <c r="C57" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D57" t="s">
-        <v>36</v>
-      </c>
-      <c r="G57" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="58" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C58" t="s">
-        <v>37</v>
-      </c>
-      <c r="D58" t="s">
-        <v>36</v>
-      </c>
-      <c r="G58" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="59" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C59" t="s">
-        <v>37</v>
-      </c>
-      <c r="D59" t="s">
-        <v>36</v>
-      </c>
-      <c r="G59" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="60" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C60" t="s">
-        <v>37</v>
-      </c>
-      <c r="D60" t="s">
-        <v>36</v>
-      </c>
-      <c r="G60" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="61" spans="3:7" x14ac:dyDescent="0.4">
+        <v>66</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="11"/>
+      <c r="B58" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A59" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="11"/>
+      <c r="B60" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C61" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D61" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G61" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="62" spans="3:7" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C62" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D62" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G62" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="63" spans="3:7" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C63" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D63" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G63" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="64" spans="3:7" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C64" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D64" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G64" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C65" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D65" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G65" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C66" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D66" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G66" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C67" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D67" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G67" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C68" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D68" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G68" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C69" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D69" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G69" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C70" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D70" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G70" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C71" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D71" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G71" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C72" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D72" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G72" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C73" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D73" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G73" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C74" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D74" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G74" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C75" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D75" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G75" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C76" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D76" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G76" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C77" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D77" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G77" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C78" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D78" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G78" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="79" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C79" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D79" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G79" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C80" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D80" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G80" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="81" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C81" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D81" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G81" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C82" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D82" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G82" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C83" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D83" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G83" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C84" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D84" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G84" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="85" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C85" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D85" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G85" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C86" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D86" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G86" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C87" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D87" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G87" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="88" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C88" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D88" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G88" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C89" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D89" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G89" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C90" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D90" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G90" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="91" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C91" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D91" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G91" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="92" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C92" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D92" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G92" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C93" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D93" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G93" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="94" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C94" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D94" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G94" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C95" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D95" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G95" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C96" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D96" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G96" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="97" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C97" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D97" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G97" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="98" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C98" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D98" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G98" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="99" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C99" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D99" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G99" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C100" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D100" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G100" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C101" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D101" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G101" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="102" spans="3:7" x14ac:dyDescent="0.4">
       <c r="C102" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D102" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G102" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="103" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C103" t="s">
+        <v>34</v>
+      </c>
+      <c r="D103" t="s">
+        <v>33</v>
+      </c>
+      <c r="G103" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="104" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C104" t="s">
+        <v>34</v>
+      </c>
+      <c r="D104" t="s">
+        <v>33</v>
+      </c>
+      <c r="G104" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="105" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C105" t="s">
+        <v>34</v>
+      </c>
+      <c r="D105" t="s">
+        <v>33</v>
+      </c>
+      <c r="G105" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="106" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C106" t="s">
+        <v>34</v>
+      </c>
+      <c r="D106" t="s">
+        <v>33</v>
+      </c>
+      <c r="G106" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="107" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C107" t="s">
+        <v>34</v>
+      </c>
+      <c r="D107" t="s">
+        <v>33</v>
+      </c>
+      <c r="G107" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="108" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C108" t="s">
+        <v>34</v>
+      </c>
+      <c r="D108" t="s">
+        <v>33</v>
+      </c>
+      <c r="G108" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G102" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}"/>
+  <autoFilter ref="A3:G108" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}"/>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G102" xr:uid="{05F1DF74-5C3A-4656-9180-8CB2E572755F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G34 G51:G108" xr:uid="{05F1DF74-5C3A-4656-9180-8CB2E572755F}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C102" xr:uid="{02D66180-7540-49E9-8878-4AAA7C63EEA4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C34 C51:C108" xr:uid="{02D66180-7540-49E9-8878-4AAA7C63EEA4}">
       <formula1>"C,B,A,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D102" xr:uid="{485BBF23-C878-4534-89D7-53615FBE9943}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D34 D51:D108" xr:uid="{485BBF23-C878-4534-89D7-53615FBE9943}">
       <formula1>"プロト,アルファ,ベータ,マスター"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3659,62 +5699,62 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB8A7F07-4822-4AA8-B3C3-66F7A08D4E6E}">
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:S36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:19" x14ac:dyDescent="0.4">
       <c r="D2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="G2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="D3" s="17"/>
       <c r="E3" s="18"/>
       <c r="F3" s="19"/>
       <c r="G3" s="20"/>
       <c r="H3" s="21"/>
     </row>
-    <row r="4" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="14" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="14" t="s">
-        <v>66</v>
-      </c>
       <c r="C5" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B6" s="9"/>
       <c r="G6">
         <v>1</v>
@@ -3723,7 +5763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B7" s="9">
         <v>3</v>
       </c>
@@ -3746,7 +5786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B8" s="9">
         <v>10</v>
       </c>
@@ -3769,7 +5809,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B9" s="9">
         <v>17</v>
       </c>
@@ -3792,7 +5832,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B10" s="9">
         <v>24</v>
       </c>
@@ -3815,7 +5855,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="11">
         <v>31</v>
       </c>
@@ -3826,35 +5866,59 @@
       <c r="G11" s="12"/>
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B12" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B13" s="6" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B14" s="31"/>
       <c r="C14" s="43">
         <v>1</v>
@@ -3874,8 +5938,31 @@
       <c r="H14" s="44">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="J14" s="31"/>
+      <c r="K14" s="54">
+        <v>1</v>
+      </c>
+      <c r="L14" s="54">
+        <v>2</v>
+      </c>
+      <c r="M14" s="54">
+        <v>3</v>
+      </c>
+      <c r="N14" s="54">
+        <v>4</v>
+      </c>
+      <c r="O14" s="54">
+        <v>5</v>
+      </c>
+      <c r="P14" s="55">
+        <v>6</v>
+      </c>
+      <c r="R14" s="21"/>
+      <c r="S14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B15" s="45">
         <v>7</v>
       </c>
@@ -3897,8 +5984,33 @@
       <c r="H15" s="51">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="J15" s="56">
+        <v>7</v>
+      </c>
+      <c r="K15" s="57">
+        <v>8</v>
+      </c>
+      <c r="L15" s="57">
+        <v>9</v>
+      </c>
+      <c r="M15" s="58">
+        <v>10</v>
+      </c>
+      <c r="N15" s="58">
+        <v>11</v>
+      </c>
+      <c r="O15" s="58">
+        <v>12</v>
+      </c>
+      <c r="P15" s="59">
+        <v>13</v>
+      </c>
+      <c r="R15" s="70"/>
+      <c r="S15" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.4">
       <c r="B16" s="45">
         <v>14</v>
       </c>
@@ -3920,8 +6032,33 @@
       <c r="H16" s="51">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="J16" s="60">
+        <v>14</v>
+      </c>
+      <c r="K16" s="58">
+        <v>15</v>
+      </c>
+      <c r="L16" s="58">
+        <v>16</v>
+      </c>
+      <c r="M16" s="58">
+        <v>17</v>
+      </c>
+      <c r="N16" s="61">
+        <v>18</v>
+      </c>
+      <c r="O16" s="61">
+        <v>19</v>
+      </c>
+      <c r="P16" s="63">
+        <v>20</v>
+      </c>
+      <c r="R16" s="17"/>
+      <c r="S16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B17" s="45">
         <v>21</v>
       </c>
@@ -3943,8 +6080,29 @@
       <c r="H17" s="51">
         <v>27</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="J17" s="62">
+        <v>21</v>
+      </c>
+      <c r="K17" s="61">
+        <v>22</v>
+      </c>
+      <c r="L17" s="61">
+        <v>23</v>
+      </c>
+      <c r="M17" s="61">
+        <v>24</v>
+      </c>
+      <c r="N17" s="61">
+        <v>25</v>
+      </c>
+      <c r="O17" s="61">
+        <v>26</v>
+      </c>
+      <c r="P17" s="63">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B18" s="52">
         <v>28</v>
       </c>
@@ -3958,36 +6116,73 @@
       <c r="F18" s="41"/>
       <c r="G18" s="41"/>
       <c r="H18" s="42"/>
-    </row>
-    <row r="19" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="J18" s="64">
+        <v>28</v>
+      </c>
+      <c r="K18" s="65">
+        <v>29</v>
+      </c>
+      <c r="L18" s="65">
+        <v>30</v>
+      </c>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="41"/>
+      <c r="P18" s="42"/>
+    </row>
+    <row r="19" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B19" s="22" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>61</v>
+      </c>
+      <c r="J19" s="22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B20" s="6" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B21" s="31"/>
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
@@ -4003,8 +6198,23 @@
       <c r="H21" s="44">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="J21" s="31"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="43">
+        <v>1</v>
+      </c>
+      <c r="N21" s="43">
+        <v>2</v>
+      </c>
+      <c r="O21" s="43">
+        <v>3</v>
+      </c>
+      <c r="P21" s="44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B22" s="45">
         <v>5</v>
       </c>
@@ -4026,8 +6236,29 @@
       <c r="H22" s="46">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="J22" s="45">
+        <v>5</v>
+      </c>
+      <c r="K22" s="23">
+        <v>6</v>
+      </c>
+      <c r="L22" s="23">
+        <v>7</v>
+      </c>
+      <c r="M22" s="23">
+        <v>8</v>
+      </c>
+      <c r="N22" s="23">
+        <v>9</v>
+      </c>
+      <c r="O22" s="23">
+        <v>10</v>
+      </c>
+      <c r="P22" s="51">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B23" s="47">
         <v>12</v>
       </c>
@@ -4049,8 +6280,29 @@
       <c r="H23" s="46">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="J23" s="45">
+        <v>12</v>
+      </c>
+      <c r="K23" s="23">
+        <v>13</v>
+      </c>
+      <c r="L23" s="23">
+        <v>14</v>
+      </c>
+      <c r="M23" s="23">
+        <v>15</v>
+      </c>
+      <c r="N23" s="57">
+        <v>16</v>
+      </c>
+      <c r="O23" s="57">
+        <v>17</v>
+      </c>
+      <c r="P23" s="66">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B24" s="47">
         <v>19</v>
       </c>
@@ -4072,8 +6324,29 @@
       <c r="H24" s="46">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="J24" s="56">
+        <v>19</v>
+      </c>
+      <c r="K24" s="57">
+        <v>20</v>
+      </c>
+      <c r="L24" s="57">
+        <v>21</v>
+      </c>
+      <c r="M24" s="57">
+        <v>22</v>
+      </c>
+      <c r="N24" s="57">
+        <v>23</v>
+      </c>
+      <c r="O24" s="57">
+        <v>24</v>
+      </c>
+      <c r="P24" s="66">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B25" s="48">
         <v>26</v>
       </c>
@@ -4093,36 +6366,55 @@
         <v>31</v>
       </c>
       <c r="H25" s="42"/>
-    </row>
-    <row r="26" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="J25" s="67">
+        <v>26</v>
+      </c>
+      <c r="K25" s="68">
+        <v>27</v>
+      </c>
+      <c r="L25" s="68">
+        <v>28</v>
+      </c>
+      <c r="M25" s="68">
+        <v>29</v>
+      </c>
+      <c r="N25" s="68">
+        <v>30</v>
+      </c>
+      <c r="O25" s="68">
+        <v>31</v>
+      </c>
+      <c r="P25" s="69"/>
+    </row>
+    <row r="26" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B26" s="24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B27" s="6" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B28" s="31"/>
       <c r="C28" s="32"/>
       <c r="D28" s="32"/>
@@ -4133,7 +6425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B29" s="34">
         <v>2</v>
       </c>
@@ -4156,7 +6448,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B30" s="34">
         <v>9</v>
       </c>
@@ -4179,7 +6471,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B31" s="34">
         <v>16</v>
       </c>
@@ -4202,7 +6494,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B32" s="37">
         <v>23</v>
       </c>
@@ -4240,30 +6532,30 @@
     </row>
     <row r="34" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B34" s="24" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B35" s="6" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4298,53 +6590,53 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -4368,27 +6660,27 @@
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
+        <v>154</v>
+      </c>
+      <c r="I3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J3" t="s">
         <v>163</v>
       </c>
-      <c r="I3" t="s">
-        <v>121</v>
-      </c>
-      <c r="J3" t="s">
-        <v>172</v>
-      </c>
       <c r="K3" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="L3" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="M3" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.4">
@@ -4401,43 +6693,43 @@
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.4">
       <c r="I5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D7" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="I7" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="N7" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="P7" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="D8" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="K9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M9" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.4">
@@ -4447,7 +6739,7 @@
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H11" t="s">
         <v>1</v>
@@ -4458,23 +6750,23 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="H13" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="J13" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B14" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -4494,17 +6786,17 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
@@ -4514,116 +6806,116 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B10" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E16" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="N16" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E17" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="N17" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C20" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B21" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -4633,8 +6925,332 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC62AB97-61B1-41EB-8933-806BF4A80E1C}">
+  <dimension ref="B1:L59"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B2" s="6"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="8"/>
+      <c r="L2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B3" s="9"/>
+      <c r="K3" s="10"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B4" s="9"/>
+      <c r="G4" t="s">
+        <v>194</v>
+      </c>
+      <c r="K4" s="10"/>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B5" s="9"/>
+      <c r="C5" t="s">
+        <v>195</v>
+      </c>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B6" s="9"/>
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B7" s="9"/>
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B8" s="9"/>
+      <c r="K8" s="10"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B9" s="9"/>
+      <c r="I9" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B10" s="9"/>
+      <c r="K10" s="10"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B11" s="9"/>
+      <c r="K11" s="10"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B12" s="9"/>
+      <c r="K12" s="10"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B13" s="9"/>
+      <c r="K13" s="10"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B14" s="9"/>
+      <c r="K14" s="10"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B15" s="9"/>
+      <c r="K15" s="10"/>
+    </row>
+    <row r="16" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="13"/>
+    </row>
+    <row r="17" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B18" s="6"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="8"/>
+      <c r="L18" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B19" s="9"/>
+      <c r="K19" s="10"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B20" s="9"/>
+      <c r="K20" s="10"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B21" s="9"/>
+      <c r="K21" s="10"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B22" s="9"/>
+      <c r="K22" s="10"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B23" s="9"/>
+      <c r="K23" s="10"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B24" s="9"/>
+      <c r="K24" s="10"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B25" s="9"/>
+      <c r="K25" s="10"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B26" s="9"/>
+      <c r="K26" s="10"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B27" s="9"/>
+      <c r="K27" s="10"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B28" s="9"/>
+      <c r="K28" s="10"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B29" s="9"/>
+      <c r="K29" s="10"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B30" s="9"/>
+      <c r="K30" s="10"/>
+    </row>
+    <row r="31" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="11"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="13"/>
+    </row>
+    <row r="32" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B33" s="6"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="8"/>
+      <c r="L33" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B34" s="9"/>
+      <c r="K34" s="10"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B35" s="9"/>
+      <c r="K35" s="10"/>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B36" s="9"/>
+      <c r="K36" s="10"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B37" s="9"/>
+      <c r="K37" s="10"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B38" s="9"/>
+      <c r="K38" s="10"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B39" s="9"/>
+      <c r="K39" s="10"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B40" s="9"/>
+      <c r="K40" s="10"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B41" s="9"/>
+      <c r="K41" s="10"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B42" s="9"/>
+      <c r="K42" s="10"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B43" s="9"/>
+      <c r="K43" s="10"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B44" s="9"/>
+      <c r="K44" s="10"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B45" s="9"/>
+      <c r="K45" s="10"/>
+    </row>
+    <row r="46" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B46" s="11"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="13"/>
+    </row>
+    <row r="47" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="B48" s="6"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="8"/>
+      <c r="L48" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B49" s="9"/>
+      <c r="K49" s="10"/>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B50" s="9"/>
+      <c r="K50" s="10"/>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B51" s="9"/>
+      <c r="K51" s="10"/>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B52" s="9"/>
+      <c r="K52" s="10"/>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B53" s="9"/>
+      <c r="K53" s="10"/>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B54" s="9"/>
+      <c r="K54" s="10"/>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B55" s="9"/>
+      <c r="K55" s="10"/>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B56" s="9"/>
+      <c r="K56" s="10"/>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B57" s="9"/>
+      <c r="K57" s="10"/>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B58" s="9"/>
+      <c r="K58" s="10"/>
+    </row>
+    <row r="59" spans="2:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B59" s="11"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="12"/>
+      <c r="K59" s="13"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CADF38F-73BE-4B6B-BA66-331B33FA1371}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -4645,7 +7261,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -4660,113 +7276,113 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" t="s">
         <v>99</v>
       </c>
-      <c r="B9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" t="s">
-        <v>108</v>
-      </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C21" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
@@ -4774,7 +7390,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
@@ -4782,133 +7398,180 @@
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C24" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C26" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C27" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C28" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C31" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C32" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C33" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C34" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C35" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C36" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C38" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C39" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C40" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C42" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C43" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C44" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C45" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C46" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B52" t="s">
+        <v>171</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B53" t="s">
+        <v>91</v>
+      </c>
+      <c r="C53" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B54" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A51" t="s">
+      <c r="C54" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B55" t="s">
         <v>170</v>
+      </c>
+      <c r="C55" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B56" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C57" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C58" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BA4B99-4859-44A0-BAE3-68A24317F737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB44681A-1307-4F6A-899F-796BD070EFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="211">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1365,6 +1365,41 @@
     <rPh sb="0" eb="3">
       <t>ザコテキ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの攻撃</t>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>突進</t>
+    <rPh sb="0" eb="2">
+      <t>トッシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>斬撃飛ばし</t>
+    <rPh sb="0" eb="2">
+      <t>ザンゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2段コンボ</t>
+    <rPh sb="1" eb="2">
+      <t>ダン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブン→ザカザカ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1802,7 +1837,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1965,16 +2000,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -2001,19 +2033,16 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4514,9 +4543,11 @@
       <c r="E23" s="7">
         <v>4</v>
       </c>
-      <c r="F23" s="7"/>
+      <c r="F23" s="7">
+        <v>4</v>
+      </c>
       <c r="G23" s="8" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
@@ -4533,8 +4564,11 @@
       <c r="E24">
         <v>2</v>
       </c>
+      <c r="F24" s="68">
+        <v>2</v>
+      </c>
       <c r="G24" s="10" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4551,9 +4585,11 @@
       <c r="E25" s="12">
         <v>3</v>
       </c>
-      <c r="F25" s="12"/>
+      <c r="F25" s="12">
+        <v>2</v>
+      </c>
       <c r="G25" s="13" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
@@ -5939,22 +5975,22 @@
         <v>6</v>
       </c>
       <c r="J14" s="31"/>
-      <c r="K14" s="54">
+      <c r="K14" s="32">
         <v>1</v>
       </c>
-      <c r="L14" s="54">
+      <c r="L14" s="32">
         <v>2</v>
       </c>
-      <c r="M14" s="54">
+      <c r="M14" s="32">
         <v>3</v>
       </c>
-      <c r="N14" s="54">
+      <c r="N14" s="32">
         <v>4</v>
       </c>
-      <c r="O14" s="54">
+      <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="P14" s="55">
+      <c r="P14" s="54">
         <v>6</v>
       </c>
       <c r="R14" s="21"/>
@@ -5984,28 +6020,28 @@
       <c r="H15" s="51">
         <v>13</v>
       </c>
-      <c r="J15" s="56">
+      <c r="J15" s="55">
         <v>7</v>
       </c>
-      <c r="K15" s="57">
+      <c r="K15" s="56">
         <v>8</v>
       </c>
-      <c r="L15" s="57">
+      <c r="L15" s="56">
         <v>9</v>
       </c>
-      <c r="M15" s="58">
+      <c r="M15" s="57">
         <v>10</v>
       </c>
-      <c r="N15" s="58">
+      <c r="N15" s="57">
         <v>11</v>
       </c>
-      <c r="O15" s="58">
+      <c r="O15" s="57">
         <v>12</v>
       </c>
-      <c r="P15" s="59">
+      <c r="P15" s="58">
         <v>13</v>
       </c>
-      <c r="R15" s="70"/>
+      <c r="R15" s="67"/>
       <c r="S15" t="s">
         <v>205</v>
       </c>
@@ -6032,25 +6068,25 @@
       <c r="H16" s="51">
         <v>20</v>
       </c>
-      <c r="J16" s="60">
+      <c r="J16" s="59">
         <v>14</v>
       </c>
-      <c r="K16" s="58">
+      <c r="K16" s="57">
         <v>15</v>
       </c>
-      <c r="L16" s="58">
+      <c r="L16" s="57">
         <v>16</v>
       </c>
-      <c r="M16" s="58">
+      <c r="M16" s="57">
         <v>17</v>
       </c>
-      <c r="N16" s="61">
+      <c r="N16" s="60">
         <v>18</v>
       </c>
-      <c r="O16" s="61">
+      <c r="O16" s="60">
         <v>19</v>
       </c>
-      <c r="P16" s="63">
+      <c r="P16" s="62">
         <v>20</v>
       </c>
       <c r="R16" s="17"/>
@@ -6080,25 +6116,25 @@
       <c r="H17" s="51">
         <v>27</v>
       </c>
-      <c r="J17" s="62">
+      <c r="J17" s="61">
         <v>21</v>
       </c>
-      <c r="K17" s="61">
+      <c r="K17" s="60">
         <v>22</v>
       </c>
-      <c r="L17" s="61">
+      <c r="L17" s="60">
         <v>23</v>
       </c>
-      <c r="M17" s="61">
+      <c r="M17" s="60">
         <v>24</v>
       </c>
-      <c r="N17" s="61">
+      <c r="N17" s="60">
         <v>25</v>
       </c>
-      <c r="O17" s="61">
+      <c r="O17" s="60">
         <v>26</v>
       </c>
-      <c r="P17" s="63">
+      <c r="P17" s="62">
         <v>27</v>
       </c>
     </row>
@@ -6116,13 +6152,13 @@
       <c r="F18" s="41"/>
       <c r="G18" s="41"/>
       <c r="H18" s="42"/>
-      <c r="J18" s="64">
+      <c r="J18" s="63">
         <v>28</v>
       </c>
-      <c r="K18" s="65">
+      <c r="K18" s="64">
         <v>29</v>
       </c>
-      <c r="L18" s="65">
+      <c r="L18" s="64">
         <v>30</v>
       </c>
       <c r="M18" s="41"/>
@@ -6292,13 +6328,13 @@
       <c r="M23" s="23">
         <v>15</v>
       </c>
-      <c r="N23" s="57">
+      <c r="N23" s="56">
         <v>16</v>
       </c>
-      <c r="O23" s="57">
+      <c r="O23" s="56">
         <v>17</v>
       </c>
-      <c r="P23" s="66">
+      <c r="P23" s="65">
         <v>18</v>
       </c>
     </row>
@@ -6324,25 +6360,25 @@
       <c r="H24" s="46">
         <v>25</v>
       </c>
-      <c r="J24" s="56">
+      <c r="J24" s="55">
         <v>19</v>
       </c>
-      <c r="K24" s="57">
+      <c r="K24" s="56">
         <v>20</v>
       </c>
-      <c r="L24" s="57">
+      <c r="L24" s="56">
         <v>21</v>
       </c>
-      <c r="M24" s="57">
+      <c r="M24" s="56">
         <v>22</v>
       </c>
-      <c r="N24" s="57">
+      <c r="N24" s="56">
         <v>23</v>
       </c>
-      <c r="O24" s="57">
+      <c r="O24" s="56">
         <v>24</v>
       </c>
-      <c r="P24" s="66">
+      <c r="P24" s="65">
         <v>25</v>
       </c>
     </row>
@@ -6366,25 +6402,25 @@
         <v>31</v>
       </c>
       <c r="H25" s="42"/>
-      <c r="J25" s="67">
+      <c r="J25" s="66">
         <v>26</v>
       </c>
-      <c r="K25" s="68">
+      <c r="K25" s="41">
         <v>27</v>
       </c>
-      <c r="L25" s="68">
+      <c r="L25" s="41">
         <v>28</v>
       </c>
-      <c r="M25" s="68">
+      <c r="M25" s="41">
         <v>29</v>
       </c>
-      <c r="N25" s="68">
+      <c r="N25" s="41">
         <v>30</v>
       </c>
-      <c r="O25" s="68">
+      <c r="O25" s="41">
         <v>31</v>
       </c>
-      <c r="P25" s="69"/>
+      <c r="P25" s="42"/>
     </row>
     <row r="26" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B26" s="24" t="s">
@@ -7250,7 +7286,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CADF38F-73BE-4B6B-BA66-331B33FA1371}">
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -7574,6 +7610,31 @@
         <v>175</v>
       </c>
     </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B60" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B61" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B62" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B63" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B64" t="s">
+        <v>210</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB44681A-1307-4F6A-899F-796BD070EFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06D30C3-3338-4BEA-A411-87F3C2F6FA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="memo" sheetId="5" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$G$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$G$109</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="213">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1400,6 +1400,17 @@
   </si>
   <si>
     <t>ブン→ザカザカ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵スポーン</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未着手</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1837,7 +1848,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2040,6 +2051,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
@@ -4043,7 +4057,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}">
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
@@ -4118,12 +4132,16 @@
         <v>77</v>
       </c>
       <c r="J4">
-        <f>SUM(E4:E106)</f>
-        <v>128</v>
+        <f>SUM(E4:E107)</f>
+        <v>162</v>
       </c>
       <c r="K4">
-        <f>SUMIFS(E4:E100,G4:G100,"未着手",G4:G100,"作業中")</f>
-        <v>0</v>
+        <f>SUMIFS(E4:E101,G4:G101,"未着手") +SUMIFS(E4:E101,G4:G101,"作業中")</f>
+        <v>83</v>
+      </c>
+      <c r="L4">
+        <f xml:space="preserve"> K4 / J4</f>
+        <v>0.51234567901234573</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -4150,8 +4168,8 @@
         <v>78</v>
       </c>
       <c r="J5">
-        <f>SUMIFS(E4:E106,D4:D106,"プロト")</f>
-        <v>128</v>
+        <f>SUMIFS(E4:E107,D4:D107,"プロト")</f>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
@@ -4178,7 +4196,7 @@
         <v>79</v>
       </c>
       <c r="J6">
-        <f>SUMIFS(E4:E106,D4:D106,"アルファ")</f>
+        <f>SUMIFS(E4:E107,D4:D107,"アルファ")</f>
         <v>0</v>
       </c>
     </row>
@@ -4203,7 +4221,7 @@
         <v>80</v>
       </c>
       <c r="J7">
-        <f>SUMIFS(E4:E106,D4:D106,"ベータ")</f>
+        <f>SUMIFS(E4:E107,D4:D107,"ベータ")</f>
         <v>0</v>
       </c>
     </row>
@@ -4231,7 +4249,7 @@
         <v>81</v>
       </c>
       <c r="J8">
-        <f>SUMIFS(E4:E106,D4:D106,"マスター")</f>
+        <f>SUMIFS(E4:E107,D4:D107,"マスター")</f>
         <v>0</v>
       </c>
     </row>
@@ -4375,7 +4393,7 @@
         <v>3</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4457,9 +4475,11 @@
       <c r="E19" s="12">
         <v>4</v>
       </c>
-      <c r="F19" s="12"/>
+      <c r="F19" s="12">
+        <v>4</v>
+      </c>
       <c r="G19" s="13" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
@@ -4564,7 +4584,7 @@
       <c r="E24">
         <v>2</v>
       </c>
-      <c r="F24" s="68">
+      <c r="F24">
         <v>2</v>
       </c>
       <c r="G24" s="10" t="s">
@@ -4668,7 +4688,7 @@
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="8" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
@@ -4686,7 +4706,7 @@
         <v>2</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4705,7 +4725,7 @@
       </c>
       <c r="F31" s="12"/>
       <c r="G31" s="13" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4771,49 +4791,50 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A35" s="6" t="s">
+    <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="9"/>
+      <c r="B35" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C35" s="69" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="69" t="s">
+        <v>33</v>
+      </c>
+      <c r="E35" s="69">
+        <v>6</v>
+      </c>
+      <c r="F35" s="68"/>
+      <c r="G35" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B36" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C36" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D36" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E36" s="7">
         <v>3</v>
       </c>
-      <c r="F35" s="7"/>
-      <c r="G35" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A36" s="9"/>
-      <c r="B36" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="C36" t="s">
-        <v>186</v>
-      </c>
-      <c r="D36" t="s">
-        <v>187</v>
-      </c>
-      <c r="E36">
-        <v>2</v>
-      </c>
-      <c r="G36" s="10" t="s">
+      <c r="F36" s="7"/>
+      <c r="G36" s="8" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="9"/>
       <c r="B37" s="10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C37" t="s">
         <v>186</v>
@@ -4828,10 +4849,10 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="9"/>
       <c r="B38" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C38" t="s">
         <v>186</v>
@@ -4840,46 +4861,55 @@
         <v>187</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A39" s="6" t="s">
+    <row r="39" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="9"/>
+      <c r="B39" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C39" t="s">
+        <v>186</v>
+      </c>
+      <c r="D39" t="s">
+        <v>187</v>
+      </c>
+      <c r="E39">
+        <v>3</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B40" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D40" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="8"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A40" s="9"/>
-      <c r="B40" t="s">
-        <v>190</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="D40" t="s">
-        <v>187</v>
-      </c>
-      <c r="G40" s="10"/>
+      <c r="E40" s="7">
+        <v>3</v>
+      </c>
+      <c r="F40" s="7"/>
+      <c r="G40" s="10" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="9"/>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>186</v>
@@ -4887,12 +4917,17 @@
       <c r="D41" t="s">
         <v>187</v>
       </c>
-      <c r="G41" s="10"/>
+      <c r="E41" s="69">
+        <v>3</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="9"/>
       <c r="B42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>186</v>
@@ -4900,12 +4935,17 @@
       <c r="D42" t="s">
         <v>187</v>
       </c>
-      <c r="G42" s="10"/>
+      <c r="E42" s="69">
+        <v>4</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" s="9"/>
       <c r="B43" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>186</v>
@@ -4913,12 +4953,17 @@
       <c r="D43" t="s">
         <v>187</v>
       </c>
-      <c r="G43" s="10"/>
+      <c r="E43" s="69">
+        <v>4</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" s="9"/>
       <c r="B44" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>186</v>
@@ -4926,12 +4971,17 @@
       <c r="D44" t="s">
         <v>187</v>
       </c>
-      <c r="G44" s="10"/>
+      <c r="E44" s="69">
+        <v>2</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45" s="9"/>
       <c r="B45" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>186</v>
@@ -4939,12 +4989,17 @@
       <c r="D45" t="s">
         <v>187</v>
       </c>
-      <c r="G45" s="10"/>
+      <c r="E45" s="69">
+        <v>3</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46" s="9"/>
       <c r="B46" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>186</v>
@@ -4952,12 +5007,17 @@
       <c r="D46" t="s">
         <v>187</v>
       </c>
-      <c r="G46" s="10"/>
+      <c r="E46" s="69">
+        <v>3</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" s="9"/>
       <c r="B47" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>186</v>
@@ -4965,17 +5025,30 @@
       <c r="D47" t="s">
         <v>187</v>
       </c>
-      <c r="G47" s="10"/>
+      <c r="E47" s="69">
+        <v>3</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" s="9"/>
+      <c r="B48" t="s">
+        <v>203</v>
+      </c>
       <c r="C48" s="9" t="s">
         <v>186</v>
       </c>
       <c r="D48" t="s">
         <v>187</v>
       </c>
-      <c r="G48" s="10"/>
+      <c r="E48" s="69">
+        <v>3</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" s="9"/>
@@ -4987,46 +5060,35 @@
       </c>
       <c r="G49" s="10"/>
     </row>
-    <row r="50" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="11"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="11" t="s">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A50" s="9"/>
+      <c r="C50" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" t="s">
         <v>187</v>
       </c>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="13"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A51" s="9" t="s">
+      <c r="G50" s="10"/>
+    </row>
+    <row r="51" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="11"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="13"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A52" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B52" t="s">
         <v>1</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D51" t="s">
-        <v>33</v>
-      </c>
-      <c r="E51">
-        <v>2</v>
-      </c>
-      <c r="F51">
-        <v>2</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A52" s="9"/>
-      <c r="B52" t="s">
-        <v>47</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>34</v>
@@ -5047,7 +5109,7 @@
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" s="9"/>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>34</v>
@@ -5058,14 +5120,17 @@
       <c r="E53">
         <v>2</v>
       </c>
+      <c r="F53">
+        <v>2</v>
+      </c>
       <c r="G53" s="10" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54" s="9"/>
       <c r="B54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>34</v>
@@ -5083,7 +5148,7 @@
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" s="9"/>
       <c r="B55" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>34</v>
@@ -5098,103 +5163,110 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="11"/>
-      <c r="B56" s="12" t="s">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A56" s="9"/>
+      <c r="B56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D56" t="s">
+        <v>33</v>
+      </c>
+      <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="11"/>
+      <c r="B57" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C56" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E56" s="12">
+      <c r="C57" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E57" s="12">
         <v>2</v>
       </c>
-      <c r="F56" s="12"/>
-      <c r="G56" s="13" t="s">
+      <c r="F57" s="12"/>
+      <c r="G57" s="13" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A57" s="9" t="s">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A58" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B58" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C57" t="s">
-        <v>34</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="C58" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" t="s">
         <v>66</v>
       </c>
-      <c r="G57" s="10" t="s">
+      <c r="G58" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="11"/>
-      <c r="B58" s="13" t="s">
+    <row r="59" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="11"/>
+      <c r="B59" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C58" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D58" s="12" t="s">
+      <c r="C59" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="13" t="s">
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A59" s="6" t="s">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A60" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B60" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C59" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D59" s="7" t="s">
+      <c r="C60" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="8" t="s">
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="11"/>
-      <c r="B60" s="13" t="s">
+    <row r="61" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="11"/>
+      <c r="B61" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C60" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D60" s="12" t="s">
+      <c r="C61" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D61" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="C61" t="s">
-        <v>34</v>
-      </c>
-      <c r="D61" t="s">
-        <v>33</v>
-      </c>
-      <c r="G61" t="s">
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5715,17 +5787,28 @@
         <v>35</v>
       </c>
     </row>
+    <row r="109" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C109" t="s">
+        <v>34</v>
+      </c>
+      <c r="D109" t="s">
+        <v>33</v>
+      </c>
+      <c r="G109" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:G108" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}"/>
+  <autoFilter ref="A3:G109" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}"/>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G34 G51:G108" xr:uid="{05F1DF74-5C3A-4656-9180-8CB2E572755F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G35 G52:G109 G40:G48" xr:uid="{05F1DF74-5C3A-4656-9180-8CB2E572755F}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C34 C51:C108" xr:uid="{02D66180-7540-49E9-8878-4AAA7C63EEA4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C35 C52:C109" xr:uid="{02D66180-7540-49E9-8878-4AAA7C63EEA4}">
       <formula1>"C,B,A,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D34 D51:D108" xr:uid="{485BBF23-C878-4534-89D7-53615FBE9943}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D35 D52:D109" xr:uid="{485BBF23-C878-4534-89D7-53615FBE9943}">
       <formula1>"プロト,アルファ,ベータ,マスター"</formula1>
     </dataValidation>
   </dataValidations>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\SummerGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06D30C3-3338-4BEA-A411-87F3C2F6FA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5DBC11-2EF7-4B58-BFB9-9D4E7036694E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="212">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1190,10 +1190,6 @@
   </si>
   <si>
     <t>オーク</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>オークロード</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1848,7 +1844,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2051,12 +2047,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4342,7 +4332,7 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="9"/>
       <c r="B13" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C13" t="s">
         <v>34</v>
@@ -4363,7 +4353,7 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="9"/>
       <c r="B14" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C14" t="s">
         <v>34</v>
@@ -4381,7 +4371,7 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="9"/>
       <c r="B15" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C15" t="s">
         <v>34</v>
@@ -4399,7 +4389,7 @@
     <row r="16" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="9"/>
       <c r="B16" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C16" t="s">
         <v>34</v>
@@ -4794,130 +4784,129 @@
     <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="9"/>
       <c r="B35" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="C35" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="D35" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="E35" s="69">
+        <v>210</v>
+      </c>
+      <c r="C35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" t="s">
+        <v>33</v>
+      </c>
+      <c r="E35">
         <v>6</v>
       </c>
-      <c r="F35" s="68"/>
       <c r="G35" s="10" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C36" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>186</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>187</v>
       </c>
       <c r="E36" s="7">
         <v>3</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="9"/>
       <c r="B37" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C37" t="s">
+        <v>185</v>
+      </c>
+      <c r="D37" t="s">
         <v>186</v>
-      </c>
-      <c r="D37" t="s">
-        <v>187</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="9"/>
       <c r="B38" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C38" t="s">
+        <v>185</v>
+      </c>
+      <c r="D38" t="s">
         <v>186</v>
-      </c>
-      <c r="D38" t="s">
-        <v>187</v>
       </c>
       <c r="E38">
         <v>2</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A39" s="9"/>
       <c r="B39" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C39" t="s">
         <v>185</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>186</v>
-      </c>
-      <c r="D39" t="s">
-        <v>187</v>
       </c>
       <c r="E39">
         <v>3</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B40" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>189</v>
-      </c>
       <c r="C40" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>186</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>187</v>
       </c>
       <c r="E40" s="7">
         <v>3</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="9"/>
       <c r="B41" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C41" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D41" t="s">
         <v>186</v>
       </c>
-      <c r="D41" t="s">
-        <v>187</v>
-      </c>
-      <c r="E41" s="69">
+      <c r="E41">
         <v>3</v>
       </c>
       <c r="G41" s="10" t="s">
@@ -4927,15 +4916,15 @@
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="9"/>
       <c r="B42" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C42" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D42" t="s">
         <v>186</v>
       </c>
-      <c r="D42" t="s">
-        <v>187</v>
-      </c>
-      <c r="E42" s="69">
+      <c r="E42">
         <v>4</v>
       </c>
       <c r="G42" s="10" t="s">
@@ -4945,15 +4934,15 @@
     <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" s="9"/>
       <c r="B43" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C43" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D43" t="s">
         <v>186</v>
       </c>
-      <c r="D43" t="s">
-        <v>187</v>
-      </c>
-      <c r="E43" s="69">
+      <c r="E43">
         <v>4</v>
       </c>
       <c r="G43" s="10" t="s">
@@ -4963,15 +4952,15 @@
     <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" s="9"/>
       <c r="B44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C44" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D44" t="s">
         <v>186</v>
       </c>
-      <c r="D44" t="s">
-        <v>187</v>
-      </c>
-      <c r="E44" s="69">
+      <c r="E44">
         <v>2</v>
       </c>
       <c r="G44" s="10" t="s">
@@ -4981,15 +4970,15 @@
     <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45" s="9"/>
       <c r="B45" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C45" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D45" t="s">
         <v>186</v>
       </c>
-      <c r="D45" t="s">
-        <v>187</v>
-      </c>
-      <c r="E45" s="69">
+      <c r="E45">
         <v>3</v>
       </c>
       <c r="G45" s="10" t="s">
@@ -4999,15 +4988,15 @@
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46" s="9"/>
       <c r="B46" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C46" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D46" t="s">
         <v>186</v>
       </c>
-      <c r="D46" t="s">
-        <v>187</v>
-      </c>
-      <c r="E46" s="69">
+      <c r="E46">
         <v>3</v>
       </c>
       <c r="G46" s="10" t="s">
@@ -5017,15 +5006,15 @@
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" s="9"/>
       <c r="B47" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C47" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D47" t="s">
         <v>186</v>
       </c>
-      <c r="D47" t="s">
-        <v>187</v>
-      </c>
-      <c r="E47" s="69">
+      <c r="E47">
         <v>3</v>
       </c>
       <c r="G47" s="10" t="s">
@@ -5035,15 +5024,15 @@
     <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" s="9"/>
       <c r="B48" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C48" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D48" t="s">
         <v>186</v>
       </c>
-      <c r="D48" t="s">
-        <v>187</v>
-      </c>
-      <c r="E48" s="69">
+      <c r="E48">
         <v>3</v>
       </c>
       <c r="G48" s="10" t="s">
@@ -5053,20 +5042,20 @@
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" s="9"/>
       <c r="C49" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D49" t="s">
         <v>186</v>
-      </c>
-      <c r="D49" t="s">
-        <v>187</v>
       </c>
       <c r="G49" s="10"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" s="9"/>
       <c r="C50" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D50" t="s">
         <v>186</v>
-      </c>
-      <c r="D50" t="s">
-        <v>187</v>
       </c>
       <c r="G50" s="10"/>
     </row>
@@ -5074,10 +5063,10 @@
       <c r="A51" s="11"/>
       <c r="B51" s="12"/>
       <c r="C51" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>186</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>187</v>
       </c>
       <c r="E51" s="12"/>
       <c r="F51" s="12"/>
@@ -6078,7 +6067,7 @@
       </c>
       <c r="R14" s="21"/>
       <c r="S14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.4">
@@ -6126,7 +6115,7 @@
       </c>
       <c r="R15" s="67"/>
       <c r="S15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.4">
@@ -7064,7 +7053,7 @@
       <c r="J2" s="7"/>
       <c r="K2" s="8"/>
       <c r="L2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.4">
@@ -7074,14 +7063,14 @@
     <row r="4" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B4" s="9"/>
       <c r="G4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B5" s="9"/>
       <c r="C5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K5" s="10"/>
     </row>
@@ -7153,7 +7142,7 @@
       <c r="J18" s="7"/>
       <c r="K18" s="8"/>
       <c r="L18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.4">
@@ -7229,7 +7218,7 @@
       <c r="J33" s="7"/>
       <c r="K33" s="8"/>
       <c r="L33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.4">
@@ -7305,7 +7294,7 @@
       <c r="J48" s="7"/>
       <c r="K48" s="8"/>
       <c r="L48" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.4">
@@ -7688,34 +7677,29 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="C58" t="s">
-        <v>175</v>
-      </c>
-    </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B60" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B61" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B62" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B63" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B64" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5DBC11-2EF7-4B58-BFB9-9D4E7036694E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71B1FE8-E411-4579-B702-D94409F62569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="214">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1407,6 +1407,14 @@
   </si>
   <si>
     <t>未着手</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オルカ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サイコネ？</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1844,7 +1852,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2047,6 +2055,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5807,7 +5818,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB8A7F07-4822-4AA8-B3C3-66F7A08D4E6E}">
-  <dimension ref="B2:S36"/>
+  <dimension ref="A2:S36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.4">
@@ -6166,7 +6177,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B17" s="45">
         <v>21</v>
       </c>
@@ -6210,7 +6221,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B18" s="52">
         <v>28</v>
       </c>
@@ -6238,7 +6249,7 @@
       <c r="O18" s="41"/>
       <c r="P18" s="42"/>
     </row>
-    <row r="19" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B19" s="22" t="s">
         <v>61</v>
       </c>
@@ -6246,7 +6257,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B20" s="6" t="s">
         <v>59</v>
       </c>
@@ -6290,7 +6301,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B21" s="31"/>
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
@@ -6322,7 +6333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B22" s="45">
         <v>5</v>
       </c>
@@ -6366,14 +6377,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.4">
-      <c r="B23" s="47">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>212</v>
+      </c>
+      <c r="B23" s="68">
         <v>12</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="28">
         <v>13</v>
       </c>
-      <c r="D23" s="25">
+      <c r="D23" s="28">
         <v>14</v>
       </c>
       <c r="E23" s="25">
@@ -6410,7 +6424,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B24" s="47">
         <v>19</v>
       </c>
@@ -6454,7 +6468,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B25" s="48">
         <v>26</v>
       </c>
@@ -6494,12 +6508,12 @@
       </c>
       <c r="P25" s="42"/>
     </row>
-    <row r="26" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B26" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="2:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B27" s="6" t="s">
         <v>59</v>
       </c>
@@ -6522,7 +6536,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B28" s="31"/>
       <c r="C28" s="32"/>
       <c r="D28" s="32"/>
@@ -6533,7 +6547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B29" s="34">
         <v>2</v>
       </c>
@@ -6556,7 +6570,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B30" s="34">
         <v>9</v>
       </c>
@@ -6579,7 +6593,10 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>213</v>
+      </c>
       <c r="B31" s="34">
         <v>16</v>
       </c>
@@ -6602,7 +6619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="B32" s="37">
         <v>23</v>
       </c>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71B1FE8-E411-4579-B702-D94409F62569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892958F3-C788-4DB2-BF3A-5380253DFB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="217">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1415,6 +1415,27 @@
   </si>
   <si>
     <t>サイコネ？</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作ガイドUIイメージ</t>
+    <rPh sb="0" eb="2">
+      <t>ソウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル名</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パッシブ名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3738,6 +3759,258 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="楕円 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6885376B-519E-DB19-92F8-DE2E01850B91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11029950" y="704850"/>
+          <a:ext cx="809625" cy="809625"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="楕円 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EC0DFEE-C4FA-4AF2-A091-734BA3C69B49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10125075" y="1638300"/>
+          <a:ext cx="809625" cy="809625"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="楕円 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1070556F-EFA7-4967-B18B-1B041CCAE84F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11077575" y="2562225"/>
+          <a:ext cx="809625" cy="809625"/>
+        </a:xfrm>
+        <a:prstGeom prst="ellipse">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>400052</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>438152</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="正方形/長方形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8F46A1E-C3DA-4F9F-87C9-5DA4E2136209}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="2513663">
+          <a:off x="12058652" y="1676400"/>
+          <a:ext cx="723900" cy="695325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7051,14 +7324,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC62AB97-61B1-41EB-8933-806BF4A80E1C}">
-  <dimension ref="B1:L59"/>
+  <dimension ref="B1:T59"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
@@ -7072,69 +7345,84 @@
       <c r="L2" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="O2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B3" s="9"/>
       <c r="K3" s="10"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B4" s="9"/>
       <c r="G4" t="s">
         <v>193</v>
       </c>
       <c r="K4" s="10"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B5" s="9"/>
       <c r="C5" t="s">
         <v>194</v>
       </c>
       <c r="K5" s="10"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="P5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B6" s="9"/>
       <c r="K6" s="10"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B7" s="9"/>
       <c r="K7" s="10"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B8" s="9"/>
       <c r="K8" s="10"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B9" s="9"/>
       <c r="I9" t="s">
         <v>2</v>
       </c>
       <c r="K9" s="10"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="O9" t="s">
+        <v>43</v>
+      </c>
+      <c r="T9" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B10" s="9"/>
       <c r="K10" s="10"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B11" s="9"/>
       <c r="K11" s="10"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B12" s="9"/>
       <c r="K12" s="10"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B13" s="9"/>
       <c r="K13" s="10"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="S13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B14" s="9"/>
       <c r="K14" s="10"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B15" s="9"/>
       <c r="K15" s="10"/>
     </row>
-    <row r="16" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B16" s="11"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892958F3-C788-4DB2-BF3A-5380253DFB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFCC818-DFF3-40BC-BEAB-904701DCCC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="memo" sheetId="5" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$G$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$G$110</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="216">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1218,10 +1218,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>未着手</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>シーン</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1231,10 +1227,6 @@
   </si>
   <si>
     <t>マネージャー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>リザルト</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1406,10 +1398,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>未着手</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>オルカ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1436,6 +1424,14 @@
     <rPh sb="4" eb="5">
       <t>メイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオーバー</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -4331,7 +4327,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}">
-  <dimension ref="A1:L109"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
@@ -4380,7 +4377,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
@@ -4406,19 +4403,19 @@
         <v>77</v>
       </c>
       <c r="J4">
-        <f>SUM(E4:E107)</f>
-        <v>162</v>
+        <f>SUM(E4:E108)</f>
+        <v>164</v>
       </c>
       <c r="K4">
-        <f>SUMIFS(E4:E101,G4:G101,"未着手") +SUMIFS(E4:E101,G4:G101,"作業中")</f>
-        <v>83</v>
+        <f>SUMIFS(E4:E102,G4:G102,"未着手") +SUMIFS(E4:E102,G4:G102,"作業中")</f>
+        <v>50</v>
       </c>
       <c r="L4">
         <f xml:space="preserve"> K4 / J4</f>
-        <v>0.51234567901234573</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+        <v>0.3048780487804878</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
       <c r="A5" s="9"/>
       <c r="B5" s="10" t="s">
         <v>36</v>
@@ -4442,11 +4439,11 @@
         <v>78</v>
       </c>
       <c r="J5">
-        <f>SUMIFS(E4:E107,D4:D107,"プロト")</f>
-        <v>162</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+        <f>SUMIFS(E4:E108,D4:D108,"プロト")</f>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
       <c r="A6" s="9"/>
       <c r="B6" s="10" t="s">
         <v>37</v>
@@ -4470,11 +4467,11 @@
         <v>79</v>
       </c>
       <c r="J6">
-        <f>SUMIFS(E4:E107,D4:D107,"アルファ")</f>
+        <f>SUMIFS(E4:E108,D4:D108,"アルファ")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
       <c r="A7" s="9"/>
       <c r="B7" s="10" t="s">
         <v>38</v>
@@ -4489,17 +4486,17 @@
         <v>2</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>168</v>
+        <v>74</v>
       </c>
       <c r="I7" t="s">
         <v>80</v>
       </c>
       <c r="J7">
-        <f>SUMIFS(E4:E107,D4:D107,"ベータ")</f>
+        <f>SUMIFS(E4:E108,D4:D108,"ベータ")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="11"/>
       <c r="B8" s="13" t="s">
         <v>39</v>
@@ -4523,11 +4520,11 @@
         <v>81</v>
       </c>
       <c r="J8">
-        <f>SUMIFS(E4:E107,D4:D107,"マスター")</f>
+        <f>SUMIFS(E4:E108,D4:D108,"マスター")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
       <c r="A9" s="6" t="s">
         <v>1</v>
       </c>
@@ -4550,7 +4547,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
       <c r="A10" s="9"/>
       <c r="B10" s="10" t="s">
         <v>8</v>
@@ -4571,7 +4568,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
       <c r="A11" s="9"/>
       <c r="B11" s="10" t="s">
         <v>10</v>
@@ -4592,7 +4589,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
       <c r="A12" s="9"/>
       <c r="B12" s="10" t="s">
         <v>50</v>
@@ -4613,7 +4610,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
       <c r="A13" s="9"/>
       <c r="B13" s="10" t="s">
         <v>175</v>
@@ -4634,7 +4631,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="9"/>
       <c r="B14" s="10" t="s">
         <v>176</v>
@@ -4652,7 +4649,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="9"/>
       <c r="B15" s="10" t="s">
         <v>177</v>
@@ -4670,7 +4667,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="9"/>
       <c r="B16" s="10" t="s">
         <v>178</v>
@@ -4691,7 +4688,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="6" t="s">
         <v>5</v>
       </c>
@@ -4714,7 +4711,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="9"/>
       <c r="B18" s="10" t="s">
         <v>11</v>
@@ -4735,7 +4732,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="11"/>
       <c r="B19" s="13" t="s">
         <v>12</v>
@@ -4756,7 +4753,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="6" t="s">
         <v>47</v>
       </c>
@@ -4779,7 +4776,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="9"/>
       <c r="B21" s="10" t="s">
         <v>7</v>
@@ -4800,7 +4797,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="11"/>
       <c r="B22" s="13" t="s">
         <v>43</v>
@@ -4821,7 +4818,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="6" t="s">
         <v>48</v>
       </c>
@@ -4844,7 +4841,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="9"/>
       <c r="B24" s="10" t="s">
         <v>7</v>
@@ -4865,7 +4862,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="11"/>
       <c r="B25" s="13" t="s">
         <v>43</v>
@@ -4944,7 +4941,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="6" t="s">
         <v>4</v>
       </c>
@@ -4965,7 +4962,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="9"/>
       <c r="B30" s="10" t="s">
         <v>7</v>
@@ -4983,7 +4980,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="11"/>
       <c r="B31" s="13" t="s">
         <v>43</v>
@@ -5023,7 +5020,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="A33" s="6" t="s">
         <v>9</v>
       </c>
@@ -5065,10 +5062,10 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="9"/>
       <c r="B35" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C35" t="s">
         <v>34</v>
@@ -5083,202 +5080,202 @@
         <v>168</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="A36" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E36" s="7">
         <v>3</v>
       </c>
       <c r="F36" s="7"/>
-      <c r="G36" s="8" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="G36" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="A37" s="9"/>
       <c r="B37" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C37" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D37" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="A38" s="9"/>
       <c r="B38" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C38" t="s">
         <v>183</v>
       </c>
-      <c r="C38" t="s">
-        <v>185</v>
-      </c>
       <c r="D38" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E38">
         <v>2</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="A39" s="9"/>
       <c r="B39" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C39" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="9"/>
+      <c r="B40" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C40" t="s">
+        <v>183</v>
+      </c>
+      <c r="D40" t="s">
         <v>184</v>
       </c>
-      <c r="C39" t="s">
+      <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D39" t="s">
+      <c r="B41" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="E39">
+      <c r="C41" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E41" s="7">
         <v>3</v>
       </c>
-      <c r="G39" s="10" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A40" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="E40" s="7">
-        <v>3</v>
-      </c>
-      <c r="F40" s="7"/>
-      <c r="G40" s="10" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A41" s="9"/>
-      <c r="B41" t="s">
-        <v>189</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="D41" t="s">
-        <v>186</v>
-      </c>
-      <c r="E41">
-        <v>3</v>
-      </c>
+      <c r="F41" s="7"/>
       <c r="G41" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="A42" s="9"/>
       <c r="B42" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D42" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="A43" s="9"/>
       <c r="B43" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D43" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E43">
         <v>4</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="A44" s="9"/>
       <c r="B44" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D44" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="A45" s="9"/>
       <c r="B45" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D45" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46" s="9"/>
       <c r="B46" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D46" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -5290,13 +5287,13 @@
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" s="9"/>
       <c r="B47" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D47" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -5305,84 +5302,81 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="A48" s="9"/>
       <c r="B48" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D48" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E48">
         <v>3</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" s="9"/>
+      <c r="B49" t="s">
+        <v>200</v>
+      </c>
       <c r="C49" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D49" t="s">
-        <v>186</v>
-      </c>
-      <c r="G49" s="10"/>
+        <v>184</v>
+      </c>
+      <c r="E49">
+        <v>3</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" s="9"/>
       <c r="C50" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D50" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G50" s="10"/>
     </row>
-    <row r="51" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="11"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="13"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A52" s="9" t="s">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A51" s="9"/>
+      <c r="C51" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D51" t="s">
+        <v>184</v>
+      </c>
+      <c r="G51" s="10"/>
+    </row>
+    <row r="52" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="13"/>
+    </row>
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B53" t="s">
         <v>1</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D52" t="s">
-        <v>33</v>
-      </c>
-      <c r="E52">
-        <v>2</v>
-      </c>
-      <c r="F52">
-        <v>2</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A53" s="9"/>
-      <c r="B53" t="s">
-        <v>47</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>34</v>
@@ -5400,10 +5394,10 @@
         <v>74</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="A54" s="9"/>
       <c r="B54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>34</v>
@@ -5414,14 +5408,17 @@
       <c r="E54">
         <v>2</v>
       </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
       <c r="G54" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="A55" s="9"/>
       <c r="B55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>34</v>
@@ -5433,13 +5430,13 @@
         <v>2</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" s="9"/>
       <c r="B56" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>34</v>
@@ -5451,106 +5448,113 @@
         <v>2</v>
       </c>
       <c r="G56" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="9"/>
+      <c r="B57" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" t="s">
+        <v>33</v>
+      </c>
+      <c r="E57">
+        <v>2</v>
+      </c>
+      <c r="G57" s="10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="11"/>
-      <c r="B57" s="12" t="s">
+    <row r="58" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="11"/>
+      <c r="B58" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C57" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E57" s="12">
+      <c r="C58" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E58" s="12">
         <v>2</v>
       </c>
-      <c r="F57" s="12"/>
-      <c r="G57" s="13" t="s">
+      <c r="F58" s="12"/>
+      <c r="G58" s="13" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A58" s="9" t="s">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A59" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B59" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C58" t="s">
-        <v>34</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="C59" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" t="s">
         <v>66</v>
       </c>
-      <c r="G58" s="10" t="s">
+      <c r="G59" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="11"/>
-      <c r="B59" s="13" t="s">
+    <row r="60" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="11"/>
+      <c r="B60" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C59" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D59" s="12" t="s">
+      <c r="C60" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="13" t="s">
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A60" s="6" t="s">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A61" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B61" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C60" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D60" s="7" t="s">
+      <c r="C61" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D61" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="8" t="s">
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="11"/>
-      <c r="B61" s="13" t="s">
+    <row r="62" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="11"/>
+      <c r="B62" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C61" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D61" s="12" t="s">
+      <c r="C62" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D62" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="C62" t="s">
-        <v>34</v>
-      </c>
-      <c r="D62" t="s">
-        <v>33</v>
-      </c>
-      <c r="G62" t="s">
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -6071,17 +6075,35 @@
         <v>35</v>
       </c>
     </row>
+    <row r="110" spans="3:7" x14ac:dyDescent="0.4">
+      <c r="C110" t="s">
+        <v>34</v>
+      </c>
+      <c r="D110" t="s">
+        <v>33</v>
+      </c>
+      <c r="G110" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:G109" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}"/>
+  <autoFilter ref="A3:G110" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}">
+    <filterColumn colId="6">
+      <filters blank="1">
+        <filter val="作業中"/>
+        <filter val="未着手"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G35 G52:G109 G40:G48" xr:uid="{05F1DF74-5C3A-4656-9180-8CB2E572755F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G53:G110 G4:G49" xr:uid="{05F1DF74-5C3A-4656-9180-8CB2E572755F}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C35 C52:C109" xr:uid="{02D66180-7540-49E9-8878-4AAA7C63EEA4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C35 C53:C110" xr:uid="{02D66180-7540-49E9-8878-4AAA7C63EEA4}">
       <formula1>"C,B,A,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D35 D52:D109" xr:uid="{485BBF23-C878-4534-89D7-53615FBE9943}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D35 D53:D110" xr:uid="{485BBF23-C878-4534-89D7-53615FBE9943}">
       <formula1>"プロト,アルファ,ベータ,マスター"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6351,7 +6373,7 @@
       </c>
       <c r="R14" s="21"/>
       <c r="S14" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.4">
@@ -6399,7 +6421,7 @@
       </c>
       <c r="R15" s="67"/>
       <c r="S15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.4">
@@ -6652,7 +6674,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B23" s="68">
         <v>12</v>
@@ -6868,7 +6890,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B31" s="34">
         <v>16</v>
@@ -7343,10 +7365,10 @@
       <c r="J2" s="7"/>
       <c r="K2" s="8"/>
       <c r="L2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="O2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.4">
@@ -7356,18 +7378,18 @@
     <row r="4" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B4" s="9"/>
       <c r="G4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B5" s="9"/>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K5" s="10"/>
       <c r="P5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.4">
@@ -7392,7 +7414,7 @@
         <v>43</v>
       </c>
       <c r="T9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.4">
@@ -7447,7 +7469,7 @@
       <c r="J18" s="7"/>
       <c r="K18" s="8"/>
       <c r="L18" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.4">
@@ -7523,7 +7545,7 @@
       <c r="J33" s="7"/>
       <c r="K33" s="8"/>
       <c r="L33" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.4">
@@ -7599,7 +7621,7 @@
       <c r="J48" s="7"/>
       <c r="K48" s="8"/>
       <c r="L48" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.4">
@@ -7984,27 +8006,27 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B60" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B61" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B62" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B63" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B64" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFCC818-DFF3-40BC-BEAB-904701DCCC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79F6F39-0D7E-4D25-B343-B6D874BE68BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="memo" sheetId="5" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$G$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$G$107</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="229">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -297,13 +297,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>リソース管理</t>
-    <rPh sb="4" eb="6">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>敵1</t>
     <rPh sb="0" eb="1">
       <t>テキ</t>
@@ -318,13 +311,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>敵3</t>
-    <rPh sb="0" eb="1">
-      <t>テキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>回避</t>
     <rPh sb="0" eb="2">
       <t>カイヒ</t>
@@ -1197,13 +1183,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>スキル2(単体攻撃)</t>
-    <rPh sb="5" eb="9">
-      <t>タンタイコウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>スキル3(範囲攻撃)</t>
     <rPh sb="5" eb="9">
       <t>ハンイコウゲキ</t>
@@ -1432,6 +1411,108 @@
   </si>
   <si>
     <t>ゲームオーバー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フェード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オプション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルファ</t>
+  </si>
+  <si>
+    <t>エフェクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー攻撃ヒット</t>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵攻撃ヒット</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス攻撃1(突進)</t>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>トッシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス攻撃2(飛ぶ斬撃)</t>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ザンゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス攻撃3(連続斬撃)</t>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>レンゾクザンゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サウンド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サウンドマネージャー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>素材探し</t>
+    <rPh sb="0" eb="3">
+      <t>ソザイサガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実装</t>
+    <rPh sb="0" eb="2">
+      <t>ジッソウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1869,7 +1950,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2075,6 +2156,27 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4327,8 +4429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
@@ -4341,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
@@ -4368,16 +4469,16 @@
         <v>31</v>
       </c>
       <c r="J3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
@@ -4397,25 +4498,25 @@
         <v>3</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J4">
-        <f>SUM(E4:E108)</f>
-        <v>164</v>
+        <f>SUM(E4:E105)</f>
+        <v>181</v>
       </c>
       <c r="K4">
-        <f>SUMIFS(E4:E102,G4:G102,"未着手") +SUMIFS(E4:E102,G4:G102,"作業中")</f>
-        <v>50</v>
+        <f>SUMIFS(E4:E99,G4:G99,"未着手") +SUMIFS(E4:E99,G4:G99,"作業中")</f>
+        <v>39</v>
       </c>
       <c r="L4">
-        <f xml:space="preserve"> K4 / J4</f>
-        <v>0.3048780487804878</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+        <f xml:space="preserve"> 1 - K4 / J4</f>
+        <v>0.78453038674033149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="9"/>
       <c r="B5" s="10" t="s">
         <v>36</v>
@@ -4433,17 +4534,25 @@
         <v>1</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J5">
-        <f>SUMIFS(E4:E108,D4:D108,"プロト")</f>
-        <v>164</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+        <f>SUMIFS(E4:E105,D4:D105,"プロト")</f>
+        <v>155</v>
+      </c>
+      <c r="K5">
+        <f>SUMIFS(E4:E99,G4:G99,"未着手",D4:D99,"プロト") +SUMIFS(E4:E99,G4:G99,"作業中",D4:D99,"プロト")</f>
+        <v>17</v>
+      </c>
+      <c r="L5">
+        <f xml:space="preserve"> 1 - K5 / J5</f>
+        <v>0.89032258064516134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="9"/>
       <c r="B6" s="10" t="s">
         <v>37</v>
@@ -4461,17 +4570,25 @@
         <v>1</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J6">
-        <f>SUMIFS(E4:E108,D4:D108,"アルファ")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+        <f>SUMIFS(E4:E105,D4:D105,"アルファ")</f>
+        <v>14</v>
+      </c>
+      <c r="K6">
+        <f>SUMIFS(E4:E99,G4:G99,"未着手",D4:D99,"アルファ") +SUMIFS(E4:E99,G4:G99,"作業中",D4:D99,"アルファ")</f>
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <f t="shared" ref="L6:L8" si="0" xml:space="preserve"> 1 - K6 / J6</f>
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="9"/>
       <c r="B7" s="10" t="s">
         <v>38</v>
@@ -4485,18 +4602,29 @@
       <c r="E7">
         <v>2</v>
       </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
       <c r="G7" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J7">
-        <f>SUMIFS(E4:E108,D4:D108,"ベータ")</f>
+        <f>SUMIFS(E4:E105,D4:D105,"ベータ")</f>
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <f>SUMIFS(E4:E99,G4:G99,"未着手",D4:D99,"ベータ") +SUMIFS(E4:E99,G4:G99,"作業中",D4:D99,"ベータ")</f>
+        <v>12</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="11"/>
       <c r="B8" s="13" t="s">
         <v>39</v>
@@ -4514,17 +4642,21 @@
         <v>3</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J8">
-        <f>SUMIFS(E4:E108,D4:D108,"マスター")</f>
+        <f>SUMIFS(E4:E105,D4:D105,"マスター")</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+      <c r="L8" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="6" t="s">
         <v>1</v>
       </c>
@@ -4544,10 +4676,10 @@
         <v>1.5</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="9"/>
       <c r="B10" s="10" t="s">
         <v>8</v>
@@ -4565,10 +4697,10 @@
         <v>1.5</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="9"/>
       <c r="B11" s="10" t="s">
         <v>10</v>
@@ -4586,13 +4718,13 @@
         <v>5</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="9"/>
       <c r="B12" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
         <v>34</v>
@@ -4607,13 +4739,13 @@
         <v>3</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="9"/>
       <c r="B13" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C13" t="s">
         <v>34</v>
@@ -4628,13 +4760,13 @@
         <v>3</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="9"/>
       <c r="B14" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C14" t="s">
         <v>34</v>
@@ -4645,14 +4777,17 @@
       <c r="E14">
         <v>3</v>
       </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
       <c r="G14" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="9"/>
       <c r="B15" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C15" t="s">
         <v>34</v>
@@ -4663,290 +4798,300 @@
       <c r="E15">
         <v>3</v>
       </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
       <c r="G15" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="9"/>
-      <c r="B16" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="7">
+        <v>2</v>
+      </c>
+      <c r="F16" s="7">
+        <v>2</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="9"/>
+      <c r="B17" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="11"/>
+      <c r="B18" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="12">
+        <v>4</v>
+      </c>
+      <c r="F18" s="12">
+        <v>4</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="7">
+        <v>4</v>
+      </c>
+      <c r="F19" s="7">
+        <v>4</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="9"/>
+      <c r="B20" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="11"/>
+      <c r="B21" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="12">
         <v>3</v>
       </c>
-      <c r="F16">
+      <c r="F21" s="12">
+        <v>2</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="7">
+        <v>4</v>
+      </c>
+      <c r="F22" s="7">
+        <v>4</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="9"/>
+      <c r="B23" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="11"/>
+      <c r="B24" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="12">
         <v>3</v>
       </c>
-      <c r="G16" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="7" t="s">
+      <c r="F24" s="12">
+        <v>2</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E25" s="7">
+        <v>6</v>
+      </c>
+      <c r="F25" s="7">
+        <v>6</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="9"/>
+      <c r="B26" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26">
         <v>2</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F26">
         <v>2</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="9"/>
-      <c r="B18" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="G26" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="11"/>
+      <c r="B27" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E18">
-        <v>5</v>
-      </c>
-      <c r="F18">
-        <v>5</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="11"/>
-      <c r="B19" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="12" t="s">
+      <c r="E27" s="12">
+        <v>4</v>
+      </c>
+      <c r="F27" s="12">
+        <v>4</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="12">
-        <v>4</v>
-      </c>
-      <c r="F19" s="12">
-        <v>4</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="7">
-        <v>4</v>
-      </c>
-      <c r="F20" s="7">
-        <v>4</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="9"/>
-      <c r="B21" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
-      <c r="F21">
-        <v>2</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="11"/>
-      <c r="B22" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="12">
-        <v>3</v>
-      </c>
-      <c r="F22" s="12">
-        <v>2</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="7">
-        <v>4</v>
-      </c>
-      <c r="F23" s="7">
-        <v>4</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="9"/>
-      <c r="B24" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24">
-        <v>2</v>
-      </c>
-      <c r="F24">
-        <v>2</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="11"/>
-      <c r="B25" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" s="12">
-        <v>3</v>
-      </c>
-      <c r="F25" s="12">
-        <v>2</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A26" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" s="7">
-        <v>4</v>
-      </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A27" s="9"/>
-      <c r="B27" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" t="s">
-        <v>33</v>
-      </c>
-      <c r="E27">
-        <v>2</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="11"/>
-      <c r="B28" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E28" s="12">
-        <v>3</v>
-      </c>
-      <c r="F28" s="12"/>
-      <c r="G28" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E28" s="15">
+        <v>15</v>
+      </c>
+      <c r="F28" s="15"/>
+      <c r="G28" s="16" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>34</v>
@@ -4955,35 +5100,40 @@
         <v>33</v>
       </c>
       <c r="E29" s="7">
-        <v>6</v>
-      </c>
-      <c r="F29" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="F29" s="7">
+        <v>1</v>
+      </c>
       <c r="G29" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="9"/>
-      <c r="B30" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="6"/>
+      <c r="B30" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C30" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="E30">
-        <v>2</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E30" s="74">
+        <v>4</v>
+      </c>
+      <c r="F30" s="74">
+        <v>4</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="11"/>
       <c r="B31" s="13" t="s">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>34</v>
@@ -4992,391 +5142,432 @@
         <v>33</v>
       </c>
       <c r="E31" s="12">
-        <v>4</v>
-      </c>
-      <c r="F31" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="F31" s="75">
+        <v>6</v>
+      </c>
       <c r="G31" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E32" s="7">
         <v>3</v>
       </c>
-      <c r="B32" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E32" s="15">
-        <v>15</v>
-      </c>
-      <c r="F32" s="15"/>
-      <c r="G32" s="16" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E33" s="7">
+      <c r="F32" s="7">
+        <v>3</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="9"/>
+      <c r="B33" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C33" s="70" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" s="70" t="s">
+        <v>181</v>
+      </c>
+      <c r="E33" s="70">
         <v>2</v>
       </c>
-      <c r="F33" s="7">
-        <v>1</v>
-      </c>
-      <c r="G33" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="11"/>
-      <c r="B34" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E34" s="12">
-        <v>4</v>
-      </c>
-      <c r="F34" s="12"/>
-      <c r="G34" s="13" t="s">
-        <v>35</v>
+      <c r="F33" s="69">
+        <v>2</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="9"/>
+      <c r="B34" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C34" s="70" t="s">
+        <v>180</v>
+      </c>
+      <c r="D34" s="70" t="s">
+        <v>181</v>
+      </c>
+      <c r="E34" s="70">
+        <v>2</v>
+      </c>
+      <c r="F34" s="69">
+        <v>2</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="9"/>
       <c r="B35" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="C35" t="s">
-        <v>34</v>
-      </c>
-      <c r="D35" t="s">
-        <v>33</v>
-      </c>
-      <c r="E35">
-        <v>6</v>
+        <v>212</v>
+      </c>
+      <c r="C35" s="70" t="s">
+        <v>100</v>
+      </c>
+      <c r="D35" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" s="70">
+        <v>2</v>
+      </c>
+      <c r="F35" s="69">
+        <v>2</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="E36" s="7">
-        <v>3</v>
-      </c>
-      <c r="F36" s="7"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="9"/>
+      <c r="B36" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C36" s="70"/>
+      <c r="D36" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" s="70">
+        <v>2</v>
+      </c>
+      <c r="F36" s="69">
+        <v>2</v>
+      </c>
       <c r="G36" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="9"/>
       <c r="B37" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C37" s="70"/>
+      <c r="D37" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="70">
+        <v>2</v>
+      </c>
+      <c r="F37" s="69">
+        <v>2</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="11"/>
+      <c r="B38" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C38" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D38" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E38" s="12">
+        <v>3</v>
+      </c>
+      <c r="F38" s="75">
+        <v>3</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B39" s="70" t="s">
         <v>183</v>
       </c>
-      <c r="D37" t="s">
+      <c r="C39" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D39" s="70" t="s">
+        <v>181</v>
+      </c>
+      <c r="E39" s="70">
+        <v>3</v>
+      </c>
+      <c r="F39" s="70">
+        <v>3</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="9"/>
+      <c r="B40" t="s">
         <v>184</v>
       </c>
-      <c r="E37">
-        <v>2</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="9"/>
-      <c r="B38" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="C38" t="s">
-        <v>183</v>
-      </c>
-      <c r="D38" t="s">
-        <v>184</v>
-      </c>
-      <c r="E38">
-        <v>2</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="9"/>
-      <c r="B39" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="C39" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39" t="s">
-        <v>64</v>
-      </c>
-      <c r="E39">
-        <v>2</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="9"/>
-      <c r="B40" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="C40" t="s">
-        <v>183</v>
+      <c r="C40" s="9" t="s">
+        <v>180</v>
       </c>
       <c r="D40" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E40">
         <v>3</v>
       </c>
+      <c r="F40" s="69">
+        <v>3</v>
+      </c>
       <c r="G40" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A41" s="9"/>
+      <c r="B41" t="s">
         <v>185</v>
       </c>
-      <c r="B41" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="E41" s="7">
+      <c r="C41" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D41" t="s">
+        <v>181</v>
+      </c>
+      <c r="E41">
+        <v>4</v>
+      </c>
+      <c r="F41" s="69">
         <v>3</v>
       </c>
-      <c r="F41" s="7"/>
       <c r="G41" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="9"/>
       <c r="B42" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D42" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E42">
+        <v>4</v>
+      </c>
+      <c r="F42" s="69">
         <v>3</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" s="9"/>
       <c r="B43" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D43" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="F43" s="69">
+        <v>3</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" s="9"/>
       <c r="B44" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D44" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F44" s="69">
+        <v>1</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45" s="9"/>
       <c r="B45" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D45" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F45" s="69">
+        <v>1</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46" s="9"/>
       <c r="B46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D46" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E46">
         <v>3</v>
       </c>
+      <c r="F46" s="69">
+        <v>2</v>
+      </c>
       <c r="G46" s="10" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" s="9"/>
       <c r="B47" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D47" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E47">
         <v>3</v>
       </c>
+      <c r="F47" s="69">
+        <v>2</v>
+      </c>
       <c r="G47" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" s="9"/>
-      <c r="B48" t="s">
-        <v>199</v>
-      </c>
       <c r="C48" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D48" t="s">
-        <v>184</v>
-      </c>
-      <c r="E48">
-        <v>3</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>74</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="G48" s="10"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" s="9"/>
-      <c r="B49" t="s">
-        <v>200</v>
-      </c>
       <c r="C49" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D49" t="s">
-        <v>184</v>
-      </c>
-      <c r="E49">
-        <v>3</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A50" s="9"/>
-      <c r="C50" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="D50" t="s">
-        <v>184</v>
-      </c>
-      <c r="G50" s="10"/>
+        <v>181</v>
+      </c>
+      <c r="G49" s="10"/>
+    </row>
+    <row r="50" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="11"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="13"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A51" s="9"/>
+      <c r="A51" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1</v>
+      </c>
       <c r="C51" s="9" t="s">
-        <v>183</v>
+        <v>34</v>
       </c>
       <c r="D51" t="s">
-        <v>184</v>
-      </c>
-      <c r="G51" s="10"/>
-    </row>
-    <row r="52" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="11"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="13"/>
-    </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="9" t="s">
-        <v>40</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="E51">
+        <v>2</v>
+      </c>
+      <c r="F51">
+        <v>2</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A52" s="9"/>
+      <c r="B52" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52" t="s">
+        <v>33</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A53" s="9"/>
       <c r="B53" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>34</v>
@@ -5387,17 +5578,14 @@
       <c r="E53">
         <v>2</v>
       </c>
-      <c r="F53">
-        <v>2</v>
-      </c>
       <c r="G53" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54" s="9"/>
       <c r="B54" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>34</v>
@@ -5408,234 +5596,296 @@
       <c r="E54">
         <v>2</v>
       </c>
-      <c r="F54">
+      <c r="G54" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="11"/>
+      <c r="B55" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E55" s="12">
         <v>2</v>
       </c>
-      <c r="G54" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="9"/>
-      <c r="B55" t="s">
-        <v>48</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D55" t="s">
-        <v>33</v>
-      </c>
-      <c r="E55">
-        <v>2</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>74</v>
+      <c r="F55" s="12"/>
+      <c r="G55" s="13" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A56" s="9"/>
-      <c r="B56" t="s">
-        <v>49</v>
-      </c>
-      <c r="C56" s="9" t="s">
+      <c r="A56" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" t="s">
         <v>34</v>
       </c>
       <c r="D56" t="s">
-        <v>33</v>
-      </c>
-      <c r="E56">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="G56" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="9"/>
-      <c r="B57" t="s">
+    <row r="57" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="11"/>
+      <c r="B57" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A58" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="11"/>
+      <c r="B59" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A60" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="B60" s="72" t="s">
+        <v>218</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E60" s="7">
+        <v>2</v>
+      </c>
+      <c r="F60" s="7"/>
+      <c r="G60" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A61" s="9"/>
+      <c r="B61" s="71" t="s">
+        <v>220</v>
+      </c>
+      <c r="C61" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="D61" s="70" t="s">
+        <v>216</v>
+      </c>
+      <c r="E61" s="70">
+        <v>2</v>
+      </c>
+      <c r="F61" s="70"/>
+      <c r="G61" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A62" s="9"/>
+      <c r="B62" s="71" t="s">
+        <v>221</v>
+      </c>
+      <c r="C62" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="D62" s="70" t="s">
+        <v>216</v>
+      </c>
+      <c r="E62" s="70">
+        <v>2</v>
+      </c>
+      <c r="F62" s="70"/>
+      <c r="G62" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A63" s="9"/>
+      <c r="B63" s="71" t="s">
+        <v>219</v>
+      </c>
+      <c r="C63" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="D63" s="70" t="s">
+        <v>216</v>
+      </c>
+      <c r="E63" s="70">
+        <v>2</v>
+      </c>
+      <c r="F63" s="70"/>
+      <c r="G63" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A64" s="9"/>
+      <c r="B64" s="71" t="s">
+        <v>222</v>
+      </c>
+      <c r="C64" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="D64" s="70" t="s">
+        <v>216</v>
+      </c>
+      <c r="E64" s="70">
+        <v>2</v>
+      </c>
+      <c r="F64" s="70"/>
+      <c r="G64" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A65" s="9"/>
+      <c r="B65" s="71" t="s">
+        <v>223</v>
+      </c>
+      <c r="C65" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="70" t="s">
+        <v>216</v>
+      </c>
+      <c r="E65" s="70">
+        <v>2</v>
+      </c>
+      <c r="F65" s="70"/>
+      <c r="G65" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A66" s="11"/>
+      <c r="B66" s="73" t="s">
+        <v>224</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="E66" s="12">
+        <v>2</v>
+      </c>
+      <c r="F66" s="12"/>
+      <c r="G66" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A67" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B67" s="72" t="s">
+        <v>226</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E67" s="7">
+        <v>1</v>
+      </c>
+      <c r="F67" s="7">
+        <v>1</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A68" s="9"/>
+      <c r="B68" s="71" t="s">
+        <v>227</v>
+      </c>
+      <c r="C68" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="D68" s="70" t="s">
+        <v>64</v>
+      </c>
+      <c r="E68" s="69">
+        <v>8</v>
+      </c>
+      <c r="F68" s="70"/>
+      <c r="G68" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A69" s="11"/>
+      <c r="B69" s="73" t="s">
+        <v>228</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E69" s="12">
         <v>4</v>
       </c>
-      <c r="C57" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D57" t="s">
-        <v>33</v>
-      </c>
-      <c r="E57">
-        <v>2</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="11"/>
-      <c r="B58" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E58" s="12">
-        <v>2</v>
-      </c>
-      <c r="F58" s="12"/>
-      <c r="G58" s="13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A59" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C59" t="s">
-        <v>34</v>
-      </c>
-      <c r="D59" t="s">
-        <v>66</v>
-      </c>
-      <c r="G59" s="10" t="s">
+      <c r="F69" s="12"/>
+      <c r="G69" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="11"/>
-      <c r="B60" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C60" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A61" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="11"/>
-      <c r="B62" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="C63" t="s">
-        <v>34</v>
-      </c>
-      <c r="D63" t="s">
-        <v>33</v>
-      </c>
-      <c r="G63" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="C64" t="s">
-        <v>34</v>
-      </c>
-      <c r="D64" t="s">
-        <v>33</v>
-      </c>
-      <c r="G64" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="65" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C65" t="s">
-        <v>34</v>
-      </c>
-      <c r="D65" t="s">
-        <v>33</v>
-      </c>
-      <c r="G65" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="66" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C66" t="s">
-        <v>34</v>
-      </c>
-      <c r="D66" t="s">
-        <v>33</v>
-      </c>
-      <c r="G66" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="67" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C67" t="s">
-        <v>34</v>
-      </c>
-      <c r="D67" t="s">
-        <v>33</v>
-      </c>
-      <c r="G67" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="68" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C68" t="s">
-        <v>34</v>
-      </c>
-      <c r="D68" t="s">
-        <v>33</v>
-      </c>
-      <c r="G68" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="69" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C69" t="s">
-        <v>34</v>
-      </c>
-      <c r="D69" t="s">
-        <v>33</v>
-      </c>
-      <c r="G69" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="70" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C70" t="s">
         <v>34</v>
       </c>
@@ -5646,7 +5896,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C71" t="s">
         <v>34</v>
       </c>
@@ -5657,7 +5907,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C72" t="s">
         <v>34</v>
       </c>
@@ -5668,7 +5918,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C73" t="s">
         <v>34</v>
       </c>
@@ -5679,7 +5929,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C74" t="s">
         <v>34</v>
       </c>
@@ -5690,7 +5940,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C75" t="s">
         <v>34</v>
       </c>
@@ -5701,7 +5951,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C76" t="s">
         <v>34</v>
       </c>
@@ -5712,7 +5962,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="77" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C77" t="s">
         <v>34</v>
       </c>
@@ -5723,7 +5973,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C78" t="s">
         <v>34</v>
       </c>
@@ -5734,7 +5984,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="79" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C79" t="s">
         <v>34</v>
       </c>
@@ -5745,7 +5995,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="3:7" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.4">
       <c r="C80" t="s">
         <v>34</v>
       </c>
@@ -6053,57 +6303,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C108" t="s">
-        <v>34</v>
-      </c>
-      <c r="D108" t="s">
-        <v>33</v>
-      </c>
-      <c r="G108" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="109" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C109" t="s">
-        <v>34</v>
-      </c>
-      <c r="D109" t="s">
-        <v>33</v>
-      </c>
-      <c r="G109" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="110" spans="3:7" x14ac:dyDescent="0.4">
-      <c r="C110" t="s">
-        <v>34</v>
-      </c>
-      <c r="D110" t="s">
-        <v>33</v>
-      </c>
-      <c r="G110" t="s">
-        <v>35</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:G110" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}">
-    <filterColumn colId="6">
-      <filters blank="1">
-        <filter val="作業中"/>
-        <filter val="未着手"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:G107" xr:uid="{3ABA19D7-703C-4BDA-ABBE-D42092489F0E}"/>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G53:G110 G4:G49" xr:uid="{05F1DF74-5C3A-4656-9180-8CB2E572755F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G47 G51:G107" xr:uid="{05F1DF74-5C3A-4656-9180-8CB2E572755F}">
       <formula1>"未着手,作業中,完了"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C35 C53:C110" xr:uid="{02D66180-7540-49E9-8878-4AAA7C63EEA4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C31 C51:C107" xr:uid="{02D66180-7540-49E9-8878-4AAA7C63EEA4}">
       <formula1>"C,B,A,S"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D35 D53:D110" xr:uid="{485BBF23-C878-4534-89D7-53615FBE9943}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D31 D51:D107" xr:uid="{485BBF23-C878-4534-89D7-53615FBE9943}">
       <formula1>"プロト,アルファ,ベータ,マスター"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6118,19 +6328,19 @@
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.4">
       <c r="D2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" t="s">
         <v>65</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>67</v>
       </c>
-      <c r="G2" t="s">
-        <v>69</v>
-      </c>
       <c r="H2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -6142,30 +6352,30 @@
     </row>
     <row r="4" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C5" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="F5" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="G5" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="H5" s="16" t="s">
         <v>56</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.4">
@@ -6282,54 +6492,54 @@
     </row>
     <row r="12" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B12" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B13" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="G13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="H13" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="J13" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>59</v>
-      </c>
       <c r="K13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M13" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="N13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="M13" s="7" t="s">
+      <c r="O13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="N13" s="7" t="s">
+      <c r="P13" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.4">
@@ -6373,7 +6583,7 @@
       </c>
       <c r="R14" s="21"/>
       <c r="S14" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.4">
@@ -6421,7 +6631,7 @@
       </c>
       <c r="R15" s="67"/>
       <c r="S15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.4">
@@ -6546,54 +6756,54 @@
     </row>
     <row r="19" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B19" s="22" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J19" s="22" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B20" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C20" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="F20" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="G20" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="H20" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="J20" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>59</v>
-      </c>
       <c r="K20" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M20" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="L20" s="7" t="s">
+      <c r="N20" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="M20" s="7" t="s">
+      <c r="O20" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="N20" s="7" t="s">
+      <c r="P20" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.4">
@@ -6674,7 +6884,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B23" s="68">
         <v>12</v>
@@ -6805,30 +7015,30 @@
     </row>
     <row r="26" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B26" s="24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B27" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C27" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="F27" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="G27" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="H27" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.4">
@@ -6890,7 +7100,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B31" s="34">
         <v>16</v>
@@ -6952,30 +7162,30 @@
     </row>
     <row r="34" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B34" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B35" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C35" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="F35" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="G35" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="H35" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -7080,27 +7290,27 @@
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J3" t="s">
+        <v>161</v>
+      </c>
+      <c r="K3" t="s">
+        <v>162</v>
+      </c>
+      <c r="L3" t="s">
         <v>163</v>
       </c>
-      <c r="K3" t="s">
+      <c r="M3" t="s">
         <v>164</v>
-      </c>
-      <c r="L3" t="s">
-        <v>165</v>
-      </c>
-      <c r="M3" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.4">
@@ -7113,43 +7323,43 @@
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.4">
       <c r="I5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D7" t="s">
         <v>155</v>
       </c>
-      <c r="D7" t="s">
-        <v>157</v>
-      </c>
       <c r="I7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N7" t="s">
+        <v>112</v>
+      </c>
+      <c r="P7" t="s">
         <v>114</v>
-      </c>
-      <c r="P7" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="K9" t="s">
         <v>32</v>
       </c>
       <c r="M9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.4">
@@ -7170,23 +7380,23 @@
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -7206,17 +7416,17 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
@@ -7231,111 +7441,111 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N17" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C20" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B21" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -7365,10 +7575,10 @@
       <c r="J2" s="7"/>
       <c r="K2" s="8"/>
       <c r="L2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="O2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.4">
@@ -7378,18 +7588,18 @@
     <row r="4" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B4" s="9"/>
       <c r="G4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B5" s="9"/>
       <c r="C5" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="K5" s="10"/>
       <c r="P5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.4">
@@ -7414,7 +7624,7 @@
         <v>43</v>
       </c>
       <c r="T9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.4">
@@ -7469,7 +7679,7 @@
       <c r="J18" s="7"/>
       <c r="K18" s="8"/>
       <c r="L18" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.4">
@@ -7545,7 +7755,7 @@
       <c r="J33" s="7"/>
       <c r="K33" s="8"/>
       <c r="L33" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.4">
@@ -7621,7 +7831,7 @@
       <c r="J48" s="7"/>
       <c r="K48" s="8"/>
       <c r="L48" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.4">
@@ -7696,7 +7906,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -7711,113 +7921,113 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" t="s">
         <v>100</v>
-      </c>
-      <c r="D10" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" t="s">
         <v>140</v>
-      </c>
-      <c r="C21" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
@@ -7825,7 +8035,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
@@ -7833,15 +8043,15 @@
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C24" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
@@ -7849,122 +8059,122 @@
         <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C26" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C28" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C31" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C32" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C33" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C35" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C36" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C38" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C39" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C40" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C42" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C43" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C44" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C45" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.4">
       <c r="C46" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C52" t="s">
         <v>2</v>
@@ -7972,31 +8182,31 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B53" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C53" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B54" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C54" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B55" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C55" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B56" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.4">
@@ -8006,27 +8216,27 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B60" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B61" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B62" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B63" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B64" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -5,21 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79F6F39-0D7E-4D25-B343-B6D874BE68BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D722D533-9403-40A2-B7C6-DD07E74C2DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-23250" yWindow="1185" windowWidth="21600" windowHeight="13440" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
-    <sheet name="カレンダー" sheetId="4" r:id="rId2"/>
-    <sheet name="クラス一覧" sheetId="2" r:id="rId3"/>
-    <sheet name="クラス図" sheetId="3" r:id="rId4"/>
-    <sheet name="プレイヤー設計" sheetId="6" r:id="rId5"/>
-    <sheet name="ゲーム画面イメージ" sheetId="7" r:id="rId6"/>
-    <sheet name="memo" sheetId="5" r:id="rId7"/>
+    <sheet name="やることとか書き出し" sheetId="8" r:id="rId2"/>
+    <sheet name="カレンダー" sheetId="4" r:id="rId3"/>
+    <sheet name="クラス一覧" sheetId="2" r:id="rId4"/>
+    <sheet name="クラス図" sheetId="3" r:id="rId5"/>
+    <sheet name="プレイヤー設計" sheetId="6" r:id="rId6"/>
+    <sheet name="ゲーム画面イメージ" sheetId="7" r:id="rId7"/>
+    <sheet name="memo" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$G$107</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="257">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1511,6 +1512,259 @@
   <si>
     <t>実装</t>
     <rPh sb="0" eb="2">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やることとか書き出し</t>
+    <rPh sb="6" eb="7">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中でスピン使えるようにする</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒットストップ実装</t>
+    <rPh sb="7" eb="9">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テレポート攻撃実装</t>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵同士の距離を空ける(テレポートをいっぱい使わせるため)</t>
+    <rPh sb="0" eb="3">
+      <t>テキドウシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キョリ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージをでかくする(上をやるため)</t>
+    <rPh sb="11" eb="12">
+      <t>ウエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動を快適にする(ダッシュとか実装)</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイテキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス登場演出でカメラを揺らす+歪みエフェクト</t>
+    <rPh sb="2" eb="6">
+      <t>トウジョウエンシュツ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ユ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ユガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンのカメラを改善する(鳥とかが高いところに行くと見えないため)</t>
+    <rPh sb="10" eb="12">
+      <t>カイゼン</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>トリ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>タカ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通常攻撃の硬直を短く</t>
+    <rPh sb="0" eb="4">
+      <t>ツウジョウコウゲキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウチョク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ミジカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス線で死んだらボス戦手前から始まるように</t>
+    <rPh sb="2" eb="3">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>テマエ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ハジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>書いた日付</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やった日付</t>
+    <rPh sb="3" eb="5">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やりたいこと</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スキル追加(ライジングフレイム)</t>
+    <rPh sb="3" eb="5">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遠距離攻撃追加(魔法)</t>
+    <rPh sb="0" eb="7">
+      <t>エンキョリコウゲキツイカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>マホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵、ステージ、ボスを増やす</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>余裕があったらやりたいこと</t>
+    <rPh sb="0" eb="2">
+      <t>ヨユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やることメモから引用</t>
+    <rPh sb="8" eb="10">
+      <t>インヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスの撃破演出</t>
+    <rPh sb="3" eb="7">
+      <t>ゲキハエンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームシーン以外を凝る</t>
+    <rPh sb="6" eb="8">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クリアシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオーバーシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーズシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オプションシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>細かいエフェクト実装</t>
+    <rPh sb="0" eb="1">
+      <t>コマ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SE、BGMの実装</t>
+    <rPh sb="7" eb="9">
       <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -1950,7 +2204,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2158,25 +2412,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5114,16 +5350,16 @@
       <c r="B30" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C30" s="74" t="s">
+      <c r="C30" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="74" t="s">
+      <c r="D30" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="74">
+      <c r="E30" s="7">
         <v>4</v>
       </c>
-      <c r="F30" s="74">
+      <c r="F30" s="7">
         <v>4</v>
       </c>
       <c r="G30" s="8" t="s">
@@ -5144,7 +5380,7 @@
       <c r="E31" s="12">
         <v>6</v>
       </c>
-      <c r="F31" s="75">
+      <c r="F31" s="12">
         <v>6</v>
       </c>
       <c r="G31" s="13" t="s">
@@ -5179,16 +5415,16 @@
       <c r="B33" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="C33" s="70" t="s">
+      <c r="C33" t="s">
         <v>180</v>
       </c>
-      <c r="D33" s="70" t="s">
+      <c r="D33" t="s">
         <v>181</v>
       </c>
-      <c r="E33" s="70">
+      <c r="E33">
         <v>2</v>
       </c>
-      <c r="F33" s="69">
+      <c r="F33">
         <v>2</v>
       </c>
       <c r="G33" s="10" t="s">
@@ -5200,16 +5436,16 @@
       <c r="B34" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="C34" s="70" t="s">
+      <c r="C34" t="s">
         <v>180</v>
       </c>
-      <c r="D34" s="70" t="s">
+      <c r="D34" t="s">
         <v>181</v>
       </c>
-      <c r="E34" s="70">
+      <c r="E34">
         <v>2</v>
       </c>
-      <c r="F34" s="69">
+      <c r="F34">
         <v>2</v>
       </c>
       <c r="G34" s="10" t="s">
@@ -5221,16 +5457,16 @@
       <c r="B35" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="C35" s="70" t="s">
+      <c r="C35" t="s">
         <v>100</v>
       </c>
-      <c r="D35" s="70" t="s">
+      <c r="D35" t="s">
         <v>62</v>
       </c>
-      <c r="E35" s="70">
+      <c r="E35">
         <v>2</v>
       </c>
-      <c r="F35" s="69">
+      <c r="F35">
         <v>2</v>
       </c>
       <c r="G35" s="10" t="s">
@@ -5242,14 +5478,13 @@
       <c r="B36" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="C36" s="70"/>
-      <c r="D36" s="70" t="s">
+      <c r="D36" t="s">
         <v>62</v>
       </c>
-      <c r="E36" s="70">
+      <c r="E36">
         <v>2</v>
       </c>
-      <c r="F36" s="69">
+      <c r="F36">
         <v>2</v>
       </c>
       <c r="G36" s="10" t="s">
@@ -5261,14 +5496,13 @@
       <c r="B37" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="C37" s="70"/>
-      <c r="D37" s="70" t="s">
+      <c r="D37" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="70">
+      <c r="E37">
         <v>2</v>
       </c>
-      <c r="F37" s="69">
+      <c r="F37">
         <v>2</v>
       </c>
       <c r="G37" s="10" t="s">
@@ -5289,7 +5523,7 @@
       <c r="E38" s="12">
         <v>3</v>
       </c>
-      <c r="F38" s="75">
+      <c r="F38" s="12">
         <v>3</v>
       </c>
       <c r="G38" s="13" t="s">
@@ -5300,19 +5534,19 @@
       <c r="A39" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B39" s="70" t="s">
+      <c r="B39" t="s">
         <v>183</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="D39" s="70" t="s">
+      <c r="D39" t="s">
         <v>181</v>
       </c>
-      <c r="E39" s="70">
+      <c r="E39">
         <v>3</v>
       </c>
-      <c r="F39" s="70">
+      <c r="F39">
         <v>3</v>
       </c>
       <c r="G39" s="10" t="s">
@@ -5333,7 +5567,7 @@
       <c r="E40">
         <v>3</v>
       </c>
-      <c r="F40" s="69">
+      <c r="F40">
         <v>3</v>
       </c>
       <c r="G40" s="10" t="s">
@@ -5354,7 +5588,7 @@
       <c r="E41">
         <v>4</v>
       </c>
-      <c r="F41" s="69">
+      <c r="F41">
         <v>3</v>
       </c>
       <c r="G41" s="10" t="s">
@@ -5375,7 +5609,7 @@
       <c r="E42">
         <v>4</v>
       </c>
-      <c r="F42" s="69">
+      <c r="F42">
         <v>3</v>
       </c>
       <c r="G42" s="10" t="s">
@@ -5396,7 +5630,7 @@
       <c r="E43">
         <v>2</v>
       </c>
-      <c r="F43" s="69">
+      <c r="F43">
         <v>3</v>
       </c>
       <c r="G43" s="10" t="s">
@@ -5417,7 +5651,7 @@
       <c r="E44">
         <v>3</v>
       </c>
-      <c r="F44" s="69">
+      <c r="F44">
         <v>1</v>
       </c>
       <c r="G44" s="10" t="s">
@@ -5438,7 +5672,7 @@
       <c r="E45">
         <v>3</v>
       </c>
-      <c r="F45" s="69">
+      <c r="F45">
         <v>1</v>
       </c>
       <c r="G45" s="10" t="s">
@@ -5459,7 +5693,7 @@
       <c r="E46">
         <v>3</v>
       </c>
-      <c r="F46" s="69">
+      <c r="F46">
         <v>2</v>
       </c>
       <c r="G46" s="10" t="s">
@@ -5480,7 +5714,7 @@
       <c r="E47">
         <v>3</v>
       </c>
-      <c r="F47" s="69">
+      <c r="F47">
         <v>2</v>
       </c>
       <c r="G47" s="10" t="s">
@@ -5693,7 +5927,7 @@
       <c r="A60" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="B60" s="72" t="s">
+      <c r="B60" s="8" t="s">
         <v>218</v>
       </c>
       <c r="C60" s="7" t="s">
@@ -5712,102 +5946,97 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" s="9"/>
-      <c r="B61" s="71" t="s">
+      <c r="B61" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="C61" s="70" t="s">
+      <c r="C61" t="s">
         <v>34</v>
       </c>
-      <c r="D61" s="70" t="s">
+      <c r="D61" t="s">
         <v>216</v>
       </c>
-      <c r="E61" s="70">
+      <c r="E61">
         <v>2</v>
       </c>
-      <c r="F61" s="70"/>
       <c r="G61" s="10" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" s="9"/>
-      <c r="B62" s="71" t="s">
+      <c r="B62" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="C62" s="70" t="s">
+      <c r="C62" t="s">
         <v>34</v>
       </c>
-      <c r="D62" s="70" t="s">
+      <c r="D62" t="s">
         <v>216</v>
       </c>
-      <c r="E62" s="70">
+      <c r="E62">
         <v>2</v>
       </c>
-      <c r="F62" s="70"/>
       <c r="G62" s="10" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" s="9"/>
-      <c r="B63" s="71" t="s">
+      <c r="B63" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="C63" s="70" t="s">
+      <c r="C63" t="s">
         <v>34</v>
       </c>
-      <c r="D63" s="70" t="s">
+      <c r="D63" t="s">
         <v>216</v>
       </c>
-      <c r="E63" s="70">
+      <c r="E63">
         <v>2</v>
       </c>
-      <c r="F63" s="70"/>
       <c r="G63" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64" s="9"/>
-      <c r="B64" s="71" t="s">
+      <c r="B64" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="C64" s="70" t="s">
+      <c r="C64" t="s">
         <v>34</v>
       </c>
-      <c r="D64" s="70" t="s">
+      <c r="D64" t="s">
         <v>216</v>
       </c>
-      <c r="E64" s="70">
+      <c r="E64">
         <v>2</v>
       </c>
-      <c r="F64" s="70"/>
       <c r="G64" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A65" s="9"/>
-      <c r="B65" s="71" t="s">
+      <c r="B65" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="C65" s="70" t="s">
+      <c r="C65" t="s">
         <v>34</v>
       </c>
-      <c r="D65" s="70" t="s">
+      <c r="D65" t="s">
         <v>216</v>
       </c>
-      <c r="E65" s="70">
+      <c r="E65">
         <v>2</v>
       </c>
-      <c r="F65" s="70"/>
       <c r="G65" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A66" s="11"/>
-      <c r="B66" s="73" t="s">
+      <c r="B66" s="13" t="s">
         <v>224</v>
       </c>
       <c r="C66" s="12" t="s">
@@ -5828,7 +6057,7 @@
       <c r="A67" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="B67" s="72" t="s">
+      <c r="B67" s="8" t="s">
         <v>226</v>
       </c>
       <c r="C67" s="7" t="s">
@@ -5849,26 +6078,25 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A68" s="9"/>
-      <c r="B68" s="71" t="s">
+      <c r="B68" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="C68" s="70" t="s">
+      <c r="C68" t="s">
         <v>34</v>
       </c>
-      <c r="D68" s="70" t="s">
+      <c r="D68" t="s">
         <v>64</v>
       </c>
-      <c r="E68" s="69">
+      <c r="E68">
         <v>8</v>
       </c>
-      <c r="F68" s="70"/>
       <c r="G68" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A69" s="11"/>
-      <c r="B69" s="73" t="s">
+      <c r="B69" s="13" t="s">
         <v>228</v>
       </c>
       <c r="C69" s="12" t="s">
@@ -6322,6 +6550,155 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA7F90A7-C149-4E5C-87DE-7BE02A71DC09}">
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.75" customWidth="1"/>
+    <col min="2" max="2" width="70.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" customWidth="1"/>
+    <col min="6" max="6" width="31.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E1" t="s">
+        <v>247</v>
+      </c>
+      <c r="I1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I2" t="s">
+        <v>241</v>
+      </c>
+      <c r="J2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" s="69">
+        <v>46221</v>
+      </c>
+      <c r="B3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E3" s="69">
+        <v>46221</v>
+      </c>
+      <c r="F3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>232</v>
+      </c>
+      <c r="F5" t="s">
+        <v>246</v>
+      </c>
+      <c r="I5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B6" t="s">
+        <v>233</v>
+      </c>
+      <c r="I6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>234</v>
+      </c>
+      <c r="I7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>235</v>
+      </c>
+      <c r="I8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>236</v>
+      </c>
+      <c r="I9" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>256</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB8A7F07-4822-4AA8-B3C3-66F7A08D4E6E}">
   <dimension ref="A2:S36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -7209,7 +7586,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7012B8F-1C48-446B-B3CE-6022D8D4AF46}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -7275,7 +7652,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61B5AFA5-DA2E-4B9D-AA4F-6348B1D1D3C1}">
   <dimension ref="B2:P14"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -7405,7 +7782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5C4C0C2-367A-48F7-A4B4-6D80F4D5CB06}">
   <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -7554,7 +7931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC62AB97-61B1-41EB-8933-806BF4A80E1C}">
   <dimension ref="B1:T59"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -7893,7 +8270,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CADF38F-73BE-4B6B-BA66-331B33FA1371}">
   <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D722D533-9403-40A2-B7C6-DD07E74C2DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F76BD4-0A64-4E49-A86A-15A9BA0E193D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23250" yWindow="1185" windowWidth="21600" windowHeight="13440" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-28920" yWindow="0" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="262">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1766,6 +1766,44 @@
     <t>SE、BGMの実装</t>
     <rPh sb="7" eb="9">
       <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通常攻撃をスピンでキャンセルできるように</t>
+    <rPh sb="0" eb="4">
+      <t>ツウジョウコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>通常攻撃をシフトでキャンセルできるように</t>
+    <rPh sb="0" eb="4">
+      <t>ツウジョウコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス登場演出をスキップできるようにする</t>
+    <rPh sb="2" eb="6">
+      <t>トウジョウエンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備考欄</t>
+    <rPh sb="0" eb="3">
+      <t>ビコウラン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>処理落ちしてるように見える…</t>
+    <rPh sb="0" eb="3">
+      <t>ショリオ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ミ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6551,31 +6589,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA7F90A7-C149-4E5C-87DE-7BE02A71DC09}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.75" customWidth="1"/>
     <col min="2" max="2" width="70.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" customWidth="1"/>
-    <col min="6" max="6" width="31.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" customWidth="1"/>
+    <col min="7" max="7" width="31.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>229</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>247</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>240</v>
       </c>
@@ -6585,111 +6624,147 @@
       <c r="C2" t="s">
         <v>242</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F2" t="s">
         <v>240</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>243</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>242</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>241</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" s="69">
         <v>46221</v>
       </c>
       <c r="B3" t="s">
         <v>230</v>
       </c>
-      <c r="E3" s="69">
+      <c r="C3" s="69">
         <v>46221</v>
       </c>
-      <c r="F3" t="s">
+      <c r="D3" s="69"/>
+      <c r="F3" s="69">
+        <v>46221</v>
+      </c>
+      <c r="G3" t="s">
         <v>244</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
         <v>231</v>
       </c>
-      <c r="F4" t="s">
+      <c r="C4" s="69">
+        <v>46221</v>
+      </c>
+      <c r="D4" s="69" t="s">
+        <v>261</v>
+      </c>
+      <c r="G4" t="s">
         <v>245</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
         <v>232</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>246</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
         <v>233</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
         <v>234</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
         <v>235</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
         <v>236</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B10" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
         <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>257</v>
+      </c>
+      <c r="C14" s="69">
+        <v>46221</v>
+      </c>
+      <c r="D14" s="69"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>258</v>
+      </c>
+      <c r="C15" s="69">
+        <v>46221</v>
+      </c>
+      <c r="D15" s="69"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\SummerGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F76BD4-0A64-4E49-A86A-15A9BA0E193D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A285BFE-9364-4133-A8D2-72A2C5E66C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="0" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="263">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1804,6 +1804,13 @@
     </rPh>
     <rPh sb="10" eb="11">
       <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チュートリアルを作る</t>
+    <rPh sb="8" eb="9">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6589,7 +6596,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA7F90A7-C149-4E5C-87DE-7BE02A71DC09}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.75" customWidth="1"/>
@@ -6765,6 +6772,14 @@
     <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
         <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" s="69">
+        <v>46224</v>
+      </c>
+      <c r="B17" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A285BFE-9364-4133-A8D2-72A2C5E66C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9FE089-8FA3-4A36-BBF7-10CE60D34883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="265">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1811,6 +1811,32 @@
     <t>チュートリアルを作る</t>
     <rPh sb="8" eb="9">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒット時のエフェクト、微振動を実装する(ヒットストップだけだとしょぼいため)</t>
+    <rPh sb="3" eb="4">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ビシンドウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロックオンしていないときに敵に攻撃が当たったらロックオンする</t>
+    <rPh sb="13" eb="14">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ア</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6596,11 +6622,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA7F90A7-C149-4E5C-87DE-7BE02A71DC09}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.75" customWidth="1"/>
-    <col min="2" max="2" width="70.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="76.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.875" customWidth="1"/>
@@ -6774,12 +6800,25 @@
         <v>259</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" s="69">
         <v>46224</v>
       </c>
       <c r="B17" t="s">
         <v>262</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>263</v>
+      </c>
+      <c r="C18" s="69">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9FE089-8FA3-4A36-BBF7-10CE60D34883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A0A9E9-E732-486C-84C3-E759464CDA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="272">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1325,17 +1325,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>スキル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>雑魚敵</t>
-    <rPh sb="0" eb="3">
-      <t>ザコテキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ボスの攻撃</t>
     <rPh sb="3" eb="5">
       <t>コウゲキ</t>
@@ -1382,10 +1371,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>サイコネ？</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>操作ガイドUIイメージ</t>
     <rPh sb="0" eb="2">
       <t>ソウサ</t>
@@ -1798,16 +1783,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>処理落ちしてるように見える…</t>
-    <rPh sb="0" eb="3">
-      <t>ショリオ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>チュートリアルを作る</t>
     <rPh sb="8" eb="9">
       <t>ツク</t>
@@ -1838,6 +1813,80 @@
     <rPh sb="18" eb="19">
       <t>ア</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラのめり込みをどうにかする</t>
+    <rPh sb="6" eb="7">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CPQ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム大祭</t>
+    <rPh sb="3" eb="5">
+      <t>タイサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バンナム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B+</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A+</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中での攻撃で浮いてる感を出す</t>
+    <rPh sb="0" eb="2">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスのエフェクトを実装する</t>
+    <rPh sb="9" eb="11">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームシーン以外を仕上げる</t>
+    <rPh sb="6" eb="8">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A-</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1907,7 +1956,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2275,7 +2324,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2360,9 +2409,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2438,52 +2484,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="24" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="25" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="26" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5419,7 +5429,7 @@
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="6"/>
       <c r="B30" s="8" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>34</v>
@@ -5440,7 +5450,7 @@
     <row r="31" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="11"/>
       <c r="B31" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>34</v>
@@ -5505,7 +5515,7 @@
     <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" s="9"/>
       <c r="B34" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C34" t="s">
         <v>180</v>
@@ -5526,7 +5536,7 @@
     <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="9"/>
       <c r="B35" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C35" t="s">
         <v>100</v>
@@ -5547,7 +5557,7 @@
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="9"/>
       <c r="B36" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D36" t="s">
         <v>62</v>
@@ -5565,7 +5575,7 @@
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="9"/>
       <c r="B37" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D37" t="s">
         <v>62</v>
@@ -5996,16 +6006,16 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E60" s="7">
         <v>2</v>
@@ -6018,13 +6028,13 @@
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" s="9"/>
       <c r="B61" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C61" t="s">
         <v>34</v>
       </c>
       <c r="D61" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -6036,13 +6046,13 @@
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" s="9"/>
       <c r="B62" s="10" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C62" t="s">
         <v>34</v>
       </c>
       <c r="D62" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E62">
         <v>2</v>
@@ -6054,13 +6064,13 @@
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" s="9"/>
       <c r="B63" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C63" t="s">
         <v>34</v>
       </c>
       <c r="D63" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E63">
         <v>2</v>
@@ -6072,13 +6082,13 @@
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64" s="9"/>
       <c r="B64" s="10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C64" t="s">
         <v>34</v>
       </c>
       <c r="D64" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E64">
         <v>2</v>
@@ -6090,13 +6100,13 @@
     <row r="65" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A65" s="9"/>
       <c r="B65" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C65" t="s">
         <v>34</v>
       </c>
       <c r="D65" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E65">
         <v>2</v>
@@ -6108,13 +6118,13 @@
     <row r="66" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A66" s="11"/>
       <c r="B66" s="13" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>34</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E66" s="12">
         <v>2</v>
@@ -6126,10 +6136,10 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A67" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>34</v>
@@ -6150,7 +6160,7 @@
     <row r="68" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A68" s="9"/>
       <c r="B68" s="10" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C68" t="s">
         <v>34</v>
@@ -6168,7 +6178,7 @@
     <row r="69" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A69" s="11"/>
       <c r="B69" s="13" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>34</v>
@@ -6622,203 +6632,297 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA7F90A7-C149-4E5C-87DE-7BE02A71DC09}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.75" customWidth="1"/>
     <col min="2" max="2" width="76.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.875" customWidth="1"/>
-    <col min="7" max="7" width="31.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.875" customWidth="1"/>
+    <col min="8" max="8" width="31.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G1" t="s">
+        <v>244</v>
+      </c>
+      <c r="K1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H2" t="s">
+        <v>240</v>
+      </c>
+      <c r="I2" t="s">
+        <v>239</v>
+      </c>
+      <c r="K2" t="s">
+        <v>238</v>
+      </c>
+      <c r="L2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A3" s="53">
+        <v>46221</v>
+      </c>
+      <c r="B3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="53">
+        <v>46221</v>
+      </c>
+      <c r="E3" s="53"/>
+      <c r="G3" s="53">
+        <v>46221</v>
+      </c>
+      <c r="H3" t="s">
+        <v>241</v>
+      </c>
+      <c r="K3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="53">
+        <v>46221</v>
+      </c>
+      <c r="E4" s="53"/>
+      <c r="H4" t="s">
+        <v>242</v>
+      </c>
+      <c r="K4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
         <v>229</v>
       </c>
-      <c r="F1" t="s">
-        <v>247</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="C5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="53">
+        <v>46225</v>
+      </c>
+      <c r="H5" t="s">
+        <v>243</v>
+      </c>
+      <c r="K5" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D2" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>102</v>
+      </c>
+      <c r="K6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" t="s">
+        <v>102</v>
+      </c>
+      <c r="K7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" t="s">
+        <v>265</v>
+      </c>
+      <c r="K8" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" t="s">
+        <v>101</v>
+      </c>
+      <c r="K9" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>235</v>
+      </c>
+      <c r="C11" t="s">
+        <v>266</v>
+      </c>
+      <c r="D11" s="53">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C12" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>253</v>
+      </c>
+      <c r="C13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>254</v>
+      </c>
+      <c r="C14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="53">
+        <v>46221</v>
+      </c>
+      <c r="E14" s="53"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>255</v>
+      </c>
+      <c r="C15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" s="53">
+        <v>46221</v>
+      </c>
+      <c r="E15" s="53"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C16" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A17" s="53">
+        <v>46224</v>
+      </c>
+      <c r="B17" t="s">
+        <v>258</v>
+      </c>
+      <c r="C17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>259</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="53">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
         <v>260</v>
       </c>
-      <c r="F2" t="s">
-        <v>240</v>
-      </c>
-      <c r="G2" t="s">
-        <v>243</v>
-      </c>
-      <c r="H2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J2" t="s">
-        <v>241</v>
-      </c>
-      <c r="K2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A3" s="69">
-        <v>46221</v>
-      </c>
-      <c r="B3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C3" s="69">
-        <v>46221</v>
-      </c>
-      <c r="D3" s="69"/>
-      <c r="F3" s="69">
-        <v>46221</v>
-      </c>
-      <c r="G3" t="s">
-        <v>244</v>
-      </c>
-      <c r="J3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B4" t="s">
-        <v>231</v>
-      </c>
-      <c r="C4" s="69">
-        <v>46221</v>
-      </c>
-      <c r="D4" s="69" t="s">
+      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A20" s="53">
+        <v>46225</v>
+      </c>
+      <c r="B20" t="s">
         <v>261</v>
       </c>
-      <c r="G4" t="s">
-        <v>245</v>
-      </c>
-      <c r="J4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B5" t="s">
-        <v>232</v>
-      </c>
-      <c r="G5" t="s">
-        <v>246</v>
-      </c>
-      <c r="J5" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B6" t="s">
-        <v>233</v>
-      </c>
-      <c r="J6" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B7" t="s">
-        <v>234</v>
-      </c>
-      <c r="J7" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B8" t="s">
-        <v>235</v>
-      </c>
-      <c r="J8" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B9" t="s">
-        <v>236</v>
-      </c>
-      <c r="J9" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B10" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B11" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B12" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B13" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B14" t="s">
-        <v>257</v>
-      </c>
-      <c r="C14" s="69">
-        <v>46221</v>
-      </c>
-      <c r="D14" s="69"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B15" t="s">
-        <v>258</v>
-      </c>
-      <c r="C15" s="69">
-        <v>46221</v>
-      </c>
-      <c r="D15" s="69"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="B16" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="69">
-        <v>46224</v>
-      </c>
-      <c r="B17" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B18" t="s">
-        <v>263</v>
-      </c>
-      <c r="C18" s="69">
-        <v>46224</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B19" t="s">
-        <v>264</v>
+      <c r="C20" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>268</v>
+      </c>
+      <c r="C21" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B22" t="s">
+        <v>269</v>
+      </c>
+      <c r="C22" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B23" t="s">
+        <v>270</v>
+      </c>
+      <c r="C23" t="s">
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -6829,10 +6933,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB8A7F07-4822-4AA8-B3C3-66F7A08D4E6E}">
-  <dimension ref="A2:S36"/>
+  <dimension ref="A2:I36"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
       <c r="D2" t="s">
         <v>62</v>
       </c>
@@ -6849,19 +6953,19 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="D3" s="17"/>
       <c r="E3" s="18"/>
       <c r="F3" s="19"/>
       <c r="G3" s="20"/>
       <c r="H3" s="21"/>
     </row>
-    <row r="4" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="14" t="s">
         <v>57</v>
       </c>
@@ -6884,7 +6988,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B6" s="9"/>
       <c r="G6">
         <v>1</v>
@@ -6893,7 +6997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B7" s="9">
         <v>3</v>
       </c>
@@ -6916,7 +7020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B8" s="9">
         <v>10</v>
       </c>
@@ -6939,7 +7043,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B9" s="9">
         <v>17</v>
       </c>
@@ -6962,7 +7066,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B10" s="9">
         <v>24</v>
       </c>
@@ -6985,7 +7089,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="11">
         <v>31</v>
       </c>
@@ -6996,15 +7100,12 @@
       <c r="G11" s="12"/>
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B12" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="2:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B13" s="6" t="s">
         <v>57</v>
       </c>
@@ -7026,74 +7127,30 @@
       <c r="H13" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="J13" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="B14" s="31"/>
-      <c r="C14" s="43">
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B14" s="30"/>
+      <c r="C14" s="42">
         <v>1</v>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="42">
         <v>2</v>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="42">
         <v>3</v>
       </c>
-      <c r="F14" s="43">
+      <c r="F14" s="42">
         <v>4</v>
       </c>
-      <c r="G14" s="43">
+      <c r="G14" s="42">
         <v>5</v>
       </c>
-      <c r="H14" s="44">
+      <c r="H14" s="43">
         <v>6</v>
       </c>
-      <c r="J14" s="31"/>
-      <c r="K14" s="32">
-        <v>1</v>
-      </c>
-      <c r="L14" s="32">
-        <v>2</v>
-      </c>
-      <c r="M14" s="32">
-        <v>3</v>
-      </c>
-      <c r="N14" s="32">
-        <v>4</v>
-      </c>
-      <c r="O14" s="32">
-        <v>5</v>
-      </c>
-      <c r="P14" s="54">
-        <v>6</v>
-      </c>
-      <c r="R14" s="21"/>
-      <c r="S14" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="B15" s="45">
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B15" s="44">
         <v>7</v>
       </c>
       <c r="C15" s="23">
@@ -7111,37 +7168,12 @@
       <c r="G15" s="23">
         <v>12</v>
       </c>
-      <c r="H15" s="51">
+      <c r="H15" s="50">
         <v>13</v>
       </c>
-      <c r="J15" s="55">
-        <v>7</v>
-      </c>
-      <c r="K15" s="56">
-        <v>8</v>
-      </c>
-      <c r="L15" s="56">
-        <v>9</v>
-      </c>
-      <c r="M15" s="57">
-        <v>10</v>
-      </c>
-      <c r="N15" s="57">
-        <v>11</v>
-      </c>
-      <c r="O15" s="57">
-        <v>12</v>
-      </c>
-      <c r="P15" s="58">
-        <v>13</v>
-      </c>
-      <c r="R15" s="67"/>
-      <c r="S15" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.4">
-      <c r="B16" s="45">
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B16" s="44">
         <v>14</v>
       </c>
       <c r="C16" s="23">
@@ -7159,37 +7191,12 @@
       <c r="G16" s="23">
         <v>19</v>
       </c>
-      <c r="H16" s="51">
+      <c r="H16" s="50">
         <v>20</v>
       </c>
-      <c r="J16" s="59">
-        <v>14</v>
-      </c>
-      <c r="K16" s="57">
-        <v>15</v>
-      </c>
-      <c r="L16" s="57">
-        <v>16</v>
-      </c>
-      <c r="M16" s="57">
-        <v>17</v>
-      </c>
-      <c r="N16" s="60">
-        <v>18</v>
-      </c>
-      <c r="O16" s="60">
-        <v>19</v>
-      </c>
-      <c r="P16" s="62">
-        <v>20</v>
-      </c>
-      <c r="R16" s="17"/>
-      <c r="S16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="B17" s="45">
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B17" s="44">
         <v>21</v>
       </c>
       <c r="C17" s="23">
@@ -7207,68 +7214,31 @@
       <c r="G17" s="23">
         <v>26</v>
       </c>
-      <c r="H17" s="51">
+      <c r="H17" s="50">
         <v>27</v>
       </c>
-      <c r="J17" s="61">
-        <v>21</v>
-      </c>
-      <c r="K17" s="60">
-        <v>22</v>
-      </c>
-      <c r="L17" s="60">
-        <v>23</v>
-      </c>
-      <c r="M17" s="60">
-        <v>24</v>
-      </c>
-      <c r="N17" s="60">
-        <v>25</v>
-      </c>
-      <c r="O17" s="60">
-        <v>26</v>
-      </c>
-      <c r="P17" s="62">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="52">
+    </row>
+    <row r="18" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="51">
         <v>28</v>
       </c>
-      <c r="C18" s="53">
+      <c r="C18" s="52">
         <v>29</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="52">
         <v>30</v>
       </c>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="42"/>
-      <c r="J18" s="63">
-        <v>28</v>
-      </c>
-      <c r="K18" s="64">
-        <v>29</v>
-      </c>
-      <c r="L18" s="64">
-        <v>30</v>
-      </c>
-      <c r="M18" s="41"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="41"/>
-      <c r="P18" s="42"/>
-    </row>
-    <row r="19" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="41"/>
+    </row>
+    <row r="19" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B19" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="J19" s="22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="20" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B20" s="6" t="s">
         <v>57</v>
       </c>
@@ -7290,62 +7260,26 @@
       <c r="H20" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="J20" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="P20" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="B21" s="31"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="43">
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B21" s="30"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="42">
         <v>1</v>
       </c>
-      <c r="F21" s="43">
+      <c r="F21" s="42">
         <v>2</v>
       </c>
-      <c r="G21" s="43">
+      <c r="G21" s="42">
         <v>3</v>
       </c>
-      <c r="H21" s="44">
+      <c r="H21" s="43">
         <v>4</v>
       </c>
-      <c r="J21" s="31"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="43">
-        <v>1</v>
-      </c>
-      <c r="N21" s="43">
-        <v>2</v>
-      </c>
-      <c r="O21" s="43">
-        <v>3</v>
-      </c>
-      <c r="P21" s="44">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="B22" s="45">
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B22" s="44">
         <v>5</v>
       </c>
       <c r="C22" s="23">
@@ -7363,42 +7297,21 @@
       <c r="G22" s="25">
         <v>10</v>
       </c>
-      <c r="H22" s="46">
+      <c r="H22" s="45">
         <v>11</v>
       </c>
-      <c r="J22" s="45">
-        <v>5</v>
-      </c>
-      <c r="K22" s="23">
-        <v>6</v>
-      </c>
-      <c r="L22" s="23">
-        <v>7</v>
-      </c>
-      <c r="M22" s="23">
-        <v>8</v>
-      </c>
-      <c r="N22" s="23">
-        <v>9</v>
-      </c>
-      <c r="O22" s="23">
-        <v>10</v>
-      </c>
-      <c r="P22" s="51">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>206</v>
-      </c>
-      <c r="B23" s="68">
+        <v>204</v>
+      </c>
+      <c r="B23" s="54">
         <v>12</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="55">
         <v>13</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="55">
         <v>14</v>
       </c>
       <c r="E23" s="25">
@@ -7410,33 +7323,12 @@
       <c r="G23" s="25">
         <v>17</v>
       </c>
-      <c r="H23" s="46">
+      <c r="H23" s="45">
         <v>18</v>
       </c>
-      <c r="J23" s="45">
-        <v>12</v>
-      </c>
-      <c r="K23" s="23">
-        <v>13</v>
-      </c>
-      <c r="L23" s="23">
-        <v>14</v>
-      </c>
-      <c r="M23" s="23">
-        <v>15</v>
-      </c>
-      <c r="N23" s="56">
-        <v>16</v>
-      </c>
-      <c r="O23" s="56">
-        <v>17</v>
-      </c>
-      <c r="P23" s="65">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="B24" s="47">
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B24" s="46">
         <v>19</v>
       </c>
       <c r="C24" s="25">
@@ -7454,77 +7346,37 @@
       <c r="G24" s="25">
         <v>24</v>
       </c>
-      <c r="H24" s="46">
+      <c r="H24" s="45">
         <v>25</v>
       </c>
-      <c r="J24" s="55">
-        <v>19</v>
-      </c>
-      <c r="K24" s="56">
-        <v>20</v>
-      </c>
-      <c r="L24" s="56">
-        <v>21</v>
-      </c>
-      <c r="M24" s="56">
-        <v>22</v>
-      </c>
-      <c r="N24" s="56">
-        <v>23</v>
-      </c>
-      <c r="O24" s="56">
-        <v>24</v>
-      </c>
-      <c r="P24" s="65">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="48">
+    </row>
+    <row r="25" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B25" s="47">
         <v>26</v>
       </c>
-      <c r="C25" s="49">
+      <c r="C25" s="48">
         <v>27</v>
       </c>
-      <c r="D25" s="49">
+      <c r="D25" s="48">
         <v>28</v>
       </c>
-      <c r="E25" s="49">
+      <c r="E25" s="48">
         <v>29</v>
       </c>
-      <c r="F25" s="50">
+      <c r="F25" s="49">
         <v>30</v>
       </c>
-      <c r="G25" s="50">
+      <c r="G25" s="49">
         <v>31</v>
       </c>
-      <c r="H25" s="42"/>
-      <c r="J25" s="66">
-        <v>26</v>
-      </c>
-      <c r="K25" s="41">
-        <v>27</v>
-      </c>
-      <c r="L25" s="41">
-        <v>28</v>
-      </c>
-      <c r="M25" s="41">
-        <v>29</v>
-      </c>
-      <c r="N25" s="41">
-        <v>30</v>
-      </c>
-      <c r="O25" s="41">
-        <v>31</v>
-      </c>
-      <c r="P25" s="42"/>
-    </row>
-    <row r="26" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="H25" s="41"/>
+    </row>
+    <row r="26" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B26" s="24" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B27" s="6" t="s">
         <v>57</v>
       </c>
@@ -7547,19 +7399,19 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="B28" s="31"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="33">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B28" s="30"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="32">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="B29" s="34">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B29" s="33">
         <v>2</v>
       </c>
       <c r="C29" s="26">
@@ -7577,12 +7429,12 @@
       <c r="G29" s="26">
         <v>7</v>
       </c>
-      <c r="H29" s="35">
+      <c r="H29" s="34">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="B30" s="34">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B30" s="33">
         <v>9</v>
       </c>
       <c r="C30" s="26">
@@ -7597,18 +7449,18 @@
       <c r="F30" s="26">
         <v>13</v>
       </c>
-      <c r="G30" s="26">
+      <c r="G30" s="55">
         <v>14</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="56">
         <v>15</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
-        <v>207</v>
-      </c>
-      <c r="B31" s="34">
+      <c r="I30" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B31" s="33">
         <v>16</v>
       </c>
       <c r="C31" s="26">
@@ -7620,51 +7472,57 @@
       <c r="E31" s="26">
         <v>19</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="55">
         <v>20</v>
       </c>
       <c r="G31" s="27">
         <v>21</v>
       </c>
-      <c r="H31" s="36">
+      <c r="H31" s="35">
         <v>22</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="B32" s="37">
+      <c r="I31" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B32" s="36">
         <v>23</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="55">
         <v>24</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="55">
         <v>25</v>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="55">
         <v>26</v>
       </c>
-      <c r="F32" s="28">
+      <c r="F32" s="55">
         <v>27</v>
       </c>
-      <c r="G32" s="28">
+      <c r="G32" s="55">
         <v>28</v>
       </c>
-      <c r="H32" s="38">
+      <c r="H32" s="37">
         <v>29</v>
       </c>
+      <c r="I32" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="33" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="39">
+      <c r="B33" s="38">
         <v>30</v>
       </c>
-      <c r="C33" s="40">
+      <c r="C33" s="39">
         <v>31</v>
       </c>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="42"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="41"/>
     </row>
     <row r="34" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B34" s="24" t="s">
@@ -7697,13 +7555,13 @@
     <row r="36" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B36" s="1"/>
       <c r="C36" s="2"/>
-      <c r="D36" s="29">
+      <c r="D36" s="28">
         <v>1</v>
       </c>
-      <c r="E36" s="29">
+      <c r="E36" s="28">
         <v>2</v>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="29">
         <v>3</v>
       </c>
       <c r="G36" s="2"/>
@@ -8084,7 +7942,7 @@
         <v>187</v>
       </c>
       <c r="O2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.4">
@@ -8105,7 +7963,7 @@
       </c>
       <c r="K5" s="10"/>
       <c r="P5" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.4">
@@ -8130,7 +7988,7 @@
         <v>43</v>
       </c>
       <c r="T9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.4">
@@ -8722,27 +8580,27 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B60" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B61" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B62" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B63" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B64" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A0A9E9-E732-486C-84C3-E759464CDA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6166CC9-E9D1-4B4A-A75D-AD8D6C336AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="273">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1887,6 +1887,10 @@
   </si>
   <si>
     <t>A-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>K2</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1911,7 +1915,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1957,6 +1961,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2324,7 +2334,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2494,6 +2504,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6889,6 +6902,9 @@
       <c r="C19" t="s">
         <v>100</v>
       </c>
+      <c r="D19" s="53">
+        <v>46226</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="53">
@@ -7343,11 +7359,14 @@
       <c r="F24" s="25">
         <v>23</v>
       </c>
-      <c r="G24" s="25">
+      <c r="G24" s="57">
         <v>24</v>
       </c>
       <c r="H24" s="45">
         <v>25</v>
+      </c>
+      <c r="I24" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6166CC9-E9D1-4B4A-A75D-AD8D6C336AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4C2649-F01F-48ED-8140-932B43C85AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="272">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1148,9 +1148,6 @@
   <si>
     <t>ターゲットマネージャー</t>
     <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作業中</t>
   </si>
   <si>
     <t>ライジングフレイム</t>
@@ -4839,11 +4836,11 @@
       </c>
       <c r="K4">
         <f>SUMIFS(E4:E99,G4:G99,"未着手") +SUMIFS(E4:E99,G4:G99,"作業中")</f>
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="L4">
         <f xml:space="preserve"> 1 - K4 / J4</f>
-        <v>0.78453038674033149</v>
+        <v>0.92265193370165743</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
@@ -4875,11 +4872,11 @@
       </c>
       <c r="K5">
         <f>SUMIFS(E4:E99,G4:G99,"未着手",D4:D99,"プロト") +SUMIFS(E4:E99,G4:G99,"作業中",D4:D99,"プロト")</f>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <f xml:space="preserve"> 1 - K5 / J5</f>
-        <v>0.89032258064516134</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
@@ -4911,11 +4908,11 @@
       </c>
       <c r="K6">
         <f>SUMIFS(E4:E99,G4:G99,"未着手",D4:D99,"アルファ") +SUMIFS(E4:E99,G4:G99,"作業中",D4:D99,"アルファ")</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <f t="shared" ref="L6:L8" si="0" xml:space="preserve"> 1 - K6 / J6</f>
-        <v>0.2857142857142857</v>
+        <v>0.85714285714285721</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
@@ -5075,7 +5072,7 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="9"/>
       <c r="B13" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
         <v>34</v>
@@ -5096,7 +5093,7 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="9"/>
       <c r="B14" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C14" t="s">
         <v>34</v>
@@ -5117,7 +5114,7 @@
     <row r="15" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="9"/>
       <c r="B15" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C15" t="s">
         <v>34</v>
@@ -5413,7 +5410,7 @@
       </c>
       <c r="F28" s="15"/>
       <c r="G28" s="16" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -5442,7 +5439,7 @@
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="6"/>
       <c r="B30" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>34</v>
@@ -5463,7 +5460,7 @@
     <row r="31" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="11"/>
       <c r="B31" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>34</v>
@@ -5483,16 +5480,16 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C32" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>180</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>181</v>
       </c>
       <c r="E32" s="7">
         <v>3</v>
@@ -5507,13 +5504,13 @@
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="9"/>
       <c r="B33" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C33" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33" t="s">
         <v>180</v>
-      </c>
-      <c r="D33" t="s">
-        <v>181</v>
       </c>
       <c r="E33">
         <v>2</v>
@@ -5528,13 +5525,13 @@
     <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" s="9"/>
       <c r="B34" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C34" t="s">
+        <v>179</v>
+      </c>
+      <c r="D34" t="s">
         <v>180</v>
-      </c>
-      <c r="D34" t="s">
-        <v>181</v>
       </c>
       <c r="E34">
         <v>2</v>
@@ -5549,7 +5546,7 @@
     <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="9"/>
       <c r="B35" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C35" t="s">
         <v>100</v>
@@ -5570,7 +5567,7 @@
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="9"/>
       <c r="B36" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D36" t="s">
         <v>62</v>
@@ -5588,7 +5585,7 @@
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="9"/>
       <c r="B37" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D37" t="s">
         <v>62</v>
@@ -5606,13 +5603,13 @@
     <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A38" s="11"/>
       <c r="B38" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="C38" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="D38" s="12" t="s">
         <v>180</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>181</v>
       </c>
       <c r="E38" s="12">
         <v>3</v>
@@ -5626,16 +5623,16 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B39" t="s">
         <v>182</v>
       </c>
-      <c r="B39" t="s">
-        <v>183</v>
-      </c>
       <c r="C39" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D39" t="s">
         <v>180</v>
-      </c>
-      <c r="D39" t="s">
-        <v>181</v>
       </c>
       <c r="E39">
         <v>3</v>
@@ -5650,13 +5647,13 @@
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="9"/>
       <c r="B40" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C40" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D40" t="s">
         <v>180</v>
-      </c>
-      <c r="D40" t="s">
-        <v>181</v>
       </c>
       <c r="E40">
         <v>3</v>
@@ -5671,13 +5668,13 @@
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="9"/>
       <c r="B41" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C41" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D41" t="s">
         <v>180</v>
-      </c>
-      <c r="D41" t="s">
-        <v>181</v>
       </c>
       <c r="E41">
         <v>4</v>
@@ -5692,13 +5689,13 @@
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="9"/>
       <c r="B42" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C42" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D42" t="s">
         <v>180</v>
-      </c>
-      <c r="D42" t="s">
-        <v>181</v>
       </c>
       <c r="E42">
         <v>4</v>
@@ -5713,13 +5710,13 @@
     <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" s="9"/>
       <c r="B43" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C43" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D43" t="s">
         <v>180</v>
-      </c>
-      <c r="D43" t="s">
-        <v>181</v>
       </c>
       <c r="E43">
         <v>2</v>
@@ -5734,13 +5731,13 @@
     <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" s="9"/>
       <c r="B44" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C44" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D44" t="s">
         <v>180</v>
-      </c>
-      <c r="D44" t="s">
-        <v>181</v>
       </c>
       <c r="E44">
         <v>3</v>
@@ -5755,13 +5752,13 @@
     <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45" s="9"/>
       <c r="B45" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C45" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D45" t="s">
         <v>180</v>
-      </c>
-      <c r="D45" t="s">
-        <v>181</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -5776,13 +5773,13 @@
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46" s="9"/>
       <c r="B46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C46" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D46" t="s">
         <v>180</v>
-      </c>
-      <c r="D46" t="s">
-        <v>181</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -5797,13 +5794,13 @@
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" s="9"/>
       <c r="B47" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C47" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D47" t="s">
         <v>180</v>
-      </c>
-      <c r="D47" t="s">
-        <v>181</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -5818,20 +5815,20 @@
     <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" s="9"/>
       <c r="C48" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D48" t="s">
         <v>180</v>
-      </c>
-      <c r="D48" t="s">
-        <v>181</v>
       </c>
       <c r="G48" s="10"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" s="9"/>
       <c r="C49" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D49" t="s">
         <v>180</v>
-      </c>
-      <c r="D49" t="s">
-        <v>181</v>
       </c>
       <c r="G49" s="10"/>
     </row>
@@ -5839,10 +5836,10 @@
       <c r="A50" s="11"/>
       <c r="B50" s="12"/>
       <c r="C50" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D50" s="12" t="s">
         <v>180</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>181</v>
       </c>
       <c r="E50" s="12"/>
       <c r="F50" s="12"/>
@@ -5944,7 +5941,7 @@
       </c>
       <c r="F55" s="12"/>
       <c r="G55" s="13" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
@@ -6019,35 +6016,35 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B60" s="8" t="s">
         <v>214</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>215</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E60" s="7">
         <v>2</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="8" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" s="9"/>
       <c r="B61" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C61" t="s">
         <v>34</v>
       </c>
       <c r="D61" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -6059,13 +6056,13 @@
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" s="9"/>
       <c r="B62" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C62" t="s">
         <v>34</v>
       </c>
       <c r="D62" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E62">
         <v>2</v>
@@ -6077,31 +6074,31 @@
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" s="9"/>
       <c r="B63" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C63" t="s">
         <v>34</v>
       </c>
       <c r="D63" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E63">
         <v>2</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64" s="9"/>
       <c r="B64" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C64" t="s">
         <v>34</v>
       </c>
       <c r="D64" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E64">
         <v>2</v>
@@ -6113,46 +6110,46 @@
     <row r="65" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A65" s="9"/>
       <c r="B65" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C65" t="s">
         <v>34</v>
       </c>
       <c r="D65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E65">
         <v>2</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A66" s="11"/>
       <c r="B66" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>34</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E66" s="12">
         <v>2</v>
       </c>
       <c r="F66" s="12"/>
       <c r="G66" s="13" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A67" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="B67" s="8" t="s">
         <v>222</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>223</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>34</v>
@@ -6173,7 +6170,7 @@
     <row r="68" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A68" s="9"/>
       <c r="B68" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C68" t="s">
         <v>34</v>
@@ -6191,7 +6188,7 @@
     <row r="69" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A69" s="11"/>
       <c r="B69" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>34</v>
@@ -6662,45 +6659,45 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K1" t="s">
         <v>244</v>
-      </c>
-      <c r="K1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B2" t="s">
         <v>237</v>
-      </c>
-      <c r="B2" t="s">
-        <v>238</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
       </c>
       <c r="D2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E2" t="s">
+        <v>256</v>
+      </c>
+      <c r="G2" t="s">
+        <v>236</v>
+      </c>
+      <c r="H2" t="s">
         <v>239</v>
       </c>
-      <c r="E2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
+        <v>238</v>
+      </c>
+      <c r="K2" t="s">
         <v>237</v>
       </c>
-      <c r="H2" t="s">
-        <v>240</v>
-      </c>
-      <c r="I2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>238</v>
-      </c>
-      <c r="L2" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
@@ -6708,7 +6705,7 @@
         <v>46221</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C3" t="s">
         <v>101</v>
@@ -6721,15 +6718,15 @@
         <v>46221</v>
       </c>
       <c r="H3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" t="s">
         <v>101</v>
@@ -6739,15 +6736,15 @@
       </c>
       <c r="E4" s="53"/>
       <c r="H4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C5" t="s">
         <v>101</v>
@@ -6756,59 +6753,62 @@
         <v>46225</v>
       </c>
       <c r="H5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" t="s">
         <v>102</v>
       </c>
       <c r="K6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C7" t="s">
         <v>102</v>
       </c>
       <c r="K7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C9" t="s">
         <v>101</v>
       </c>
+      <c r="D9" s="53">
+        <v>46226</v>
+      </c>
       <c r="K9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C10" t="s">
         <v>100</v>
@@ -6816,10 +6816,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D11" s="53">
         <v>46225</v>
@@ -6827,15 +6827,15 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C13" t="s">
         <v>102</v>
@@ -6843,7 +6843,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C14" t="s">
         <v>101</v>
@@ -6855,7 +6855,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C15" t="s">
         <v>101</v>
@@ -6867,10 +6867,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
@@ -6878,7 +6878,7 @@
         <v>46224</v>
       </c>
       <c r="B17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C17" t="s">
         <v>101</v>
@@ -6886,7 +6886,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B18" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C18" t="s">
         <v>101</v>
@@ -6897,7 +6897,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C19" t="s">
         <v>100</v>
@@ -6911,34 +6911,34 @@
         <v>46225</v>
       </c>
       <c r="B20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C23" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -7319,7 +7319,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B23" s="54">
         <v>12</v>
@@ -7366,7 +7366,7 @@
         <v>25</v>
       </c>
       <c r="I24" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -7475,7 +7475,7 @@
         <v>15</v>
       </c>
       <c r="I30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
@@ -7501,7 +7501,7 @@
         <v>22</v>
       </c>
       <c r="I31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
@@ -7527,7 +7527,7 @@
         <v>29</v>
       </c>
       <c r="I32" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -7958,10 +7958,10 @@
       <c r="J2" s="7"/>
       <c r="K2" s="8"/>
       <c r="L2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="O2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.4">
@@ -7971,18 +7971,18 @@
     <row r="4" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B4" s="9"/>
       <c r="G4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.4">
       <c r="B5" s="9"/>
       <c r="C5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K5" s="10"/>
       <c r="P5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.4">
@@ -8007,7 +8007,7 @@
         <v>43</v>
       </c>
       <c r="T9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.4">
@@ -8062,7 +8062,7 @@
       <c r="J18" s="7"/>
       <c r="K18" s="8"/>
       <c r="L18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.4">
@@ -8138,7 +8138,7 @@
       <c r="J33" s="7"/>
       <c r="K33" s="8"/>
       <c r="L33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.4">
@@ -8214,7 +8214,7 @@
       <c r="J48" s="7"/>
       <c r="K48" s="8"/>
       <c r="L48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.4">
@@ -8557,7 +8557,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C52" t="s">
         <v>2</v>
@@ -8568,23 +8568,23 @@
         <v>89</v>
       </c>
       <c r="C53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B54" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C54" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B55" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.4">
@@ -8599,27 +8599,27 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B60" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B61" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B62" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B63" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B64" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4C2649-F01F-48ED-8140-932B43C85AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDD4531-81DB-4E48-BE27-5A8A17D82D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="プレイヤー設計" sheetId="6" r:id="rId6"/>
     <sheet name="ゲーム画面イメージ" sheetId="7" r:id="rId7"/>
     <sheet name="memo" sheetId="5" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$G$107</definedName>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="276">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1888,6 +1889,37 @@
   </si>
   <si>
     <t>K2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>のこり期間でやること</t>
+    <rPh sb="3" eb="5">
+      <t>キカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラをブラッシュアップする</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵、ステージを増やす</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>その他シーンを仕上げる</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シア</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -8626,4 +8658,35 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A40E5CC-49DB-4C8A-882D-E21B34D11A24}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDD4531-81DB-4E48-BE27-5A8A17D82D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4EE4B92-699E-4AB4-B6DF-CC4CC68F08F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -1983,12 +1983,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1996,6 +1990,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2445,12 +2445,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2470,18 +2464,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="23" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
@@ -2526,16 +2508,34 @@
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="24" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6733,7 +6733,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A3" s="53">
+      <c r="A3" s="47">
         <v>46221</v>
       </c>
       <c r="B3" t="s">
@@ -6742,11 +6742,11 @@
       <c r="C3" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="53">
+      <c r="D3" s="47">
         <v>46221</v>
       </c>
-      <c r="E3" s="53"/>
-      <c r="G3" s="53">
+      <c r="E3" s="47"/>
+      <c r="G3" s="47">
         <v>46221</v>
       </c>
       <c r="H3" t="s">
@@ -6763,10 +6763,10 @@
       <c r="C4" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="53">
+      <c r="D4" s="47">
         <v>46221</v>
       </c>
-      <c r="E4" s="53"/>
+      <c r="E4" s="47"/>
       <c r="H4" t="s">
         <v>241</v>
       </c>
@@ -6781,7 +6781,7 @@
       <c r="C5" t="s">
         <v>101</v>
       </c>
-      <c r="D5" s="53">
+      <c r="D5" s="47">
         <v>46225</v>
       </c>
       <c r="H5" t="s">
@@ -6831,7 +6831,7 @@
       <c r="C9" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="53">
+      <c r="D9" s="47">
         <v>46226</v>
       </c>
       <c r="K9" t="s">
@@ -6853,7 +6853,7 @@
       <c r="C11" t="s">
         <v>265</v>
       </c>
-      <c r="D11" s="53">
+      <c r="D11" s="47">
         <v>46225</v>
       </c>
     </row>
@@ -6880,10 +6880,10 @@
       <c r="C14" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="53">
+      <c r="D14" s="47">
         <v>46221</v>
       </c>
-      <c r="E14" s="53"/>
+      <c r="E14" s="47"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
@@ -6892,10 +6892,10 @@
       <c r="C15" t="s">
         <v>101</v>
       </c>
-      <c r="D15" s="53">
+      <c r="D15" s="47">
         <v>46221</v>
       </c>
-      <c r="E15" s="53"/>
+      <c r="E15" s="47"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
@@ -6906,7 +6906,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A17" s="53">
+      <c r="A17" s="47">
         <v>46224</v>
       </c>
       <c r="B17" t="s">
@@ -6923,7 +6923,7 @@
       <c r="C18" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="47">
         <v>46224</v>
       </c>
     </row>
@@ -6934,12 +6934,12 @@
       <c r="C19" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="53">
+      <c r="D19" s="47">
         <v>46226</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A20" s="53">
+      <c r="A20" s="47">
         <v>46225</v>
       </c>
       <c r="B20" t="s">
@@ -7177,28 +7177,28 @@
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B14" s="30"/>
-      <c r="C14" s="42">
+      <c r="B14" s="28"/>
+      <c r="C14" s="36">
         <v>1</v>
       </c>
-      <c r="D14" s="42">
+      <c r="D14" s="36">
         <v>2</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="36">
         <v>3</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="36">
         <v>4</v>
       </c>
-      <c r="G14" s="42">
+      <c r="G14" s="36">
         <v>5</v>
       </c>
-      <c r="H14" s="43">
+      <c r="H14" s="37">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B15" s="44">
+      <c r="B15" s="38">
         <v>7</v>
       </c>
       <c r="C15" s="23">
@@ -7216,12 +7216,12 @@
       <c r="G15" s="23">
         <v>12</v>
       </c>
-      <c r="H15" s="50">
+      <c r="H15" s="44">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B16" s="44">
+      <c r="B16" s="38">
         <v>14</v>
       </c>
       <c r="C16" s="23">
@@ -7239,12 +7239,12 @@
       <c r="G16" s="23">
         <v>19</v>
       </c>
-      <c r="H16" s="50">
+      <c r="H16" s="44">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B17" s="44">
+      <c r="B17" s="38">
         <v>21</v>
       </c>
       <c r="C17" s="23">
@@ -7262,24 +7262,24 @@
       <c r="G17" s="23">
         <v>26</v>
       </c>
-      <c r="H17" s="50">
+      <c r="H17" s="44">
         <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="51">
+      <c r="B18" s="45">
         <v>28</v>
       </c>
-      <c r="C18" s="52">
+      <c r="C18" s="46">
         <v>29</v>
       </c>
-      <c r="D18" s="52">
+      <c r="D18" s="46">
         <v>30</v>
       </c>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="41"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="35"/>
     </row>
     <row r="19" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B19" s="22" t="s">
@@ -7310,24 +7310,24 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B21" s="30"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="42">
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="36">
         <v>1</v>
       </c>
-      <c r="F21" s="42">
+      <c r="F21" s="36">
         <v>2</v>
       </c>
-      <c r="G21" s="42">
+      <c r="G21" s="36">
         <v>3</v>
       </c>
-      <c r="H21" s="43">
+      <c r="H21" s="37">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B22" s="44">
+      <c r="B22" s="38">
         <v>5</v>
       </c>
       <c r="C22" s="23">
@@ -7345,7 +7345,7 @@
       <c r="G22" s="25">
         <v>10</v>
       </c>
-      <c r="H22" s="45">
+      <c r="H22" s="39">
         <v>11</v>
       </c>
     </row>
@@ -7353,13 +7353,13 @@
       <c r="A23" t="s">
         <v>203</v>
       </c>
-      <c r="B23" s="54">
+      <c r="B23" s="48">
         <v>12</v>
       </c>
-      <c r="C23" s="55">
+      <c r="C23" s="49">
         <v>13</v>
       </c>
-      <c r="D23" s="55">
+      <c r="D23" s="49">
         <v>14</v>
       </c>
       <c r="E23" s="25">
@@ -7371,12 +7371,12 @@
       <c r="G23" s="25">
         <v>17</v>
       </c>
-      <c r="H23" s="45">
+      <c r="H23" s="39">
         <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B24" s="46">
+      <c r="B24" s="40">
         <v>19</v>
       </c>
       <c r="C24" s="25">
@@ -7391,10 +7391,10 @@
       <c r="F24" s="25">
         <v>23</v>
       </c>
-      <c r="G24" s="57">
+      <c r="G24" s="51">
         <v>24</v>
       </c>
-      <c r="H24" s="45">
+      <c r="H24" s="39">
         <v>25</v>
       </c>
       <c r="I24" t="s">
@@ -7402,25 +7402,25 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="47">
+      <c r="B25" s="41">
         <v>26</v>
       </c>
-      <c r="C25" s="48">
+      <c r="C25" s="42">
         <v>27</v>
       </c>
-      <c r="D25" s="48">
+      <c r="D25" s="42">
         <v>28</v>
       </c>
-      <c r="E25" s="48">
+      <c r="E25" s="42">
         <v>29</v>
       </c>
-      <c r="F25" s="49">
+      <c r="F25" s="43">
         <v>30</v>
       </c>
-      <c r="G25" s="49">
+      <c r="G25" s="43">
         <v>31</v>
       </c>
-      <c r="H25" s="41"/>
+      <c r="H25" s="35"/>
     </row>
     <row r="26" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B26" s="24" t="s">
@@ -7451,18 +7451,18 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B28" s="30"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="32">
+      <c r="B28" s="28"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B29" s="33">
+      <c r="B29" s="31">
         <v>2</v>
       </c>
       <c r="C29" s="26">
@@ -7480,30 +7480,30 @@
       <c r="G29" s="26">
         <v>7</v>
       </c>
-      <c r="H29" s="34">
+      <c r="H29" s="32">
         <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B30" s="33">
+      <c r="B30" s="31">
         <v>9</v>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="55">
         <v>10</v>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="55">
         <v>11</v>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="55">
         <v>12</v>
       </c>
-      <c r="F30" s="26">
+      <c r="F30" s="55">
         <v>13</v>
       </c>
-      <c r="G30" s="55">
+      <c r="G30" s="49">
         <v>14</v>
       </c>
-      <c r="H30" s="56">
+      <c r="H30" s="50">
         <v>15</v>
       </c>
       <c r="I30" t="s">
@@ -7511,25 +7511,25 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B31" s="33">
+      <c r="B31" s="56">
         <v>16</v>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="55">
         <v>17</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="55">
         <v>18</v>
       </c>
-      <c r="E31" s="26">
+      <c r="E31" s="55">
         <v>19</v>
       </c>
-      <c r="F31" s="55">
+      <c r="F31" s="49">
         <v>20</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="55">
         <v>21</v>
       </c>
-      <c r="H31" s="35">
+      <c r="H31" s="57">
         <v>22</v>
       </c>
       <c r="I31" t="s">
@@ -7537,25 +7537,25 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B32" s="36">
+      <c r="B32" s="56">
         <v>23</v>
       </c>
-      <c r="C32" s="55">
+      <c r="C32" s="49">
         <v>24</v>
       </c>
-      <c r="D32" s="55">
+      <c r="D32" s="49">
         <v>25</v>
       </c>
-      <c r="E32" s="55">
+      <c r="E32" s="49">
         <v>26</v>
       </c>
-      <c r="F32" s="55">
+      <c r="F32" s="49">
         <v>27</v>
       </c>
-      <c r="G32" s="55">
+      <c r="G32" s="49">
         <v>28</v>
       </c>
-      <c r="H32" s="37">
+      <c r="H32" s="33">
         <v>29</v>
       </c>
       <c r="I32" t="s">
@@ -7563,17 +7563,17 @@
       </c>
     </row>
     <row r="33" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="38">
+      <c r="B33" s="52">
         <v>30</v>
       </c>
-      <c r="C33" s="39">
+      <c r="C33" s="53">
         <v>31</v>
       </c>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="41"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="35"/>
     </row>
     <row r="34" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B34" s="24" t="s">
@@ -7606,13 +7606,13 @@
     <row r="36" spans="2:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B36" s="1"/>
       <c r="C36" s="2"/>
-      <c r="D36" s="28">
+      <c r="D36" s="54">
         <v>1</v>
       </c>
-      <c r="E36" s="28">
+      <c r="E36" s="54">
         <v>2</v>
       </c>
-      <c r="F36" s="29">
+      <c r="F36" s="27">
         <v>3</v>
       </c>
       <c r="G36" s="2"/>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4EE4B92-699E-4AB4-B6DF-CC4CC68F08F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C73F830-1DB9-4FCA-8A44-D3EAFAB4C968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-28920" yWindow="0" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="282">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1919,6 +1919,51 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>シア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加する効果音</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>コウカオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃空振り</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カラブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃ヒット</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>足音</t>
+    <rPh sb="0" eb="2">
+      <t>アシオト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テレポート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被弾</t>
+    <rPh sb="0" eb="2">
+      <t>ヒダン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8662,27 +8707,72 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A40E5CC-49DB-4C8A-882D-E21B34D11A24}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C73F830-1DB9-4FCA-8A44-D3EAFAB4C968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0A903D-83EF-47FC-A5B8-40C109BD8E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="0" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="288">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1965,6 +1965,60 @@
     <rPh sb="0" eb="2">
       <t>ヒダン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スピン被弾の効果音</t>
+    <rPh sb="3" eb="5">
+      <t>ヒダン</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>コウカオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シフト攻撃の硬直をキャンセルできるように</t>
+    <rPh sb="3" eb="5">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コウチョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ1の障害物の見た目をやる</t>
+    <rPh sb="6" eb="9">
+      <t>ショウガイブツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージセレクトシーンを作る</t>
+    <rPh sb="12" eb="13">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスとかその他の効果音</t>
+    <rPh sb="6" eb="7">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>コウカオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チュートリアル</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -8707,70 +8761,91 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A40E5CC-49DB-4C8A-882D-E21B34D11A24}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D7" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D9" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B10" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D10" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="D12" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B14" t="s">
         <v>281</v>
       </c>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\SummerGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0A903D-83EF-47FC-A5B8-40C109BD8E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BFCAC8-9393-4C67-B174-26A2C5715A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="0" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="287">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1964,16 +1964,6 @@
     <t>被弾</t>
     <rPh sb="0" eb="2">
       <t>ヒダン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スピン被弾の効果音</t>
-    <rPh sb="3" eb="5">
-      <t>ヒダン</t>
-    </rPh>
-    <rPh sb="6" eb="9">
-      <t>コウカオン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8796,16 +8786,13 @@
       <c r="A7" t="s">
         <v>1</v>
       </c>
-      <c r="D7" t="s">
-        <v>282</v>
-      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
         <v>277</v>
       </c>
       <c r="D8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -8813,7 +8800,7 @@
         <v>278</v>
       </c>
       <c r="D9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -8821,7 +8808,7 @@
         <v>279</v>
       </c>
       <c r="D10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -8829,7 +8816,7 @@
         <v>280</v>
       </c>
       <c r="D11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -8837,7 +8824,7 @@
         <v>216</v>
       </c>
       <c r="D12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SasakiTaiga\Documents\GitHub\SummerGame_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BFCAC8-9393-4C67-B174-26A2C5715A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4968136-4E1E-4BA9-B0B0-A0993C1B3856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-28920" yWindow="0" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="286">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1987,13 +1987,6 @@
     </rPh>
     <rPh sb="12" eb="13">
       <t>メ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ステージセレクトシーンを作る</t>
-    <rPh sb="12" eb="13">
-      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8807,16 +8800,13 @@
       <c r="B10" t="s">
         <v>279</v>
       </c>
-      <c r="D10" t="s">
-        <v>284</v>
-      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
         <v>280</v>
       </c>
       <c r="D11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -8824,7 +8814,7 @@
         <v>216</v>
       </c>
       <c r="D12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4968136-4E1E-4BA9-B0B0-A0993C1B3856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2DA04B-BE74-4C19-A126-CD7B878B4C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="0" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-28320" yWindow="1350" windowWidth="21600" windowHeight="13440" activeTab="8" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="284">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1933,41 +1933,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>攻撃空振り</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カラブ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>攻撃ヒット</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>足音</t>
-    <rPh sb="0" eb="2">
-      <t>アシオト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>テレポート</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被弾</t>
-    <rPh sb="0" eb="2">
-      <t>ヒダン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>シフト攻撃の硬直をキャンセルできるように</t>
     <rPh sb="3" eb="5">
       <t>コウゲキ</t>
@@ -1978,19 +1943,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ステージ1の障害物の見た目をやる</t>
-    <rPh sb="6" eb="9">
-      <t>ショウガイブツ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>メ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ボスとかその他の効果音</t>
     <rPh sb="6" eb="7">
       <t>タ</t>
@@ -2002,6 +1954,34 @@
   </si>
   <si>
     <t>チュートリアル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡</t>
+    <rPh sb="0" eb="2">
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加するエフェクト</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゾンビボス攻撃</t>
+    <rPh sb="5" eb="7">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゾンビボス地面攻撃</t>
+    <rPh sb="5" eb="9">
+      <t>ジメンコウゲキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -8744,7 +8724,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A40E5CC-49DB-4C8A-882D-E21B34D11A24}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
@@ -8777,54 +8757,41 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>277</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D9" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B10" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B11" t="s">
-        <v>280</v>
-      </c>
-      <c r="D11" t="s">
-        <v>284</v>
+      <c r="A11" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>216</v>
-      </c>
-      <c r="D12" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2DA04B-BE74-4C19-A126-CD7B878B4C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A34BC5-2F63-4084-A3EA-C836294D8CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28320" yWindow="1350" windowWidth="21600" windowHeight="13440" activeTab="8" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="283">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1950,10 +1950,6 @@
     <rPh sb="8" eb="11">
       <t>コウカオン</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>チュートリアル</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -8773,25 +8769,22 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>280</v>
-      </c>
-      <c r="D9" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A34BC5-2F63-4084-A3EA-C836294D8CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8BB2D8-A253-4109-97F7-42343A701AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28320" yWindow="1350" windowWidth="21600" windowHeight="13440" activeTab="8" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="287">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1977,6 +1977,52 @@
     <t>ゾンビボス地面攻撃</t>
     <rPh sb="5" eb="9">
       <t>ジメンコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>向かう方向をわかりやすくする</t>
+    <rPh sb="0" eb="1">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵グループを全滅させたときにリアクションをつける</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゼンメツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージクリア後次ステージを選択した状態にする</t>
+    <rPh sb="7" eb="8">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テレポートをもっと活かせるステージを作る</t>
+    <rPh sb="9" eb="10">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -8771,15 +8817,29 @@
       <c r="B9" t="s">
         <v>279</v>
       </c>
+      <c r="D9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="D10" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>280</v>
       </c>
+      <c r="D11" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
         <v>281</v>
+      </c>
+      <c r="D12" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">

--- a/夏ゲームコスト表.xlsx
+++ b/夏ゲームコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\SummerGame_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8BB2D8-A253-4109-97F7-42343A701AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685B7FCD-E9B4-4D0B-8988-AFD88249C876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28320" yWindow="1350" windowWidth="21600" windowHeight="13440" activeTab="8" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
+    <workbookView xWindow="-28320" yWindow="1350" windowWidth="21600" windowHeight="13440" firstSheet="3" activeTab="9" xr2:uid="{81B07F0C-6B3F-4216-A9DE-E30603DB1347}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,8 @@
     <sheet name="プレイヤー設計" sheetId="6" r:id="rId6"/>
     <sheet name="ゲーム画面イメージ" sheetId="7" r:id="rId7"/>
     <sheet name="memo" sheetId="5" r:id="rId8"/>
-    <sheet name="Sheet1" sheetId="9" r:id="rId9"/>
+    <sheet name="Sheet2" sheetId="10" r:id="rId9"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">コスト表!$A$3:$G$107</definedName>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="292">
   <si>
     <t>夏ゲームコスト表</t>
     <rPh sb="0" eb="1">
@@ -1981,16 +1982,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>向かう方向をわかりやすくする</t>
-    <rPh sb="0" eb="1">
-      <t>ム</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ホウコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>敵グループを全滅させたときにリアクションをつける</t>
     <rPh sb="0" eb="1">
       <t>テキ</t>
@@ -2023,6 +2014,69 @@
     </rPh>
     <rPh sb="18" eb="19">
       <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テレポート、必殺技時に自動ロックオンをする</t>
+    <rPh sb="6" eb="10">
+      <t>ヒッサツワザジ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>進む方向をわかりやすくする</t>
+    <rPh sb="0" eb="1">
+      <t>スス</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスとかその他のエフェクト</t>
+    <rPh sb="6" eb="7">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>必殺技を空中でキャンセルして発動できるバグの修正</t>
+    <rPh sb="0" eb="3">
+      <t>ヒッサツワザ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>クウチュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ハツドウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス戦で死んだらボス手前で始まるように</t>
+    <rPh sb="2" eb="3">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>テマエ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ハジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -6776,6 +6830,122 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A40E5CC-49DB-4C8A-882D-E21B34D11A24}">
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>276</v>
+      </c>
+      <c r="E6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>279</v>
+      </c>
+      <c r="E9" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="E10" t="s">
+        <v>287</v>
+      </c>
+      <c r="H10" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>280</v>
+      </c>
+      <c r="E11" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>281</v>
+      </c>
+      <c r="E12" t="s">
+        <v>284</v>
+      </c>
+      <c r="J12" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>282</v>
+      </c>
+      <c r="E13" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="E14" t="s">
+        <v>286</v>
+      </c>
+      <c r="J14" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="E15" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="E16" t="s">
+        <v>291</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA7F90A7-C149-4E5C-87DE-7BE02A71DC09}">
   <dimension ref="A1:L23"/>
@@ -8765,89 +8935,10 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A40E5CC-49DB-4C8A-882D-E21B34D11A24}">
-  <dimension ref="A1:D13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D766C20-A8F3-4B42-B79E-95A60131970E}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>276</v>
-      </c>
-      <c r="D6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B9" t="s">
-        <v>279</v>
-      </c>
-      <c r="D9" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="D10" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>280</v>
-      </c>
-      <c r="D11" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B12" t="s">
-        <v>281</v>
-      </c>
-      <c r="D12" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B13" t="s">
-        <v>282</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
